--- a/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4420D9F7-73E8-441A-B51F-74BACC928EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDE411C-CB91-4771-87FC-995C82F464A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="5" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="101">
   <si>
     <t>Problema/Dominio:</t>
   </si>
@@ -321,9 +321,6 @@
     <t>fechaHoraInicio</t>
   </si>
   <si>
-    <t>NombreAgenda</t>
-  </si>
-  <si>
     <t>Atributo que contiene la información del identificador de una zona común en el contexto de Conjuntos Residenciales</t>
   </si>
   <si>
@@ -336,15 +333,6 @@
     <t>Entero</t>
   </si>
   <si>
-    <t>Atributo que contiene la información del identificador de un inmueble en el contexto de Conjuntos Residenciales</t>
-  </si>
-  <si>
-    <t>tipoZonaInmueble</t>
-  </si>
-  <si>
-    <t>numeroZonaInmueble</t>
-  </si>
-  <si>
     <t>fechaHoraFin</t>
   </si>
   <si>
@@ -358,6 +346,9 @@
   </si>
   <si>
     <t>unidadTiempoUso</t>
+  </si>
+  <si>
+    <t>TipoInmueble</t>
   </si>
 </sst>
 </file>
@@ -410,7 +401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,8 +474,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="46">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -926,30 +923,63 @@
       <right style="thick">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <left/>
+      <right style="thick">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -957,108 +987,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1068,7 +1002,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1226,6 +1160,21 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1349,6 +1298,78 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1364,154 +1385,61 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1951,10 +1879,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="54"/>
+      <c r="B1" s="59"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -2081,75 +2009,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="101" t="str">
+      <c r="B1" s="99" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="102"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="100"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="90"/>
-      <c r="S2" s="91"/>
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="95"/>
+      <c r="S2" s="96"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104" t="s">
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="104"/>
-      <c r="Q3" s="104"/>
-      <c r="R3" s="105" t="s">
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="107" t="s">
+      <c r="S3" s="105" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2205,14 +2133,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="106"/>
-      <c r="S4" s="108"/>
+      <c r="R4" s="120"/>
+      <c r="S4" s="106"/>
     </row>
     <row r="5" spans="1:19" ht="28.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="123" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="126" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -2249,17 +2177,17 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="51"/>
-      <c r="R5" s="137" t="s">
-        <v>92</v>
-      </c>
-      <c r="S5" s="110" t="str">
+      <c r="R5" s="112" t="s">
+        <v>91</v>
+      </c>
+      <c r="S5" s="114" t="str">
         <f>B11</f>
         <v>Turno</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
-      <c r="B6" s="98"/>
+      <c r="A6" s="124"/>
+      <c r="B6" s="127"/>
       <c r="C6" s="51" t="s">
         <v>4</v>
       </c>
@@ -2294,12 +2222,12 @@
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="138"/>
-      <c r="S6" s="111"/>
+      <c r="R6" s="113"/>
+      <c r="S6" s="115"/>
     </row>
     <row r="7" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
-      <c r="B7" s="114" t="s">
+      <c r="A7" s="124"/>
+      <c r="B7" s="128" t="s">
         <v>64</v>
       </c>
       <c r="C7" s="50" t="s">
@@ -2340,11 +2268,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B7,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador de un Agenda  en el contexto de Agendas.</v>
       </c>
-      <c r="S7" s="111"/>
+      <c r="S7" s="115"/>
     </row>
     <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
-      <c r="B8" s="115"/>
+      <c r="A8" s="124"/>
+      <c r="B8" s="129"/>
       <c r="C8" s="50" t="s">
         <v>4</v>
       </c>
@@ -2380,13 +2308,13 @@
       <c r="P8" s="31"/>
       <c r="Q8" s="31"/>
       <c r="R8" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="S8" s="111"/>
+        <v>96</v>
+      </c>
+      <c r="S8" s="115"/>
     </row>
     <row r="9" spans="1:19" ht="58.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="95"/>
-      <c r="B9" s="115"/>
+      <c r="A9" s="124"/>
+      <c r="B9" s="129"/>
       <c r="C9" s="31" t="s">
         <v>90</v>
       </c>
@@ -2417,13 +2345,13 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B7," en el contexto de ",A5," asociado al residente con el identificador' ",J9,"'.")</f>
         <v>Atributo que contiene la información del nombre de un Agenda en el contexto de Agendas asociado al residente con el identificador' fechaHoraInicioAgenda'.</v>
       </c>
-      <c r="S9" s="111"/>
+      <c r="S9" s="115"/>
     </row>
     <row r="10" spans="1:19" ht="58.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="95"/>
-      <c r="B10" s="99"/>
+      <c r="A10" s="124"/>
+      <c r="B10" s="130"/>
       <c r="C10" s="31" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D10" s="31" t="s">
         <v>58</v>
@@ -2452,11 +2380,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B8," en el contexto de ",A6," asociado al residente con el identificador' ",J10,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' fechaHoraFinAgenda'.</v>
       </c>
-      <c r="S10" s="111"/>
+      <c r="S10" s="115"/>
     </row>
     <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="95"/>
-      <c r="B11" s="100" t="s">
+      <c r="A11" s="124"/>
+      <c r="B11" s="122" t="s">
         <v>65</v>
       </c>
       <c r="C11" s="32" t="s">
@@ -2497,11 +2425,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B11,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador de un Turno  en el contexto de Agendas.</v>
       </c>
-      <c r="S11" s="111"/>
+      <c r="S11" s="115"/>
     </row>
     <row r="12" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="95"/>
-      <c r="B12" s="100"/>
+      <c r="A12" s="124"/>
+      <c r="B12" s="122"/>
       <c r="C12" s="32" t="s">
         <v>57</v>
       </c>
@@ -2540,11 +2468,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B11," en el contexto de ",A5," asociado a la reserva con el identificador' ",J12,"'.")</f>
         <v>Atributo que contiene la información del nombre de un Turno en el contexto de Agendas asociado a la reserva con el identificador' NombreTurno'.</v>
       </c>
-      <c r="S12" s="111"/>
+      <c r="S12" s="115"/>
     </row>
     <row r="13" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="96"/>
-      <c r="B13" s="100"/>
+      <c r="A13" s="125"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="32" t="s">
         <v>62</v>
       </c>
@@ -2568,7 +2496,7 @@
       <c r="P13" s="32"/>
       <c r="Q13" s="32"/>
       <c r="R13" s="41"/>
-      <c r="S13" s="112"/>
+      <c r="S13" s="121"/>
     </row>
     <row r="14" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2621,75 +2549,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="101" t="str">
+      <c r="B1" s="99" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="102"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="100"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="90"/>
-      <c r="S2" s="91"/>
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="95"/>
+      <c r="S2" s="96"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104" t="s">
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="104"/>
-      <c r="Q3" s="104"/>
-      <c r="R3" s="105" t="s">
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="107" t="s">
+      <c r="S3" s="105" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2745,14 +2673,14 @@
       <c r="Q4" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="113"/>
-      <c r="S4" s="108"/>
+      <c r="R4" s="104"/>
+      <c r="S4" s="106"/>
     </row>
     <row r="5" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="109" t="s">
+      <c r="A5" s="131" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="139" t="s">
+      <c r="B5" s="132" t="s">
         <v>82</v>
       </c>
       <c r="C5" s="31" t="s">
@@ -2793,16 +2721,16 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B5,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador de un Inmueble  en el contexto de Residentes.</v>
       </c>
-      <c r="S5" s="110" t="str">
+      <c r="S5" s="114" t="str">
         <f>B8</f>
         <v>Residente</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="109"/>
-      <c r="B6" s="140"/>
+      <c r="A6" s="131"/>
+      <c r="B6" s="133"/>
       <c r="C6" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D6" s="31" t="s">
         <v>58</v>
@@ -2839,16 +2767,16 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B5," en el contexto de ",A5," asociado al residente con el identificador' ",J6,"'.")</f>
         <v>Atributo que contiene la información del nombre de un Inmueble en el contexto de Residentes asociado al residente con el identificador' tipoInmuebleInmueble'.</v>
       </c>
-      <c r="S6" s="111"/>
+      <c r="S6" s="115"/>
     </row>
     <row r="7" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="109"/>
-      <c r="B7" s="141"/>
+      <c r="A7" s="131"/>
+      <c r="B7" s="134"/>
       <c r="C7" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="31" t="s">
         <v>94</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>95</v>
       </c>
       <c r="E7" s="31">
         <v>1</v>
@@ -2882,11 +2810,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B6," en el contexto de ",A6," asociado al residente con el identificador' ",J7,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' numeroViviendaInmueble'.</v>
       </c>
-      <c r="S7" s="111"/>
+      <c r="S7" s="115"/>
     </row>
     <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="109"/>
-      <c r="B8" s="100" t="s">
+      <c r="A8" s="131"/>
+      <c r="B8" s="122" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="32" t="s">
@@ -2927,11 +2855,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B8,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador de un Residente  en el contexto de Residentes.</v>
       </c>
-      <c r="S8" s="111"/>
+      <c r="S8" s="115"/>
     </row>
     <row r="9" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="109"/>
-      <c r="B9" s="100"/>
+      <c r="A9" s="131"/>
+      <c r="B9" s="122"/>
       <c r="C9" s="32" t="s">
         <v>57</v>
       </c>
@@ -2970,7 +2898,7 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B8," en el contexto de ",A5," asociado a la reserva con el identificador' ",J9,"'.")</f>
         <v>Atributo que contiene la información del nombre de un Residente en el contexto de Residentes asociado a la reserva con el identificador' tipoInmuebleResidente'.</v>
       </c>
-      <c r="S9" s="112"/>
+      <c r="S9" s="121"/>
     </row>
     <row r="10" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -3015,29 +2943,29 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="65"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="70"/>
     </row>
     <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="68"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="73"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="76"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -3054,132 +2982,132 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="80" t="s">
         <v>79</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="76" t="s">
+      <c r="D5" s="81" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="74"/>
-      <c r="B6" s="75"/>
+      <c r="A6" s="79"/>
+      <c r="B6" s="80"/>
       <c r="C6" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="76"/>
+      <c r="D6" s="81"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="74"/>
-      <c r="B7" s="75"/>
+      <c r="A7" s="79"/>
+      <c r="B7" s="80"/>
       <c r="C7" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="76"/>
+      <c r="D7" s="81"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="74"/>
-      <c r="B8" s="75"/>
+      <c r="A8" s="79"/>
+      <c r="B8" s="80"/>
       <c r="C8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="76"/>
+      <c r="D8" s="81"/>
     </row>
     <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="74"/>
-      <c r="B9" s="75"/>
+      <c r="A9" s="79"/>
+      <c r="B9" s="80"/>
       <c r="C9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="76"/>
+      <c r="D9" s="81"/>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="78" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="77" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="72"/>
-      <c r="B11" s="73"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="78"/>
       <c r="C11" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="72"/>
+      <c r="D11" s="77"/>
     </row>
     <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="80" t="s">
+      <c r="A12" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="82" t="s">
         <v>83</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="80" t="s">
+      <c r="D12" s="85" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="81"/>
-      <c r="B13" s="78"/>
+      <c r="A13" s="86"/>
+      <c r="B13" s="83"/>
       <c r="C13" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="81"/>
+      <c r="D13" s="86"/>
     </row>
     <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82"/>
-      <c r="B14" s="79"/>
+      <c r="A14" s="87"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="82"/>
+      <c r="D14" s="87"/>
     </row>
     <row r="15" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="63" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="61" t="s">
+      <c r="D15" s="66" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="56"/>
-      <c r="B16" s="59"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="64"/>
       <c r="C16" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="62"/>
+      <c r="D16" s="67"/>
     </row>
     <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="57"/>
-      <c r="B17" s="60"/>
+      <c r="A17" s="62"/>
+      <c r="B17" s="65"/>
       <c r="C17" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="63"/>
+      <c r="D17" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3251,50 +3179,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="83" t="str">
+      <c r="B1" s="88" t="str">
         <f>Contextos!B5</f>
         <v xml:space="preserve"> Conjuntos residenciales</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
     </row>
     <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="85" t="str">
+      <c r="B2" s="90" t="str">
         <f>Contextos!D5</f>
         <v>Contexto cuya motivación es Gestionar la estructura física y los recursos disponibles en cada conjunto residencial. Aquí se manejan los datos sobre qué conjuntos existen, dónde están ubicados, qué recursos ofrecen según una Agenda con respectivos turnos para cada zona.</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="91"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="87" t="str">
+      <c r="B3" s="92" t="str">
         <f>Contextos!A5</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="88"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="93"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="91"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="96"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -3303,14 +3231,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="93" t="s">
+      <c r="E5" s="97"/>
+      <c r="F5" s="98" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3321,10 +3249,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="93"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="98"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -3333,14 +3261,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="92"/>
+      <c r="C7" s="97"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="93"/>
+      <c r="F7" s="98"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
@@ -3474,50 +3402,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="83" t="str">
+      <c r="B1" s="88" t="str">
         <f>Contextos!B10</f>
         <v>Residentes</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="85" t="str">
+      <c r="B2" s="90" t="str">
         <f>Contextos!D10</f>
         <v>Contexto cuya motivación es encargarce de manejar la información de los residentes, incluidas sus identificaciones, contacto, y la relación entre el residente y su residencia dentro del conjunto.</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="91"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="87" t="str">
+      <c r="B3" s="92" t="str">
         <f>Contextos!A10</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="88"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="93"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="91"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="96"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -3526,14 +3454,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="93" t="s">
+      <c r="E5" s="97"/>
+      <c r="F5" s="98" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3544,10 +3472,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="93"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="98"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -3556,14 +3484,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="92"/>
+      <c r="C7" s="97"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="93"/>
+      <c r="F7" s="98"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
@@ -3618,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59635CF3-0DE6-45E6-A198-1E7042F5E8F9}">
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
@@ -3647,75 +3575,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="101" t="str">
+      <c r="B1" s="99" t="str">
         <f>Residentes!D8</f>
         <v>Residente Inmueble-0001</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="102"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="100"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="90"/>
-      <c r="S2" s="91"/>
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="95"/>
+      <c r="S2" s="96"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104" t="s">
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="104"/>
-      <c r="Q3" s="104"/>
-      <c r="R3" s="105" t="s">
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="107" t="s">
+      <c r="S3" s="105" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3771,340 +3699,331 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="113"/>
-      <c r="S4" s="108"/>
-    </row>
-    <row r="5" spans="1:19" ht="28.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="134" t="s">
+      <c r="R4" s="104"/>
+      <c r="S4" s="106"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="129" t="s">
+      <c r="B5" s="140" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="51" t="s">
-        <v>55</v>
+      <c r="C5" s="139" t="s">
+        <v>93</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="E5" s="51">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F5" s="51">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G5" s="51"/>
       <c r="H5" s="51"/>
       <c r="I5" s="51"/>
       <c r="J5" s="51" t="str">
         <f>_xlfn.CONCAT(C5,$B$5)</f>
-        <v>identificadorInmueble</v>
+        <v>numeroViviendaInmueble</v>
       </c>
       <c r="K5" s="51" t="s">
         <v>59</v>
       </c>
       <c r="L5" s="51" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="M5" s="51">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="N5" s="51">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="52"/>
-      <c r="R5" s="118" t="s">
-        <v>96</v>
-      </c>
-      <c r="S5" s="119" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="28.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="135"/>
-      <c r="B6" s="130"/>
-      <c r="C6" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="51" t="s">
+      <c r="R5" s="143" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del numeroVivienda del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S5" s="141" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="108"/>
+      <c r="B6" s="110" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="31">
+        <v>32</v>
+      </c>
+      <c r="F6" s="31">
+        <v>32</v>
+      </c>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31" t="str">
+        <f>_xlfn.CONCAT(C6,$B$6)</f>
+        <v>identificadorTipoInmueble</v>
+      </c>
+      <c r="K6" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" s="31">
+        <v>32</v>
+      </c>
+      <c r="N6" s="31">
+        <v>32</v>
+      </c>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="53"/>
+      <c r="R6" s="144" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S6" s="141"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="108"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E7" s="31">
         <v>1</v>
       </c>
-      <c r="F6" s="51">
-        <v>20</v>
-      </c>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51" t="str">
-        <f t="shared" ref="J6:J7" si="0">_xlfn.CONCAT(C6,$B$5)</f>
-        <v>tipoInmuebleInmueble</v>
-      </c>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="120"/>
-      <c r="S6" s="121"/>
-    </row>
-    <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="135"/>
-      <c r="B7" s="131"/>
-      <c r="C7" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="51">
+      <c r="F7" s="31">
+        <v>50</v>
+      </c>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31" t="str">
+        <f>_xlfn.CONCAT(C7,$B$6)</f>
+        <v>nombreTipoInmueble</v>
+      </c>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="31">
         <v>1</v>
       </c>
-      <c r="F7" s="51">
+      <c r="N7" s="31">
         <v>50</v>
       </c>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51" t="str">
-        <f t="shared" si="0"/>
-        <v>numeroViviendaInmueble</v>
-      </c>
-      <c r="K7" s="51" t="s">
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="53"/>
+      <c r="R7" s="144" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C7," del objeto dominio ",B7,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S7" s="141"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="108"/>
+      <c r="B8" s="135" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="136" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="137" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="137">
+        <v>32</v>
+      </c>
+      <c r="F8" s="137">
+        <v>32</v>
+      </c>
+      <c r="G8" s="137"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="137" t="str">
+        <f>_xlfn.CONCAT(C8,$B$6)</f>
+        <v>identificadorTipoInmueble</v>
+      </c>
+      <c r="K8" s="137" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="M7" s="51">
+      <c r="L8" s="137" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="137">
+        <v>32</v>
+      </c>
+      <c r="N8" s="137">
+        <v>32</v>
+      </c>
+      <c r="O8" s="137"/>
+      <c r="P8" s="137"/>
+      <c r="Q8" s="138"/>
+      <c r="R8" s="145" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C8," del objeto dominio ",B8,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S8" s="141"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="108"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="137" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="137">
         <v>1</v>
       </c>
-      <c r="N7" s="51">
+      <c r="F9" s="137">
         <v>50</v>
       </c>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="122"/>
-      <c r="S7" s="121"/>
-    </row>
-    <row r="8" spans="1:19" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="135"/>
-      <c r="B8" s="132" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="50" t="s">
+      <c r="G9" s="137"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="137" t="str">
+        <f>_xlfn.CONCAT(C9,$B$6)</f>
+        <v>nombreTipoInmueble</v>
+      </c>
+      <c r="K9" s="137"/>
+      <c r="L9" s="137" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="137">
+        <v>1</v>
+      </c>
+      <c r="N9" s="137">
+        <v>50</v>
+      </c>
+      <c r="O9" s="137"/>
+      <c r="P9" s="137"/>
+      <c r="Q9" s="138"/>
+      <c r="R9" s="145" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C9," del objeto dominio ",B9,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S9" s="141"/>
+    </row>
+    <row r="10" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="108"/>
+      <c r="B10" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D10" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E10" s="32">
         <v>32</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F10" s="32">
         <v>32</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31" t="str">
-        <f>_xlfn.CONCAT(C8,$B$8)</f>
-        <v>identificadorZonaInmueble</v>
-      </c>
-      <c r="K8" s="31" t="s">
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32" t="str">
+        <f>_xlfn.CONCAT(C6,$B$10)</f>
+        <v>identificadorConjuntoResidencial</v>
+      </c>
+      <c r="K10" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="L10" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M10" s="32">
         <v>32</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N10" s="32">
         <v>32</v>
       </c>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="116"/>
-      <c r="R8" s="123" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B8,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador de un ZonaInmueble  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S8" s="121"/>
-    </row>
-    <row r="9" spans="1:19" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="135"/>
-      <c r="B9" s="132"/>
-      <c r="C9" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="31" t="s">
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="146" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S10" s="141"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="109"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="31">
-        <v>5</v>
-      </c>
-      <c r="F9" s="31">
-        <v>6</v>
-      </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31" t="str">
-        <f>_xlfn.CONCAT(C9,$B$8)</f>
-        <v>tipoZonaInmuebleZonaInmueble</v>
-      </c>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="116"/>
-      <c r="R9" s="124"/>
-      <c r="S9" s="121"/>
-    </row>
-    <row r="10" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="135"/>
-      <c r="B10" s="132"/>
-      <c r="C10" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="31">
+      <c r="E11" s="32">
         <v>1</v>
       </c>
-      <c r="F10" s="31">
-        <v>30</v>
-      </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="116"/>
-      <c r="R10" s="125"/>
-      <c r="S10" s="121"/>
-    </row>
-    <row r="11" spans="1:19" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="135"/>
-      <c r="B11" s="133" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="32">
-        <v>32</v>
-      </c>
       <c r="F11" s="32">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32" t="str">
-        <f>_xlfn.CONCAT(C8,$B$11)</f>
-        <v>identificadorConjuntoResidencial</v>
+        <f>_xlfn.CONCAT(C7,$B$10)</f>
+        <v>nombreConjuntoResidencial</v>
       </c>
       <c r="K11" s="32" t="s">
         <v>59</v>
       </c>
       <c r="L11" s="32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M11" s="32">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="N11" s="32">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="O11" s="32"/>
       <c r="P11" s="32"/>
-      <c r="Q11" s="117"/>
-      <c r="R11" s="126" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B11,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador de un ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S11" s="121"/>
-    </row>
-    <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="136"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="32">
-        <v>1</v>
-      </c>
-      <c r="F12" s="32">
-        <v>50</v>
-      </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32" t="str">
-        <f>_xlfn.CONCAT(C9,$B$11)</f>
-        <v>tipoZonaInmuebleConjuntoResidencial</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="M12" s="32">
-        <v>1</v>
-      </c>
-      <c r="N12" s="32">
-        <v>50</v>
-      </c>
-      <c r="O12" s="32"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="117"/>
-      <c r="R12" s="127"/>
-      <c r="S12" s="128"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="146" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C11," del objeto dominio ",B11,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S11" s="142"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="11">
+    <mergeCell ref="A5:A11"/>
+    <mergeCell ref="S5:S11"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B8:B9"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="S5:S12"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="R5:R7"/>
-    <mergeCell ref="R8:R10"/>
-    <mergeCell ref="R11:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4127,50 +4046,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="83" t="str">
+      <c r="B1" s="88" t="str">
         <f>Contextos!B12</f>
         <v>Agendas</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
     </row>
     <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="85" t="str">
+      <c r="B2" s="90" t="str">
         <f>Contextos!D12</f>
         <v>Contexto cuya motivación es la de gestionar la estructura de la agenda que va a tener una zona común durante un un tiempo estimado y sus diferentes turnos.</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="91"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="87" t="str">
+      <c r="B3" s="92" t="str">
         <f>Contextos!A12</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="88"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="93"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="91"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="96"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -4179,14 +4098,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="93" t="s">
+      <c r="E5" s="97"/>
+      <c r="F5" s="98" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4197,10 +4116,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="93"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="98"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -4209,14 +4128,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="92"/>
+      <c r="C7" s="97"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="93"/>
+      <c r="F7" s="98"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
@@ -4322,75 +4241,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="101" t="str">
+      <c r="B1" s="99" t="str">
         <f>Agendas!D8</f>
         <v>Agenda ZonaComun-0001</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="102"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="100"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="90"/>
-      <c r="S2" s="91"/>
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="95"/>
+      <c r="S2" s="96"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104" t="s">
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="104"/>
-      <c r="Q3" s="104"/>
-      <c r="R3" s="105" t="s">
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="107" t="s">
+      <c r="S3" s="105" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4446,14 +4365,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="106"/>
-      <c r="S4" s="108"/>
+      <c r="R4" s="120"/>
+      <c r="S4" s="106"/>
     </row>
     <row r="5" spans="1:19" ht="28.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="142" t="s">
+      <c r="B5" s="116" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -4490,17 +4409,17 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="51"/>
-      <c r="R5" s="137" t="str">
+      <c r="R5" s="112" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B7," en el contexto de ",A5," asociado al residente con el identificador' ",J9,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de Conjuntos Residenciales asociado al residente con el identificador' unidadTiempoUsoZonaComun'.</v>
       </c>
-      <c r="S5" s="110" t="s">
+      <c r="S5" s="114" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="135"/>
-      <c r="B6" s="143"/>
+      <c r="A6" s="108"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="51" t="s">
         <v>4</v>
       </c>
@@ -4535,17 +4454,17 @@
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="138"/>
-      <c r="S6" s="111"/>
+      <c r="R6" s="113"/>
+      <c r="S6" s="115"/>
     </row>
     <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="135"/>
-      <c r="B7" s="143"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E7" s="51"/>
       <c r="F7" s="51"/>
@@ -4563,20 +4482,20 @@
       <c r="O7" s="51"/>
       <c r="P7" s="51"/>
       <c r="Q7" s="51"/>
-      <c r="R7" s="137" t="str">
+      <c r="R7" s="112" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B9," en el contexto de ",A7," asociado al residente con el identificador' ",J11,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' nombreConjuntoResidencial'.</v>
       </c>
-      <c r="S7" s="111"/>
+      <c r="S7" s="115"/>
     </row>
     <row r="8" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="135"/>
-      <c r="B8" s="143"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="51" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E8" s="51"/>
       <c r="F8" s="51"/>
@@ -4594,14 +4513,14 @@
       <c r="O8" s="51"/>
       <c r="P8" s="51"/>
       <c r="Q8" s="51"/>
-      <c r="R8" s="147"/>
-      <c r="S8" s="111"/>
+      <c r="R8" s="119"/>
+      <c r="S8" s="115"/>
     </row>
     <row r="9" spans="1:19" ht="61.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="135"/>
-      <c r="B9" s="144"/>
+      <c r="A9" s="108"/>
+      <c r="B9" s="118"/>
       <c r="C9" s="51" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D9" s="51" t="s">
         <v>58</v>
@@ -4622,15 +4541,15 @@
       <c r="O9" s="51"/>
       <c r="P9" s="51"/>
       <c r="Q9" s="52"/>
-      <c r="R9" s="148" t="str">
+      <c r="R9" s="57" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B11," en el contexto de ",A9," asociado al residente con el identificador' ",J13,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' '.</v>
       </c>
-      <c r="S9" s="111"/>
+      <c r="S9" s="115"/>
     </row>
     <row r="10" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="135"/>
-      <c r="B10" s="133" t="s">
+      <c r="A10" s="108"/>
+      <c r="B10" s="111" t="s">
         <v>61</v>
       </c>
       <c r="C10" s="32" t="s">
@@ -4666,16 +4585,16 @@
       </c>
       <c r="O10" s="32"/>
       <c r="P10" s="32"/>
-      <c r="Q10" s="117"/>
-      <c r="R10" s="146" t="str">
+      <c r="Q10" s="54"/>
+      <c r="R10" s="56" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B10," en el contexto de ",A10," asociado a la reserva con el identificador' ",J10,"'.")</f>
         <v>Atributo que contiene la información del nombre de un ConjuntoResidencial en el contexto de  asociado a la reserva con el identificador' identificadorConjuntoResidencial'.</v>
       </c>
-      <c r="S10" s="111"/>
+      <c r="S10" s="115"/>
     </row>
     <row r="11" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="136"/>
-      <c r="B11" s="133"/>
+      <c r="A11" s="109"/>
+      <c r="B11" s="111"/>
       <c r="C11" s="32" t="s">
         <v>57</v>
       </c>
@@ -4710,26 +4629,26 @@
       <c r="O11" s="32"/>
       <c r="P11" s="32"/>
       <c r="Q11" s="32"/>
-      <c r="R11" s="145" t="str">
+      <c r="R11" s="55" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B11," en el contexto de ",A11," asociado a la reserva con el identificador' ",J11,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado a la reserva con el identificador' nombreConjuntoResidencial'.</v>
       </c>
-      <c r="S11" s="111"/>
+      <c r="S11" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
     <mergeCell ref="A5:A11"/>
     <mergeCell ref="R5:R6"/>
     <mergeCell ref="S5:S11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="R7:R8"/>
-    <mergeCell ref="B1:S1"/>
-    <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="J3:Q3"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="S3:S4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4753,50 +4672,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="83" t="str">
+      <c r="B1" s="88" t="str">
         <f>Contextos!B15</f>
         <v>Reservas</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="85" t="str">
+      <c r="B2" s="90" t="str">
         <f>Contextos!D15</f>
         <v>Contexto cuya intención enfocarse en la gestión del proceso de reservas de los recursos, incluyendo la disponibilidad de los recursos y las reservas que los residentes realizan.</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="91"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="87" t="str">
+      <c r="B3" s="92" t="str">
         <f>Contextos!A15</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="88"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="93"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="91"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="96"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -4805,14 +4724,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="93" t="s">
+      <c r="E5" s="97"/>
+      <c r="F5" s="98" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4823,10 +4742,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="93"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="98"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -4835,14 +4754,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="92"/>
+      <c r="C7" s="97"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="93"/>
+      <c r="F7" s="98"/>
     </row>
     <row r="8" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">

--- a/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDE411C-CB91-4771-87FC-995C82F464A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C280229-26CD-4B80-88ED-7C2DB4826BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="5" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="102">
   <si>
     <t>Problema/Dominio:</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>TipoInmueble</t>
+  </si>
+  <si>
+    <t>TipoZonaInmueble</t>
   </si>
 </sst>
 </file>
@@ -481,7 +484,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -997,12 +1000,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1175,6 +1191,30 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1298,6 +1338,21 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1322,21 +1377,12 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1361,9 +1407,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1406,41 +1449,32 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1879,10 +1913,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="59"/>
+      <c r="B1" s="67"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -2009,75 +2043,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99" t="str">
+      <c r="B1" s="112" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="100"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="113"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="96"/>
+      <c r="A2" s="102"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="104"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="114" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102" t="s">
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103" t="s">
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="105" t="s">
+      <c r="S3" s="118" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2134,13 +2168,13 @@
         <v>52</v>
       </c>
       <c r="R4" s="120"/>
-      <c r="S4" s="106"/>
+      <c r="S4" s="119"/>
     </row>
     <row r="5" spans="1:19" ht="28.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="123" t="s">
+      <c r="A5" s="132" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="126" t="s">
+      <c r="B5" s="135" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -2177,17 +2211,17 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="51"/>
-      <c r="R5" s="112" t="s">
+      <c r="R5" s="122" t="s">
         <v>91</v>
       </c>
-      <c r="S5" s="114" t="str">
+      <c r="S5" s="124" t="str">
         <f>B11</f>
         <v>Turno</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="124"/>
-      <c r="B6" s="127"/>
+      <c r="A6" s="133"/>
+      <c r="B6" s="136"/>
       <c r="C6" s="51" t="s">
         <v>4</v>
       </c>
@@ -2222,12 +2256,12 @@
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="113"/>
-      <c r="S6" s="115"/>
+      <c r="R6" s="123"/>
+      <c r="S6" s="125"/>
     </row>
     <row r="7" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="124"/>
-      <c r="B7" s="128" t="s">
+      <c r="A7" s="133"/>
+      <c r="B7" s="137" t="s">
         <v>64</v>
       </c>
       <c r="C7" s="50" t="s">
@@ -2268,11 +2302,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B7,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador de un Agenda  en el contexto de Agendas.</v>
       </c>
-      <c r="S7" s="115"/>
+      <c r="S7" s="125"/>
     </row>
     <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="124"/>
-      <c r="B8" s="129"/>
+      <c r="A8" s="133"/>
+      <c r="B8" s="138"/>
       <c r="C8" s="50" t="s">
         <v>4</v>
       </c>
@@ -2310,11 +2344,11 @@
       <c r="R8" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="S8" s="115"/>
+      <c r="S8" s="125"/>
     </row>
     <row r="9" spans="1:19" ht="58.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="124"/>
-      <c r="B9" s="129"/>
+      <c r="A9" s="133"/>
+      <c r="B9" s="138"/>
       <c r="C9" s="31" t="s">
         <v>90</v>
       </c>
@@ -2345,11 +2379,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B7," en el contexto de ",A5," asociado al residente con el identificador' ",J9,"'.")</f>
         <v>Atributo que contiene la información del nombre de un Agenda en el contexto de Agendas asociado al residente con el identificador' fechaHoraInicioAgenda'.</v>
       </c>
-      <c r="S9" s="115"/>
+      <c r="S9" s="125"/>
     </row>
     <row r="10" spans="1:19" ht="58.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="124"/>
-      <c r="B10" s="130"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="139"/>
       <c r="C10" s="31" t="s">
         <v>95</v>
       </c>
@@ -2380,11 +2414,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B8," en el contexto de ",A6," asociado al residente con el identificador' ",J10,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' fechaHoraFinAgenda'.</v>
       </c>
-      <c r="S10" s="115"/>
+      <c r="S10" s="125"/>
     </row>
     <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="124"/>
-      <c r="B11" s="122" t="s">
+      <c r="A11" s="133"/>
+      <c r="B11" s="131" t="s">
         <v>65</v>
       </c>
       <c r="C11" s="32" t="s">
@@ -2425,11 +2459,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B11,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador de un Turno  en el contexto de Agendas.</v>
       </c>
-      <c r="S11" s="115"/>
+      <c r="S11" s="125"/>
     </row>
     <row r="12" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="124"/>
-      <c r="B12" s="122"/>
+      <c r="A12" s="133"/>
+      <c r="B12" s="131"/>
       <c r="C12" s="32" t="s">
         <v>57</v>
       </c>
@@ -2468,11 +2502,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B11," en el contexto de ",A5," asociado a la reserva con el identificador' ",J12,"'.")</f>
         <v>Atributo que contiene la información del nombre de un Turno en el contexto de Agendas asociado a la reserva con el identificador' NombreTurno'.</v>
       </c>
-      <c r="S12" s="115"/>
+      <c r="S12" s="125"/>
     </row>
     <row r="13" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="125"/>
-      <c r="B13" s="122"/>
+      <c r="A13" s="134"/>
+      <c r="B13" s="131"/>
       <c r="C13" s="32" t="s">
         <v>62</v>
       </c>
@@ -2496,7 +2530,7 @@
       <c r="P13" s="32"/>
       <c r="Q13" s="32"/>
       <c r="R13" s="41"/>
-      <c r="S13" s="121"/>
+      <c r="S13" s="130"/>
     </row>
     <row r="14" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2549,75 +2583,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99" t="str">
+      <c r="B1" s="112" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="100"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="113"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="96"/>
+      <c r="A2" s="102"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="104"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="114" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102" t="s">
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103" t="s">
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="105" t="s">
+      <c r="S3" s="118" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2673,14 +2707,14 @@
       <c r="Q4" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="104"/>
-      <c r="S4" s="106"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="119"/>
     </row>
     <row r="5" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="141" t="s">
         <v>82</v>
       </c>
       <c r="C5" s="31" t="s">
@@ -2721,14 +2755,14 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B5,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador de un Inmueble  en el contexto de Residentes.</v>
       </c>
-      <c r="S5" s="114" t="str">
+      <c r="S5" s="124" t="str">
         <f>B8</f>
         <v>Residente</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="131"/>
-      <c r="B6" s="133"/>
+      <c r="A6" s="140"/>
+      <c r="B6" s="142"/>
       <c r="C6" s="31" t="s">
         <v>92</v>
       </c>
@@ -2767,11 +2801,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B5," en el contexto de ",A5," asociado al residente con el identificador' ",J6,"'.")</f>
         <v>Atributo que contiene la información del nombre de un Inmueble en el contexto de Residentes asociado al residente con el identificador' tipoInmuebleInmueble'.</v>
       </c>
-      <c r="S6" s="115"/>
+      <c r="S6" s="125"/>
     </row>
     <row r="7" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="131"/>
-      <c r="B7" s="134"/>
+      <c r="A7" s="140"/>
+      <c r="B7" s="143"/>
       <c r="C7" s="31" t="s">
         <v>93</v>
       </c>
@@ -2810,11 +2844,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B6," en el contexto de ",A6," asociado al residente con el identificador' ",J7,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' numeroViviendaInmueble'.</v>
       </c>
-      <c r="S7" s="115"/>
+      <c r="S7" s="125"/>
     </row>
     <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="131"/>
-      <c r="B8" s="122" t="s">
+      <c r="A8" s="140"/>
+      <c r="B8" s="131" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="32" t="s">
@@ -2855,11 +2889,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B8,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador de un Residente  en el contexto de Residentes.</v>
       </c>
-      <c r="S8" s="115"/>
+      <c r="S8" s="125"/>
     </row>
     <row r="9" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="131"/>
-      <c r="B9" s="122"/>
+      <c r="A9" s="140"/>
+      <c r="B9" s="131"/>
       <c r="C9" s="32" t="s">
         <v>57</v>
       </c>
@@ -2898,7 +2932,7 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B8," en el contexto de ",A5," asociado a la reserva con el identificador' ",J9,"'.")</f>
         <v>Atributo que contiene la información del nombre de un Residente en el contexto de Residentes asociado a la reserva con el identificador' tipoInmuebleResidente'.</v>
       </c>
-      <c r="S9" s="121"/>
+      <c r="S9" s="130"/>
     </row>
     <row r="10" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2943,29 +2977,29 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="70"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="73"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="76"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="84"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -2982,132 +3016,132 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="88" t="s">
         <v>79</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="89" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79"/>
-      <c r="B6" s="80"/>
+      <c r="A6" s="87"/>
+      <c r="B6" s="88"/>
       <c r="C6" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="81"/>
+      <c r="D6" s="89"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="79"/>
-      <c r="B7" s="80"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="81"/>
+      <c r="D7" s="89"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="79"/>
-      <c r="B8" s="80"/>
+      <c r="A8" s="87"/>
+      <c r="B8" s="88"/>
       <c r="C8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="81"/>
+      <c r="D8" s="89"/>
     </row>
     <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="79"/>
-      <c r="B9" s="80"/>
+      <c r="A9" s="87"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="81"/>
+      <c r="D9" s="89"/>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="86" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="77" t="s">
+      <c r="D10" s="85" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="77"/>
-      <c r="B11" s="78"/>
+      <c r="A11" s="85"/>
+      <c r="B11" s="86"/>
       <c r="C11" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="77"/>
+      <c r="D11" s="85"/>
     </row>
     <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="82" t="s">
+      <c r="B12" s="90" t="s">
         <v>83</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="85" t="s">
+      <c r="D12" s="93" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="83"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="91"/>
       <c r="C13" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="86"/>
+      <c r="D13" s="94"/>
     </row>
     <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="87"/>
-      <c r="B14" s="84"/>
+      <c r="A14" s="95"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="87"/>
+      <c r="D14" s="95"/>
     </row>
     <row r="15" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="71" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="66" t="s">
+      <c r="D15" s="74" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="61"/>
-      <c r="B16" s="64"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="72"/>
       <c r="C16" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="67"/>
+      <c r="D16" s="75"/>
     </row>
     <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="62"/>
-      <c r="B17" s="65"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="73"/>
       <c r="C17" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3179,50 +3213,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="88" t="str">
+      <c r="B1" s="96" t="str">
         <f>Contextos!B5</f>
         <v xml:space="preserve"> Conjuntos residenciales</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="89"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="90" t="str">
+      <c r="B2" s="98" t="str">
         <f>Contextos!D5</f>
         <v>Contexto cuya motivación es Gestionar la estructura física y los recursos disponibles en cada conjunto residencial. Aquí se manejan los datos sobre qué conjuntos existen, dónde están ubicados, qué recursos ofrecen según una Agenda con respectivos turnos para cada zona.</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="99"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="92" t="str">
+      <c r="B3" s="100" t="str">
         <f>Contextos!A5</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="93"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="101"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="96"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -3231,14 +3265,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="97" t="s">
+      <c r="D5" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="98" t="s">
+      <c r="E5" s="105"/>
+      <c r="F5" s="106" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3249,10 +3283,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="98"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="106"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -3261,14 +3295,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="97"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="98"/>
+      <c r="F7" s="106"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
@@ -3402,50 +3436,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="88" t="str">
+      <c r="B1" s="96" t="str">
         <f>Contextos!B10</f>
         <v>Residentes</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="89"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="90" t="str">
+      <c r="B2" s="98" t="str">
         <f>Contextos!D10</f>
         <v>Contexto cuya motivación es encargarce de manejar la información de los residentes, incluidas sus identificaciones, contacto, y la relación entre el residente y su residencia dentro del conjunto.</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="99"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="92" t="str">
+      <c r="B3" s="100" t="str">
         <f>Contextos!A10</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="93"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="101"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="96"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -3454,14 +3488,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="97" t="s">
+      <c r="D5" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="98" t="s">
+      <c r="E5" s="105"/>
+      <c r="F5" s="106" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3472,10 +3506,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="98"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="106"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -3484,14 +3518,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="97"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="98"/>
+      <c r="F7" s="106"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
@@ -3546,7 +3580,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59635CF3-0DE6-45E6-A198-1E7042F5E8F9}">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
@@ -3575,75 +3609,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99" t="str">
+      <c r="B1" s="112" t="str">
         <f>Residentes!D8</f>
         <v>Residente Inmueble-0001</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="100"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="113"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="96"/>
+      <c r="A2" s="102"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="104"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="114" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102" t="s">
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103" t="s">
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="105" t="s">
+      <c r="S3" s="118" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3699,17 +3733,17 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="104"/>
-      <c r="S4" s="106"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="119"/>
     </row>
     <row r="5" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="140" t="s">
+      <c r="B5" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="139" t="s">
+      <c r="C5" s="61" t="s">
         <v>93</v>
       </c>
       <c r="D5" s="51" t="s">
@@ -3743,287 +3777,435 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="52"/>
-      <c r="R5" s="143" t="str">
+      <c r="R5" s="62" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del numeroVivienda del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S5" s="141" t="s">
+      <c r="S5" s="109" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="108"/>
-      <c r="B6" s="110" t="s">
+    <row r="6" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="107"/>
+      <c r="B6" s="146"/>
+      <c r="C6" s="144" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="109"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="107"/>
+      <c r="B7" s="147" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D7" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E7" s="31">
         <v>32</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F7" s="31">
         <v>32</v>
-      </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31" t="str">
-        <f>_xlfn.CONCAT(C6,$B$6)</f>
-        <v>identificadorTipoInmueble</v>
-      </c>
-      <c r="K6" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6" s="31">
-        <v>32</v>
-      </c>
-      <c r="N6" s="31">
-        <v>32</v>
-      </c>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="53"/>
-      <c r="R6" s="144" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S6" s="141"/>
-    </row>
-    <row r="7" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="108"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="31">
-        <v>1</v>
-      </c>
-      <c r="F7" s="31">
-        <v>50</v>
       </c>
       <c r="G7" s="31"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="J7" s="31" t="str">
-        <f>_xlfn.CONCAT(C7,$B$6)</f>
-        <v>nombreTipoInmueble</v>
-      </c>
-      <c r="K7" s="31"/>
+        <f>_xlfn.CONCAT(C7,$B$7)</f>
+        <v>identificadorTipoInmueble</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>59</v>
+      </c>
       <c r="L7" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M7" s="31">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N7" s="31">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O7" s="31"/>
       <c r="P7" s="31"/>
       <c r="Q7" s="53"/>
-      <c r="R7" s="144" t="str">
+      <c r="R7" s="63" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C7," del objeto dominio ",B7,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S7" s="109"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="107"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="31">
+        <v>1</v>
+      </c>
+      <c r="F8" s="31">
+        <v>50</v>
+      </c>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31" t="str">
+        <f>_xlfn.CONCAT(C8,$B$7)</f>
+        <v>nombreTipoInmueble</v>
+      </c>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="31">
+        <v>1</v>
+      </c>
+      <c r="N8" s="31">
+        <v>50</v>
+      </c>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="53"/>
+      <c r="R8" s="63" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C8," del objeto dominio ",B8,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S7" s="141"/>
-    </row>
-    <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="108"/>
-      <c r="B8" s="135" t="s">
+      <c r="S8" s="109"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="107"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="136" t="s">
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="53"/>
+      <c r="R9" s="63"/>
+      <c r="S9" s="109"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="107"/>
+      <c r="B10" s="150" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="137" t="s">
+      <c r="D10" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="137">
+      <c r="E10" s="59">
         <v>32</v>
       </c>
-      <c r="F8" s="137">
+      <c r="F10" s="59">
         <v>32</v>
       </c>
-      <c r="G8" s="137"/>
-      <c r="H8" s="137"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="137" t="str">
-        <f>_xlfn.CONCAT(C8,$B$6)</f>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59" t="str">
+        <f>_xlfn.CONCAT(C10,$B$7)</f>
         <v>identificadorTipoInmueble</v>
       </c>
-      <c r="K8" s="137" t="s">
+      <c r="K10" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="137" t="s">
+      <c r="L10" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="137">
+      <c r="M10" s="59">
         <v>32</v>
       </c>
-      <c r="N8" s="137">
+      <c r="N10" s="59">
         <v>32</v>
       </c>
-      <c r="O8" s="137"/>
-      <c r="P8" s="137"/>
-      <c r="Q8" s="138"/>
-      <c r="R8" s="145" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C8," del objeto dominio ",B8,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S8" s="141"/>
-    </row>
-    <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="108"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136" t="s">
+      <c r="O10" s="59"/>
+      <c r="P10" s="59"/>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="64" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",A3,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Caracterización Origen.</v>
+      </c>
+      <c r="S10" s="109"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="107"/>
+      <c r="B11" s="152"/>
+      <c r="C11" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59" t="str">
+        <f>_xlfn.CONCAT(C11,$B$7)</f>
+        <v>TipoZonaInmuebleTipoInmueble</v>
+      </c>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="59"/>
+      <c r="P11" s="59"/>
+      <c r="Q11" s="60"/>
+      <c r="R11" s="64" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C11," del objeto dominio ",B11,"  en el contexto de ",A3,".")</f>
+        <v>Atributo que contiene la informacion del TipoZonaInmueble del objeto dominio   en el contexto de Caracterización Origen.</v>
+      </c>
+      <c r="S11" s="109"/>
+    </row>
+    <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="107"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59" t="str">
+        <f>_xlfn.CONCAT(C12,$B$7)</f>
+        <v>ConjuntoResidencialTipoInmueble</v>
+      </c>
+      <c r="K12" s="59"/>
+      <c r="L12" s="59"/>
+      <c r="M12" s="59"/>
+      <c r="N12" s="59"/>
+      <c r="O12" s="59"/>
+      <c r="P12" s="59"/>
+      <c r="Q12" s="60"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="109"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="107"/>
+      <c r="B13" s="150" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="59">
+        <v>32</v>
+      </c>
+      <c r="F13" s="59">
+        <v>32</v>
+      </c>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59" t="str">
+        <f>_xlfn.CONCAT(C13,$B$7)</f>
+        <v>identificadorTipoInmueble</v>
+      </c>
+      <c r="K13" s="59" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="59">
+        <v>32</v>
+      </c>
+      <c r="N13" s="59">
+        <v>32</v>
+      </c>
+      <c r="O13" s="59"/>
+      <c r="P13" s="59"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="64" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C13," del objeto dominio ",B13,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio TipoZonaInmueble  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S13" s="109"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="107"/>
+      <c r="B14" s="152"/>
+      <c r="C14" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="137" t="s">
+      <c r="D14" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="137">
+      <c r="E14" s="59">
         <v>1</v>
       </c>
-      <c r="F9" s="137">
+      <c r="F14" s="59">
         <v>50</v>
       </c>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137" t="str">
-        <f>_xlfn.CONCAT(C9,$B$6)</f>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59" t="str">
+        <f>_xlfn.CONCAT(C14,$B$7)</f>
         <v>nombreTipoInmueble</v>
       </c>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137" t="s">
+      <c r="K14" s="59"/>
+      <c r="L14" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="137">
+      <c r="M14" s="59">
         <v>1</v>
       </c>
-      <c r="N9" s="137">
+      <c r="N14" s="59">
         <v>50</v>
       </c>
-      <c r="O9" s="137"/>
-      <c r="P9" s="137"/>
-      <c r="Q9" s="138"/>
-      <c r="R9" s="145" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C9," del objeto dominio ",B9,"  en el contexto de ",A5,".")</f>
+      <c r="O14" s="59"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="64" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C14," del objeto dominio ",B14,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S9" s="141"/>
-    </row>
-    <row r="10" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="108"/>
-      <c r="B10" s="111" t="s">
+      <c r="S14" s="109"/>
+    </row>
+    <row r="15" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="107"/>
+      <c r="B15" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C15" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D15" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E15" s="32">
         <v>32</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F15" s="32">
         <v>32</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32" t="str">
-        <f>_xlfn.CONCAT(C6,$B$10)</f>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32" t="str">
+        <f>_xlfn.CONCAT(C7,$B$15)</f>
         <v>identificadorConjuntoResidencial</v>
       </c>
-      <c r="K10" s="32" t="s">
+      <c r="K15" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="32" t="s">
+      <c r="L15" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="M10" s="32">
+      <c r="M15" s="32">
         <v>32</v>
       </c>
-      <c r="N10" s="32">
+      <c r="N15" s="32">
         <v>32</v>
       </c>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="146" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",A5,".")</f>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="65" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C15," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S10" s="141"/>
-    </row>
-    <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="109"/>
-      <c r="B11" s="111"/>
-      <c r="C11" s="32" t="s">
+      <c r="S15" s="109"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="108"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D16" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E16" s="32">
         <v>1</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F16" s="32">
         <v>50</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32" t="str">
-        <f>_xlfn.CONCAT(C7,$B$10)</f>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32" t="str">
+        <f>_xlfn.CONCAT(C8,$B$15)</f>
         <v>nombreConjuntoResidencial</v>
       </c>
-      <c r="K11" s="32" t="s">
+      <c r="K16" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="32" t="s">
+      <c r="L16" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="32">
+      <c r="M16" s="32">
         <v>1</v>
       </c>
-      <c r="N11" s="32">
+      <c r="N16" s="32">
         <v>50</v>
       </c>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="146" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C11," del objeto dominio ",B11,"  en el contexto de ",A5,".")</f>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="65" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S11" s="142"/>
+      <c r="S16" s="110"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A5:A11"/>
-    <mergeCell ref="S5:S11"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B8:B9"/>
+  <mergeCells count="13">
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
+    <mergeCell ref="A5:A16"/>
+    <mergeCell ref="S5:S16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B10:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4046,50 +4228,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="88" t="str">
+      <c r="B1" s="96" t="str">
         <f>Contextos!B12</f>
         <v>Agendas</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="89"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="90" t="str">
+      <c r="B2" s="98" t="str">
         <f>Contextos!D12</f>
         <v>Contexto cuya motivación es la de gestionar la estructura de la agenda que va a tener una zona común durante un un tiempo estimado y sus diferentes turnos.</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="99"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="92" t="str">
+      <c r="B3" s="100" t="str">
         <f>Contextos!A12</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="93"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="101"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="96"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -4098,14 +4280,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="97" t="s">
+      <c r="D5" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="98" t="s">
+      <c r="E5" s="105"/>
+      <c r="F5" s="106" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4116,10 +4298,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="98"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="106"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -4128,14 +4310,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="97"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="98"/>
+      <c r="F7" s="106"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
@@ -4241,75 +4423,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99" t="str">
+      <c r="B1" s="112" t="str">
         <f>Agendas!D8</f>
         <v>Agenda ZonaComun-0001</v>
       </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="100"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="113"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="96"/>
+      <c r="A2" s="102"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="104"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="114" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102" t="s">
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103" t="s">
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="105" t="s">
+      <c r="S3" s="118" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4366,13 +4548,13 @@
         <v>52</v>
       </c>
       <c r="R4" s="120"/>
-      <c r="S4" s="106"/>
+      <c r="S4" s="119"/>
     </row>
     <row r="5" spans="1:19" ht="28.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="126" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -4409,17 +4591,17 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="51"/>
-      <c r="R5" s="112" t="str">
+      <c r="R5" s="122" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B7," en el contexto de ",A5," asociado al residente con el identificador' ",J9,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de Conjuntos Residenciales asociado al residente con el identificador' unidadTiempoUsoZonaComun'.</v>
       </c>
-      <c r="S5" s="114" t="s">
+      <c r="S5" s="124" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="108"/>
-      <c r="B6" s="117"/>
+      <c r="A6" s="107"/>
+      <c r="B6" s="127"/>
       <c r="C6" s="51" t="s">
         <v>4</v>
       </c>
@@ -4454,12 +4636,12 @@
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="113"/>
-      <c r="S6" s="115"/>
+      <c r="R6" s="123"/>
+      <c r="S6" s="125"/>
     </row>
     <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="108"/>
-      <c r="B7" s="117"/>
+      <c r="A7" s="107"/>
+      <c r="B7" s="127"/>
       <c r="C7" s="51" t="s">
         <v>97</v>
       </c>
@@ -4482,15 +4664,15 @@
       <c r="O7" s="51"/>
       <c r="P7" s="51"/>
       <c r="Q7" s="51"/>
-      <c r="R7" s="112" t="str">
+      <c r="R7" s="122" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B9," en el contexto de ",A7," asociado al residente con el identificador' ",J11,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' nombreConjuntoResidencial'.</v>
       </c>
-      <c r="S7" s="115"/>
+      <c r="S7" s="125"/>
     </row>
     <row r="8" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="108"/>
-      <c r="B8" s="117"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="127"/>
       <c r="C8" s="51" t="s">
         <v>98</v>
       </c>
@@ -4513,12 +4695,12 @@
       <c r="O8" s="51"/>
       <c r="P8" s="51"/>
       <c r="Q8" s="51"/>
-      <c r="R8" s="119"/>
-      <c r="S8" s="115"/>
+      <c r="R8" s="129"/>
+      <c r="S8" s="125"/>
     </row>
     <row r="9" spans="1:19" ht="61.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="108"/>
-      <c r="B9" s="118"/>
+      <c r="A9" s="107"/>
+      <c r="B9" s="128"/>
       <c r="C9" s="51" t="s">
         <v>99</v>
       </c>
@@ -4545,10 +4727,10 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B11," en el contexto de ",A9," asociado al residente con el identificador' ",J13,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' '.</v>
       </c>
-      <c r="S9" s="115"/>
+      <c r="S9" s="125"/>
     </row>
     <row r="10" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="108"/>
+      <c r="A10" s="107"/>
       <c r="B10" s="111" t="s">
         <v>61</v>
       </c>
@@ -4590,10 +4772,10 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B10," en el contexto de ",A10," asociado a la reserva con el identificador' ",J10,"'.")</f>
         <v>Atributo que contiene la información del nombre de un ConjuntoResidencial en el contexto de  asociado a la reserva con el identificador' identificadorConjuntoResidencial'.</v>
       </c>
-      <c r="S10" s="115"/>
+      <c r="S10" s="125"/>
     </row>
     <row r="11" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="109"/>
+      <c r="A11" s="108"/>
       <c r="B11" s="111"/>
       <c r="C11" s="32" t="s">
         <v>57</v>
@@ -4633,22 +4815,22 @@
         <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B11," en el contexto de ",A11," asociado a la reserva con el identificador' ",J11,"'.")</f>
         <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado a la reserva con el identificador' nombreConjuntoResidencial'.</v>
       </c>
-      <c r="S11" s="115"/>
+      <c r="S11" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A5:A11"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="R7:R8"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
-    <mergeCell ref="A5:A11"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="R7:R8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4672,50 +4854,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="88" t="str">
+      <c r="B1" s="96" t="str">
         <f>Contextos!B15</f>
         <v>Reservas</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="89"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="90" t="str">
+      <c r="B2" s="98" t="str">
         <f>Contextos!D15</f>
         <v>Contexto cuya intención enfocarse en la gestión del proceso de reservas de los recursos, incluyendo la disponibilidad de los recursos y las reservas que los residentes realizan.</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="99"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="92" t="str">
+      <c r="B3" s="100" t="str">
         <f>Contextos!A15</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="93"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="101"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="96"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -4724,14 +4906,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="97" t="s">
+      <c r="D5" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="98" t="s">
+      <c r="E5" s="105"/>
+      <c r="F5" s="106" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4742,10 +4924,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="98"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="106"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -4754,14 +4936,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="97"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="98"/>
+      <c r="F7" s="106"/>
     </row>
     <row r="8" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">

--- a/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C280229-26CD-4B80-88ED-7C2DB4826BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E636CC19-D5C4-402C-B0F8-7C9B6589C008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="5" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="7" activeTab="9" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="3" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="Contextos" sheetId="2" r:id="rId3"/>
     <sheet name="Conjuntos Residenciales" sheetId="4" r:id="rId4"/>
     <sheet name="Residentes" sheetId="5" r:id="rId5"/>
-    <sheet name="Residente-Inmueble-0001" sheetId="12" r:id="rId6"/>
+    <sheet name="Residente ConjutosResidenciales" sheetId="12" r:id="rId6"/>
     <sheet name="Agendas" sheetId="11" r:id="rId7"/>
-    <sheet name="AgendaZonaComun-0001" sheetId="13" r:id="rId8"/>
+    <sheet name="Agenda ConjuntosResidenciales-0" sheetId="13" r:id="rId8"/>
     <sheet name="Reservas" sheetId="6" r:id="rId9"/>
     <sheet name="Reserva-0001" sheetId="8" r:id="rId10"/>
     <sheet name="Reserva-0002" sheetId="10" r:id="rId11"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="135">
   <si>
     <t>Problema/Dominio:</t>
   </si>
@@ -321,9 +321,6 @@
     <t>fechaHoraInicio</t>
   </si>
   <si>
-    <t>Atributo que contiene la información del identificador de una zona común en el contexto de Conjuntos Residenciales</t>
-  </si>
-  <si>
     <t>tipoInmueble</t>
   </si>
   <si>
@@ -336,9 +333,6 @@
     <t>fechaHoraFin</t>
   </si>
   <si>
-    <t>Atributo que contiene el nombre de una agenda en el contexto de agendas</t>
-  </si>
-  <si>
     <t>capacidadPersonas</t>
   </si>
   <si>
@@ -352,13 +346,118 @@
   </si>
   <si>
     <t>TipoZonaInmueble</t>
+  </si>
+  <si>
+    <t>ConjutosResidenciales</t>
+  </si>
+  <si>
+    <t>zonaInmueble</t>
+  </si>
+  <si>
+    <t>tipoZonaInmueble</t>
+  </si>
+  <si>
+    <t>ConjuntosResidenciales</t>
+  </si>
+  <si>
+    <t>UnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>abreviatura</t>
+  </si>
+  <si>
+    <t>enBase</t>
+  </si>
+  <si>
+    <t>Logico</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>zonaComun</t>
+  </si>
+  <si>
+    <t>agenda</t>
+  </si>
+  <si>
+    <t>TipoInmueble(Nombre)</t>
+  </si>
+  <si>
+    <t>TipoZonaInmueble(Identificador)</t>
+  </si>
+  <si>
+    <t>TipoZonaInmueble(Nombre)</t>
+  </si>
+  <si>
+    <t>ZonaInmueble(NumeroZonaInmueble)</t>
+  </si>
+  <si>
+    <t>inmueble</t>
+  </si>
+  <si>
+    <t>entero</t>
+  </si>
+  <si>
+    <t>numeroDocumento</t>
+  </si>
+  <si>
+    <t>identificadorConjuntoResidencial</t>
+  </si>
+  <si>
+    <t>nombreConjuntoResidencial</t>
+  </si>
+  <si>
+    <t>identificadorUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>nombreUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>abreviaturaUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>enBaseUnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>IdentificadorZonaComun</t>
+  </si>
+  <si>
+    <t>nombreZonaComun</t>
+  </si>
+  <si>
+    <t>capacidadPersonasZonaComun</t>
+  </si>
+  <si>
+    <t>decripcionZonaComun</t>
+  </si>
+  <si>
+    <t>tiempoUsoZonaComun</t>
+  </si>
+  <si>
+    <t>numeroTurno</t>
+  </si>
+  <si>
+    <t>horaInicio</t>
+  </si>
+  <si>
+    <t>Fecha-Tiempo</t>
+  </si>
+  <si>
+    <t>horaFin</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>Lógico</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,6 +498,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -484,7 +591,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -702,21 +809,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color indexed="64"/>
       </left>
@@ -819,17 +911,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom style="thick">
         <color indexed="64"/>
@@ -866,57 +947,11 @@
       <left style="thick">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
       <right style="thick">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1013,12 +1048,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1110,13 +1169,13 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1137,10 +1196,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1167,54 +1226,48 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1224,30 +1277,30 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1290,21 +1343,21 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1338,143 +1391,224 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1905,20 +2039,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0E5666-F6A5-49FF-B12A-1FE829F0A68B}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.44140625" style="2"/>
+    <col min="2" max="2" width="79.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="67"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B1" s="65"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
@@ -1926,7 +2060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
@@ -1934,7 +2068,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
@@ -1942,13 +2076,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>16</v>
       </c>
@@ -1956,7 +2090,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>17</v>
       </c>
@@ -1964,7 +2098,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>18</v>
       </c>
@@ -1972,7 +2106,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
         <v>19</v>
       </c>
@@ -1980,7 +2114,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>20</v>
       </c>
@@ -1988,7 +2122,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
         <v>21</v>
       </c>
@@ -1996,7 +2130,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>22</v>
       </c>
@@ -2014,108 +2148,108 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3888799-E6A1-4FAB-A09B-AF9FE652AF52}">
-  <dimension ref="A1:S14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="31" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="42.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="58" style="26" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.44140625" style="13"/>
+    <col min="19" max="19" width="17.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="112" t="str">
+      <c r="B1" s="118" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="113"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="102"/>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="104"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="114" t="s">
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="119"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="102"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115" t="s">
+      <c r="B3" s="121"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="116" t="s">
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="118" t="s">
+      <c r="S3" s="124" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>28</v>
       </c>
@@ -2167,18 +2301,18 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="120"/>
-      <c r="S4" s="119"/>
-    </row>
-    <row r="5" spans="1:19" ht="28.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="132" t="s">
+      <c r="R4" s="126"/>
+      <c r="S4" s="125"/>
+    </row>
+    <row r="5" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="135" t="s">
+      <c r="B5" s="137" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="D5" s="51" t="s">
         <v>56</v>
@@ -2193,8 +2327,8 @@
       <c r="H5" s="51"/>
       <c r="I5" s="51"/>
       <c r="J5" s="51" t="str">
-        <f>_xlfn.CONCAT(C5,$B$5)</f>
-        <v>identificadorZonaComun</v>
+        <f>_xlfn.CONCAT(C5,"(",$B$5,")")</f>
+        <v>identificadorConjuntoResidencial(ZonaComun)</v>
       </c>
       <c r="K5" s="51" t="s">
         <v>59</v>
@@ -2211,25 +2345,25 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="51"/>
-      <c r="R5" s="122" t="s">
-        <v>91</v>
-      </c>
-      <c r="S5" s="124" t="str">
-        <f>B11</f>
-        <v>Turno</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="133"/>
-      <c r="B6" s="136"/>
+      <c r="R5" s="154" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificadorConjuntoResidencial del objeto dominio ZonaComun  en el contexto de Agendas.</v>
+      </c>
+      <c r="S5" s="129" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="135"/>
+      <c r="B6" s="177"/>
       <c r="C6" s="51" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="D6" s="51" t="s">
         <v>58</v>
       </c>
       <c r="E6" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="51">
         <v>50</v>
@@ -2238,8 +2372,8 @@
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
       <c r="J6" s="51" t="str">
-        <f>_xlfn.CONCAT(C6,$B$5)</f>
-        <v>NombreZonaComun</v>
+        <f t="shared" ref="J6:J15" si="0">_xlfn.CONCAT(C6,"(",$B$5,")")</f>
+        <v>nombreConjuntoResidencial(ZonaComun)</v>
       </c>
       <c r="K6" s="51" t="s">
         <v>59</v>
@@ -2248,414 +2382,937 @@
         <v>58</v>
       </c>
       <c r="M6" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N6" s="51">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="123"/>
-      <c r="S6" s="125"/>
-    </row>
-    <row r="7" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="133"/>
-      <c r="B7" s="137" t="s">
+      <c r="R6" s="154" t="str">
+        <f t="shared" ref="R6:R15" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del nombreConjuntoResidencial del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S6" s="129"/>
+    </row>
+    <row r="7" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="135"/>
+      <c r="B7" s="177"/>
+      <c r="C7" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="51">
+        <v>32</v>
+      </c>
+      <c r="F7" s="51">
+        <v>32</v>
+      </c>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>identificadorUnidadTiempoUso(ZonaComun)</v>
+      </c>
+      <c r="K7" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="51">
+        <v>32</v>
+      </c>
+      <c r="N7" s="51">
+        <v>32</v>
+      </c>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
+      <c r="R7" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del identificadorUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S7" s="129"/>
+    </row>
+    <row r="8" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="135"/>
+      <c r="B8" s="177"/>
+      <c r="C8" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="51">
+        <v>3</v>
+      </c>
+      <c r="F8" s="51">
+        <v>50</v>
+      </c>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>nombreUnidadTiempoUso(ZonaComun)</v>
+      </c>
+      <c r="K8" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="51">
+        <v>3</v>
+      </c>
+      <c r="N8" s="51">
+        <v>50</v>
+      </c>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="51"/>
+      <c r="R8" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del nombreUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S8" s="129"/>
+    </row>
+    <row r="9" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="135"/>
+      <c r="B9" s="177"/>
+      <c r="C9" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="51">
+        <v>1</v>
+      </c>
+      <c r="F9" s="51">
+        <v>6</v>
+      </c>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>abreviaturaUnidadTiempoUso(ZonaComun)</v>
+      </c>
+      <c r="K9" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="51">
+        <v>1</v>
+      </c>
+      <c r="N9" s="51">
+        <v>6</v>
+      </c>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del abreviaturaUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S9" s="129"/>
+    </row>
+    <row r="10" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="135"/>
+      <c r="B10" s="177"/>
+      <c r="C10" s="166" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="51">
+        <v>1</v>
+      </c>
+      <c r="F10" s="51">
+        <v>10</v>
+      </c>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>enBaseUnidadTiempoUso(ZonaComun)</v>
+      </c>
+      <c r="K10" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="M10" s="51">
+        <v>1</v>
+      </c>
+      <c r="N10" s="51">
+        <v>10</v>
+      </c>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del enBaseUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S10" s="129"/>
+    </row>
+    <row r="11" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="135"/>
+      <c r="B11" s="177"/>
+      <c r="C11" s="166" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="51">
+        <v>32</v>
+      </c>
+      <c r="F11" s="51">
+        <v>32</v>
+      </c>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>IdentificadorZonaComun(ZonaComun)</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="51">
+        <v>32</v>
+      </c>
+      <c r="N11" s="51">
+        <v>32</v>
+      </c>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del IdentificadorZonaComun del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S11" s="129"/>
+    </row>
+    <row r="12" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="135"/>
+      <c r="B12" s="177"/>
+      <c r="C12" s="166" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="51">
+        <v>3</v>
+      </c>
+      <c r="F12" s="51">
+        <v>50</v>
+      </c>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>nombreZonaComun(ZonaComun)</v>
+      </c>
+      <c r="K12" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="51">
+        <v>3</v>
+      </c>
+      <c r="N12" s="51">
+        <v>50</v>
+      </c>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del nombreZonaComun del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S12" s="129"/>
+    </row>
+    <row r="13" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="135"/>
+      <c r="B13" s="177"/>
+      <c r="C13" s="166" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="51">
+        <v>1</v>
+      </c>
+      <c r="F13" s="51">
+        <v>4</v>
+      </c>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>capacidadPersonasZonaComun(ZonaComun)</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="M13" s="51">
+        <v>1</v>
+      </c>
+      <c r="N13" s="51">
+        <v>4</v>
+      </c>
+      <c r="O13" s="51"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del capacidadPersonasZonaComun del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S13" s="129"/>
+    </row>
+    <row r="14" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="135"/>
+      <c r="B14" s="177"/>
+      <c r="C14" s="166" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="51">
+        <v>0</v>
+      </c>
+      <c r="F14" s="51">
+        <v>255</v>
+      </c>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>decripcionZonaComun(ZonaComun)</v>
+      </c>
+      <c r="K14" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="51">
+        <v>0</v>
+      </c>
+      <c r="N14" s="51">
+        <v>255</v>
+      </c>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del decripcionZonaComun del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S14" s="129"/>
+    </row>
+    <row r="15" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="135"/>
+      <c r="B15" s="165"/>
+      <c r="C15" s="166" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="51">
+        <v>1</v>
+      </c>
+      <c r="F15" s="51">
+        <v>5</v>
+      </c>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51">
+        <v>0</v>
+      </c>
+      <c r="I15" s="51">
+        <v>3600</v>
+      </c>
+      <c r="J15" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>tiempoUsoZonaComun(ZonaComun)</v>
+      </c>
+      <c r="K15" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="M15" s="51">
+        <v>1</v>
+      </c>
+      <c r="N15" s="51">
+        <v>5</v>
+      </c>
+      <c r="O15" s="51"/>
+      <c r="P15" s="51">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="51">
+        <v>3600</v>
+      </c>
+      <c r="R15" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del tiempoUsoZonaComun del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S15" s="129"/>
+    </row>
+    <row r="16" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="135"/>
+      <c r="B16" s="176" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C16" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D16" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E16" s="31">
         <v>32</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F16" s="31">
         <v>32</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31" t="str">
-        <f>_xlfn.CONCAT(C7,$B$7)</f>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31" t="str">
+        <f>_xlfn.CONCAT(C16,$B$16)</f>
         <v>identificadorAgenda</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="K16" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="31" t="s">
+      <c r="L16" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="M7" s="31">
+      <c r="M16" s="31">
         <v>32</v>
       </c>
-      <c r="N7" s="31">
+      <c r="N16" s="31">
         <v>32</v>
       </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="40" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B7,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador de un Agenda  en el contexto de Agendas.</v>
-      </c>
-      <c r="S7" s="125"/>
-    </row>
-    <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="133"/>
-      <c r="B8" s="138"/>
-      <c r="C8" s="50" t="s">
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="40" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio Agenda  en el contexto de Agendas.</v>
+      </c>
+      <c r="S16" s="129"/>
+    </row>
+    <row r="17" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="135"/>
+      <c r="B17" s="176"/>
+      <c r="C17" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D17" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E17" s="31">
         <v>1</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F17" s="31">
         <v>50</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31" t="str">
-        <f t="shared" ref="J8:J10" si="0">_xlfn.CONCAT(C8,$B$7)</f>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31" t="str">
+        <f t="shared" ref="J17:J20" si="2">_xlfn.CONCAT(C17,$B$16)</f>
         <v>NombreAgenda</v>
       </c>
-      <c r="K8" s="31" t="s">
+      <c r="K17" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="L17" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M17" s="31">
         <v>1</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N17" s="31">
         <v>50</v>
       </c>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="S8" s="125"/>
-    </row>
-    <row r="9" spans="1:19" ht="58.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="133"/>
-      <c r="B9" s="138"/>
-      <c r="C9" s="31" t="s">
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="40" t="str">
+        <f t="shared" ref="R17:R20" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S17" s="129"/>
+    </row>
+    <row r="18" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="135"/>
+      <c r="B18" s="176"/>
+      <c r="C18" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D18" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31" t="str">
-        <f t="shared" si="0"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>fechaHoraInicioAgenda</v>
       </c>
-      <c r="K9" s="31" t="s">
+      <c r="K18" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="31" t="s">
+      <c r="L18" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="40" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B7," en el contexto de ",A5," asociado al residente con el identificador' ",J9,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un Agenda en el contexto de Agendas asociado al residente con el identificador' fechaHoraInicioAgenda'.</v>
-      </c>
-      <c r="S9" s="125"/>
-    </row>
-    <row r="10" spans="1:19" ht="58.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="133"/>
-      <c r="B10" s="139"/>
-      <c r="C10" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="31" t="s">
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>Atributo que contiene la informacion del fechaHoraInicio del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S18" s="129"/>
+    </row>
+    <row r="19" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="135"/>
+      <c r="B19" s="176"/>
+      <c r="C19" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31" t="str">
-        <f t="shared" si="0"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>fechaHoraFinAgenda</v>
       </c>
-      <c r="K10" s="31" t="s">
+      <c r="K19" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="31" t="s">
+      <c r="L19" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="40" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B8," en el contexto de ",A6," asociado al residente con el identificador' ",J10,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' fechaHoraFinAgenda'.</v>
-      </c>
-      <c r="S10" s="125"/>
-    </row>
-    <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="133"/>
-      <c r="B11" s="131" t="s">
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v>Atributo que contiene la informacion del fechaHoraFin del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S19" s="129"/>
+    </row>
+    <row r="20" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="135"/>
+      <c r="B20" s="176"/>
+      <c r="C20" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="167" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="40"/>
+      <c r="S20" s="129"/>
+    </row>
+    <row r="21" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="135"/>
+      <c r="B21" s="134" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C21" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D21" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E21" s="32">
         <v>32</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F21" s="32">
         <v>32</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32" t="str">
-        <f>_xlfn.CONCAT(C7,$B$11)</f>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32" t="str">
+        <f>_xlfn.CONCAT(C21,$B$21)</f>
         <v>identificadorTurno</v>
       </c>
-      <c r="K11" s="32" t="s">
+      <c r="K21" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="32" t="s">
+      <c r="L21" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="32">
+      <c r="M21" s="32">
         <v>32</v>
       </c>
-      <c r="N11" s="32">
+      <c r="N21" s="32">
         <v>32</v>
       </c>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="41" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B11,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador de un Turno  en el contexto de Agendas.</v>
-      </c>
-      <c r="S11" s="125"/>
-    </row>
-    <row r="12" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="133"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="32" t="s">
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="41" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C21," del objeto dominio ",B21,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio Turno  en el contexto de Agendas.</v>
+      </c>
+      <c r="S21" s="129"/>
+    </row>
+    <row r="22" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="135"/>
+      <c r="B22" s="134"/>
+      <c r="C22" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E22" s="32">
         <v>1</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F22" s="32">
         <v>50</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32" t="str">
-        <f t="shared" ref="J12:J13" si="1">_xlfn.CONCAT(C8,$B$11)</f>
-        <v>NombreTurno</v>
-      </c>
-      <c r="K12" s="32" t="s">
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32" t="str">
+        <f t="shared" ref="J22:J25" si="4">_xlfn.CONCAT(C22,$B$21)</f>
+        <v>numeroTurnoTurno</v>
+      </c>
+      <c r="K22" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="32" t="s">
+      <c r="L22" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="32">
+      <c r="M22" s="32">
         <v>1</v>
       </c>
-      <c r="N12" s="32">
+      <c r="N22" s="32">
         <v>50</v>
       </c>
-      <c r="O12" s="32"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="41" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B11," en el contexto de ",A5," asociado a la reserva con el identificador' ",J12,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un Turno en el contexto de Agendas asociado a la reserva con el identificador' NombreTurno'.</v>
-      </c>
-      <c r="S12" s="125"/>
-    </row>
-    <row r="13" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="134"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32" t="str">
-        <f t="shared" si="1"/>
-        <v>fechaHoraInicioTurno</v>
-      </c>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="130"/>
-    </row>
-    <row r="14" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="41" t="str">
+        <f t="shared" ref="R22:R26" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C22," del objeto dominio ",B22,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del numeroTurno del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S22" s="129"/>
+    </row>
+    <row r="23" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="135"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>horaInicioTurno</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="41" t="str">
+        <f t="shared" si="5"/>
+        <v>Atributo que contiene la informacion del horaInicio del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S23" s="129"/>
+    </row>
+    <row r="24" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="135"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>horaFinTurno</v>
+      </c>
+      <c r="K24" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="41" t="str">
+        <f t="shared" si="5"/>
+        <v>Atributo que contiene la informacion del horaFin del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S24" s="129"/>
+    </row>
+    <row r="25" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="135"/>
+      <c r="B25" s="134"/>
+      <c r="C25" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>estadoTurno</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="41" t="str">
+        <f t="shared" si="5"/>
+        <v>Atributo que contiene la informacion del estado del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S25" s="129"/>
+    </row>
+    <row r="26" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="136"/>
+      <c r="B26" s="134"/>
+      <c r="C26" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="168" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="41"/>
+      <c r="S26" s="133"/>
+    </row>
+    <row r="27" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="S5:S13"/>
-    <mergeCell ref="B11:B13"/>
+  <mergeCells count="11">
+    <mergeCell ref="S5:S26"/>
+    <mergeCell ref="B21:B26"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="A5:A26"/>
+    <mergeCell ref="B16:B20"/>
+    <mergeCell ref="B5:B15"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D20" location="'Reserva-0001'!B5" display="ZonaComun" xr:uid="{9609D778-59AA-40D8-8622-3E7E74B0DA78}"/>
+    <hyperlink ref="D26" location="'Reserva-0001'!B16" display="Agenda" xr:uid="{965909F4-EE4F-44DD-B44D-2F2AEA991811}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4E4C5E7-072D-46C9-A943-F12FD1E94927}">
-  <dimension ref="A1:S10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="13" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="13" customWidth="1"/>
     <col min="2" max="2" width="21" style="13" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="58" style="26" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.44140625" style="13"/>
+    <col min="19" max="19" width="17.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="112" t="str">
+      <c r="B1" s="118" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="113"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="102"/>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="104"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="114" t="s">
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="119"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="102"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115" t="s">
+      <c r="B3" s="121"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="116" t="s">
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="118" t="s">
+      <c r="S3" s="124" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>28</v>
       </c>
@@ -2707,123 +3364,123 @@
       <c r="Q4" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="117"/>
-      <c r="S4" s="119"/>
-    </row>
-    <row r="5" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="140" t="s">
+      <c r="R4" s="123"/>
+      <c r="S4" s="125"/>
+    </row>
+    <row r="5" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="169" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="141" t="s">
+      <c r="B5" s="138" t="s">
         <v>82</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E5" s="31">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F5" s="31">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G5" s="31"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="J5" s="31" t="str">
-        <f>_xlfn.CONCAT(C5,$B$5)</f>
-        <v>identificadorInmueble</v>
+        <f t="shared" ref="J5" si="0">_xlfn.CONCAT(C5,$B$5)</f>
+        <v>TipoInmueble(Nombre)Inmueble</v>
       </c>
       <c r="K5" s="31" t="s">
         <v>59</v>
       </c>
       <c r="L5" s="31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M5" s="31">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="N5" s="31">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="O5" s="31"/>
       <c r="P5" s="31"/>
       <c r="Q5" s="31"/>
       <c r="R5" s="40" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B5,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador de un Inmueble  en el contexto de Residentes.</v>
-      </c>
-      <c r="S5" s="124" t="str">
-        <f>B8</f>
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del TipoInmueble(Nombre) del objeto dominio Inmueble  en el contexto de Residentes.</v>
+      </c>
+      <c r="S5" s="128" t="str">
+        <f>B9</f>
         <v>Residente</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="140"/>
-      <c r="B6" s="142"/>
+    <row r="6" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="170"/>
+      <c r="B6" s="139"/>
       <c r="C6" s="31" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" s="31">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F6" s="31">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G6" s="31"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="J6" s="31" t="str">
-        <f t="shared" ref="J6:J7" si="0">_xlfn.CONCAT(C6,$B$5)</f>
-        <v>tipoInmuebleInmueble</v>
+        <f>_xlfn.CONCAT(C6,$B$5)</f>
+        <v>TipoZonaInmueble(Identificador)Inmueble</v>
       </c>
       <c r="K6" s="31" t="s">
         <v>59</v>
       </c>
       <c r="L6" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M6" s="31">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N6" s="31">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="O6" s="31"/>
       <c r="P6" s="31"/>
       <c r="Q6" s="31"/>
       <c r="R6" s="40" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B5," en el contexto de ",A5," asociado al residente con el identificador' ",J6,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un Inmueble en el contexto de Residentes asociado al residente con el identificador' tipoInmuebleInmueble'.</v>
-      </c>
-      <c r="S6" s="125"/>
-    </row>
-    <row r="7" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="140"/>
-      <c r="B7" s="143"/>
+        <f t="shared" ref="R6:R8" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del TipoZonaInmueble(Identificador) del objeto dominio   en el contexto de Residentes.</v>
+      </c>
+      <c r="S6" s="129"/>
+    </row>
+    <row r="7" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="170"/>
+      <c r="B7" s="139"/>
       <c r="C7" s="31" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="E7" s="31">
         <v>1</v>
       </c>
       <c r="F7" s="31">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G7" s="31"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="J7" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>numeroViviendaInmueble</v>
+        <f t="shared" ref="J7" si="2">_xlfn.CONCAT(C7,$B$5)</f>
+        <v>TipoZonaInmueble(Nombre)Inmueble</v>
       </c>
       <c r="K7" s="31" t="s">
         <v>59</v>
@@ -2835,118 +3492,237 @@
         <v>1</v>
       </c>
       <c r="N7" s="31">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O7" s="31"/>
       <c r="P7" s="31"/>
       <c r="Q7" s="31"/>
       <c r="R7" s="40" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B6," en el contexto de ",A6," asociado al residente con el identificador' ",J7,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' numeroViviendaInmueble'.</v>
-      </c>
-      <c r="S7" s="125"/>
-    </row>
-    <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="140"/>
-      <c r="B8" s="131" t="s">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del TipoZonaInmueble(Nombre) del objeto dominio   en el contexto de Residentes.</v>
+      </c>
+      <c r="S7" s="129"/>
+    </row>
+    <row r="8" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="170"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="31">
+        <v>1</v>
+      </c>
+      <c r="F8" s="31">
+        <v>20</v>
+      </c>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31">
+        <v>1</v>
+      </c>
+      <c r="I8" s="31">
+        <v>200</v>
+      </c>
+      <c r="J8" s="31" t="str">
+        <f t="shared" ref="J8" si="3">_xlfn.CONCAT(C8,$B$5)</f>
+        <v>ZonaInmueble(NumeroZonaInmueble)Inmueble</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="M8" s="31">
+        <v>1</v>
+      </c>
+      <c r="N8" s="31">
+        <v>20</v>
+      </c>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="31">
+        <v>200</v>
+      </c>
+      <c r="R8" s="40" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del ZonaInmueble(NumeroZonaInmueble) del objeto dominio   en el contexto de Residentes.</v>
+      </c>
+      <c r="S8" s="129"/>
+    </row>
+    <row r="9" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="170"/>
+      <c r="B9" s="173" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C9" s="32" t="s">
         <v>55</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="32">
-        <v>32</v>
-      </c>
-      <c r="F8" s="32">
-        <v>32</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32" t="str">
-        <f>_xlfn.CONCAT(C5,$B$8)</f>
-        <v>identificadorResidente</v>
-      </c>
-      <c r="K8" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="32">
-        <v>32</v>
-      </c>
-      <c r="N8" s="32">
-        <v>32</v>
-      </c>
-      <c r="O8" s="32"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="32"/>
-      <c r="R8" s="41" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del identificador de un ",B8,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador de un Residente  en el contexto de Residentes.</v>
-      </c>
-      <c r="S8" s="125"/>
-    </row>
-    <row r="9" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="140"/>
-      <c r="B9" s="131"/>
-      <c r="C9" s="32" t="s">
-        <v>57</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>56</v>
       </c>
       <c r="E9" s="32">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F9" s="32">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32" t="str">
-        <f>_xlfn.CONCAT(C6,$B$8)</f>
-        <v>tipoInmuebleResidente</v>
+        <f>_xlfn.CONCAT(C9,$B$9)</f>
+        <v>identificadorResidente</v>
       </c>
       <c r="K9" s="32" t="s">
         <v>59</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M9" s="32">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N9" s="32">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O9" s="32"/>
       <c r="P9" s="32"/>
       <c r="Q9" s="32"/>
       <c r="R9" s="41" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B8," en el contexto de ",A5," asociado a la reserva con el identificador' ",J9,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un Residente en el contexto de Residentes asociado a la reserva con el identificador' tipoInmuebleResidente'.</v>
-      </c>
-      <c r="S9" s="130"/>
-    </row>
-    <row r="10" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C9," del objeto dominio ",B9,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio Residente  en el contexto de Residentes.</v>
+      </c>
+      <c r="S9" s="129"/>
+    </row>
+    <row r="10" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="170"/>
+      <c r="B10" s="174"/>
+      <c r="C10" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="32">
+        <v>1</v>
+      </c>
+      <c r="F10" s="32">
+        <v>50</v>
+      </c>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32" t="str">
+        <f t="shared" ref="J10:J11" si="4">_xlfn.CONCAT(C10,$B$9)</f>
+        <v>nombreResidente</v>
+      </c>
+      <c r="K10" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="32">
+        <v>1</v>
+      </c>
+      <c r="N10" s="32">
+        <v>50</v>
+      </c>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="41" t="str">
+        <f t="shared" ref="R10:R11" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Residentes.</v>
+      </c>
+      <c r="S10" s="129"/>
+    </row>
+    <row r="11" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="170"/>
+      <c r="B11" s="174"/>
+      <c r="C11" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32">
+        <v>1</v>
+      </c>
+      <c r="I11" s="32">
+        <v>100000000000</v>
+      </c>
+      <c r="J11" s="32" t="str">
+        <f t="shared" si="4"/>
+        <v>numeroDocumentoResidente</v>
+      </c>
+      <c r="K11" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="32">
+        <v>100000000000</v>
+      </c>
+      <c r="R11" s="41" t="str">
+        <f t="shared" si="5"/>
+        <v>Atributo que contiene la informacion del numeroDocumento del objeto dominio   en el contexto de Residentes.</v>
+      </c>
+      <c r="S11" s="129"/>
+    </row>
+    <row r="12" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="171"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="172"/>
+    </row>
+    <row r="13" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="S5:S9"/>
-    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="S5:S12"/>
+    <mergeCell ref="B9:B12"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B5:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2955,7 +3731,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1464EB49-FF8E-46BB-B8BB-A3B13262BCA8}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2965,43 +3741,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825409BB-6EDF-4233-9680-0DFD77A9FF39}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="22.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.6640625" style="7" customWidth="1"/>
-    <col min="5" max="16384" width="11.44140625" style="2"/>
+    <col min="1" max="1" width="36.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="22.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.7109375" style="7" customWidth="1"/>
+    <col min="5" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="78"/>
-    </row>
-    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="75"/>
+      <c r="D1" s="76"/>
+    </row>
+    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="82" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="84"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="82"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -3015,133 +3791,133 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="86" t="s">
         <v>79</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="89" t="s">
+      <c r="D5" s="87" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="87"/>
-      <c r="B6" s="88"/>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="85"/>
+      <c r="B6" s="86"/>
       <c r="C6" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="89"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="87"/>
-      <c r="B7" s="88"/>
+      <c r="D6" s="87"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="85"/>
+      <c r="B7" s="86"/>
       <c r="C7" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="89"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="87"/>
-      <c r="B8" s="88"/>
+      <c r="D7" s="87"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="85"/>
+      <c r="B8" s="86"/>
       <c r="C8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="89"/>
-    </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="87"/>
-      <c r="B9" s="88"/>
+      <c r="D8" s="87"/>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="85"/>
+      <c r="B9" s="86"/>
       <c r="C9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="89"/>
-    </row>
-    <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="85" t="s">
+      <c r="D9" s="87"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="84" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="85" t="s">
+      <c r="D10" s="83" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="85"/>
-      <c r="B11" s="86"/>
+    <row r="11" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="83"/>
+      <c r="B11" s="84"/>
       <c r="C11" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="85"/>
-    </row>
-    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="93" t="s">
+      <c r="D11" s="83"/>
+    </row>
+    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="88" t="s">
         <v>83</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="93" t="s">
+      <c r="D12" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
-      <c r="B13" s="91"/>
+    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="92"/>
+      <c r="B13" s="89"/>
       <c r="C13" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="94"/>
-    </row>
-    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="95"/>
-      <c r="B14" s="92"/>
+      <c r="D13" s="92"/>
+    </row>
+    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="93"/>
+      <c r="B14" s="90"/>
       <c r="C14" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="95"/>
-    </row>
-    <row r="15" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="68" t="s">
+      <c r="D14" s="93"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="71" t="s">
+      <c r="B15" s="69" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="74" t="s">
+      <c r="D15" s="72" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="69"/>
-      <c r="B16" s="72"/>
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="67"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="75"/>
-    </row>
-    <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="70"/>
-      <c r="B17" s="73"/>
+      <c r="D16" s="73"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="68"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="76"/>
+      <c r="D17" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3199,112 +3975,112 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450F8E16-67C6-432D-A5AA-BF67F960EE18}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="38.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="38.28515625" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="64" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="13"/>
+    <col min="7" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="96" t="str">
+      <c r="B1" s="94" t="str">
         <f>Contextos!B5</f>
         <v xml:space="preserve"> Conjuntos residenciales</v>
       </c>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="97"/>
-    </row>
-    <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="95"/>
+    </row>
+    <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="98" t="str">
+      <c r="B2" s="96" t="str">
         <f>Contextos!D5</f>
         <v>Contexto cuya motivación es Gestionar la estructura física y los recursos disponibles en cada conjunto residencial. Aquí se manejan los datos sobre qué conjuntos existen, dónde están ubicados, qué recursos ofrecen según una Agenda con respectivos turnos para cada zona.</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="99"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="97"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="100" t="str">
+      <c r="B3" s="98" t="str">
         <f>Contextos!A5</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="101"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="102" t="s">
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="99"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="102"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="105" t="s">
+      <c r="D5" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="105"/>
-      <c r="F5" s="106" t="s">
+      <c r="E5" s="103"/>
+      <c r="F5" s="104" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="106"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="104"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="105"/>
+      <c r="C7" s="103"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="106"/>
-    </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F7" s="104"/>
+    </row>
+    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
         <v>40</v>
       </c>
@@ -3326,7 +4102,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>40</v>
       </c>
@@ -3348,7 +4124,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
         <v>40</v>
       </c>
@@ -3370,7 +4146,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>81</v>
       </c>
@@ -3421,115 +4197,115 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D386A343-6D12-4FEA-AEEF-63E15D63FE79}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.88671875" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.28515625" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="64" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="13"/>
+    <col min="7" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="96" t="str">
+      <c r="B1" s="94" t="str">
         <f>Contextos!B10</f>
         <v>Residentes</v>
       </c>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="97"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="95"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="98" t="str">
+      <c r="B2" s="96" t="str">
         <f>Contextos!D10</f>
         <v>Contexto cuya motivación es encargarce de manejar la información de los residentes, incluidas sus identificaciones, contacto, y la relación entre el residente y su residencia dentro del conjunto.</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="99"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="97"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="100" t="str">
+      <c r="B3" s="98" t="str">
         <f>Contextos!A10</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="101"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="102" t="s">
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="99"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="102"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="105" t="s">
+      <c r="D5" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="105"/>
-      <c r="F5" s="106" t="s">
+      <c r="E5" s="103"/>
+      <c r="F5" s="104" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="106"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="104"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="105"/>
+      <c r="C7" s="103"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="106"/>
-    </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F7" s="104"/>
+    </row>
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>24</v>
@@ -3539,11 +4315,11 @@
       </c>
       <c r="D8" s="20" t="str">
         <f>B8&amp;" "&amp;A8&amp;"-0001"</f>
-        <v>Residente Inmueble-0001</v>
+        <v>Residente ConjutosResidenciales-0001</v>
       </c>
       <c r="E8" s="21" t="str">
         <f>_xlfn.CONCAT(A8," de ",B8)</f>
-        <v>Inmueble de Residente</v>
+        <v>ConjutosResidenciales de Residente</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>87</v>
@@ -3580,108 +4356,108 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59635CF3-0DE6-45E6-A198-1E7042F5E8F9}">
-  <dimension ref="A1:S16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="31" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="58" style="26" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.44140625" style="13"/>
+    <col min="19" max="19" width="17.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="112" t="str">
+      <c r="B1" s="118" t="str">
         <f>Residentes!D8</f>
-        <v>Residente Inmueble-0001</v>
-      </c>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="113"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="102"/>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="104"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="114" t="s">
+        <v>Residente ConjutosResidenciales-0001</v>
+      </c>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="119"/>
+    </row>
+    <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="151"/>
+      <c r="S2" s="102"/>
+    </row>
+    <row r="3" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115" t="s">
+      <c r="B3" s="121"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="116" t="s">
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="147"/>
+      <c r="R3" s="152" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="118" t="s">
+      <c r="S3" s="149" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>28</v>
       </c>
@@ -3730,24 +4506,24 @@
       <c r="P4" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="16" t="s">
+      <c r="Q4" s="148" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="117"/>
-      <c r="S4" s="119"/>
-    </row>
-    <row r="5" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="107" t="s">
+      <c r="R4" s="153"/>
+      <c r="S4" s="150"/>
+    </row>
+    <row r="5" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="145" t="s">
+      <c r="B5" s="110" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="51" t="s">
         <v>93</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>94</v>
       </c>
       <c r="E5" s="51">
         <v>1</v>
@@ -3766,7 +4542,7 @@
         <v>59</v>
       </c>
       <c r="L5" s="51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M5" s="51">
         <v>1</v>
@@ -3777,21 +4553,23 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="52"/>
-      <c r="R5" s="62" t="str">
+      <c r="R5" s="154" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del numeroVivienda del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S5" s="109" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="107"/>
-      <c r="B6" s="146"/>
-      <c r="C6" s="144" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="51"/>
+      <c r="S5" s="107" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="105"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="155" t="s">
+        <v>81</v>
+      </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
@@ -3805,307 +4583,311 @@
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="52"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="109"/>
-    </row>
-    <row r="7" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="107"/>
-      <c r="B7" s="147" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="50" t="s">
+      <c r="R6" s="154"/>
+      <c r="S6" s="107"/>
+    </row>
+    <row r="7" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="105"/>
+      <c r="B7" s="112"/>
+      <c r="C7" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="155" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="154"/>
+      <c r="S7" s="107"/>
+    </row>
+    <row r="8" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="105"/>
+      <c r="B8" s="113" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D8" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E8" s="31">
         <v>32</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F8" s="31">
         <v>32</v>
-      </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31" t="str">
-        <f>_xlfn.CONCAT(C7,$B$7)</f>
-        <v>identificadorTipoInmueble</v>
-      </c>
-      <c r="K7" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="L7" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="M7" s="31">
-        <v>32</v>
-      </c>
-      <c r="N7" s="31">
-        <v>32</v>
-      </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="63" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C7," del objeto dominio ",B7,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S7" s="109"/>
-    </row>
-    <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="107"/>
-      <c r="B8" s="148"/>
-      <c r="C8" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="31">
-        <v>1</v>
-      </c>
-      <c r="F8" s="31">
-        <v>50</v>
       </c>
       <c r="G8" s="31"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="J8" s="31" t="str">
-        <f>_xlfn.CONCAT(C8,$B$7)</f>
-        <v>nombreTipoInmueble</v>
-      </c>
-      <c r="K8" s="31"/>
+        <f t="shared" ref="J8:J14" si="0">_xlfn.CONCAT(C8,$B$8)</f>
+        <v>identificadorTipoInmueble</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>59</v>
+      </c>
       <c r="L8" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M8" s="31">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N8" s="31">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O8" s="31"/>
       <c r="P8" s="31"/>
       <c r="Q8" s="53"/>
       <c r="R8" s="63" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C8," del objeto dominio ",B8,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S8" s="109"/>
-    </row>
-    <row r="9" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="107"/>
-      <c r="B9" s="149"/>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S8" s="107"/>
+    </row>
+    <row r="9" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="105"/>
+      <c r="B9" s="114"/>
       <c r="C9" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
+        <v>57</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="31">
+        <v>1</v>
+      </c>
+      <c r="F9" s="31">
+        <v>50</v>
+      </c>
       <c r="G9" s="31"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
+      <c r="J9" s="31" t="str">
+        <f t="shared" si="0"/>
+        <v>nombreTipoInmueble</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="31">
+        <v>1</v>
+      </c>
+      <c r="N9" s="31">
+        <v>50</v>
+      </c>
       <c r="O9" s="31"/>
       <c r="P9" s="31"/>
       <c r="Q9" s="53"/>
-      <c r="R9" s="63"/>
-      <c r="S9" s="109"/>
-    </row>
-    <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="107"/>
-      <c r="B10" s="150" t="s">
+      <c r="R9" s="59" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C9," del objeto dominio ",B9,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S9" s="107"/>
+    </row>
+    <row r="10" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="105"/>
+      <c r="B10" s="115" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="56">
         <v>32</v>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="56">
         <v>32</v>
       </c>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="59" t="str">
-        <f>_xlfn.CONCAT(C10,$B$7)</f>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56" t="str">
+        <f t="shared" si="0"/>
         <v>identificadorTipoInmueble</v>
       </c>
-      <c r="K10" s="59" t="s">
+      <c r="K10" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="59" t="s">
+      <c r="L10" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="M10" s="59">
+      <c r="M10" s="56">
         <v>32</v>
       </c>
-      <c r="N10" s="59">
+      <c r="N10" s="56">
         <v>32</v>
       </c>
-      <c r="O10" s="59"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="64" t="str">
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="60" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",A3,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Caracterización Origen.</v>
       </c>
-      <c r="S10" s="109"/>
-    </row>
-    <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="107"/>
-      <c r="B11" s="152"/>
-      <c r="C11" s="58" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59" t="str">
-        <f>_xlfn.CONCAT(C11,$B$7)</f>
-        <v>TipoZonaInmuebleTipoInmueble</v>
-      </c>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="59"/>
-      <c r="O11" s="59"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="64" t="str">
+      <c r="S10" s="107"/>
+    </row>
+    <row r="11" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="105"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="156" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="56"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="60" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C11," del objeto dominio ",B11,"  en el contexto de ",A3,".")</f>
-        <v>Atributo que contiene la informacion del TipoZonaInmueble del objeto dominio   en el contexto de Caracterización Origen.</v>
-      </c>
-      <c r="S11" s="109"/>
-    </row>
-    <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="107"/>
-      <c r="B12" s="151"/>
-      <c r="C12" s="58" t="s">
+        <v>Atributo que contiene la informacion del tipoZonaInmueble del objeto dominio   en el contexto de Caracterización Origen.</v>
+      </c>
+      <c r="S11" s="107"/>
+    </row>
+    <row r="12" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="105"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="156" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="59" t="str">
-        <f>_xlfn.CONCAT(C12,$B$7)</f>
-        <v>ConjuntoResidencialTipoInmueble</v>
-      </c>
-      <c r="K12" s="59"/>
-      <c r="L12" s="59"/>
-      <c r="M12" s="59"/>
-      <c r="N12" s="59"/>
-      <c r="O12" s="59"/>
-      <c r="P12" s="59"/>
-      <c r="Q12" s="60"/>
-      <c r="R12" s="64"/>
-      <c r="S12" s="109"/>
-    </row>
-    <row r="13" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="107"/>
-      <c r="B13" s="150" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="58" t="s">
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="60"/>
+      <c r="S12" s="107"/>
+    </row>
+    <row r="13" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="105"/>
+      <c r="B13" s="141" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="59" t="s">
+      <c r="D13" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="59">
+      <c r="E13" s="143">
         <v>32</v>
       </c>
-      <c r="F13" s="59">
+      <c r="F13" s="143">
         <v>32</v>
       </c>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59" t="str">
-        <f>_xlfn.CONCAT(C13,$B$7)</f>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143" t="str">
+        <f t="shared" si="0"/>
         <v>identificadorTipoInmueble</v>
       </c>
-      <c r="K13" s="59" t="s">
+      <c r="K13" s="143" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="59" t="s">
+      <c r="L13" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="M13" s="59">
+      <c r="M13" s="143">
         <v>32</v>
       </c>
-      <c r="N13" s="59">
+      <c r="N13" s="143">
         <v>32</v>
       </c>
-      <c r="O13" s="59"/>
-      <c r="P13" s="59"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="64" t="str">
+      <c r="O13" s="143"/>
+      <c r="P13" s="143"/>
+      <c r="Q13" s="144"/>
+      <c r="R13" s="145" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C13," del objeto dominio ",B13,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio TipoZonaInmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S13" s="109"/>
-    </row>
-    <row r="14" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="107"/>
-      <c r="B14" s="152"/>
-      <c r="C14" s="58" t="s">
+      <c r="S13" s="107"/>
+    </row>
+    <row r="14" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="105"/>
+      <c r="B14" s="146"/>
+      <c r="C14" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="143" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="59">
+      <c r="E14" s="143">
         <v>1</v>
       </c>
-      <c r="F14" s="59">
+      <c r="F14" s="143">
         <v>50</v>
       </c>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59" t="str">
-        <f>_xlfn.CONCAT(C14,$B$7)</f>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143" t="str">
+        <f t="shared" si="0"/>
         <v>nombreTipoInmueble</v>
       </c>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59" t="s">
+      <c r="K14" s="143" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="143" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="59">
+      <c r="M14" s="143">
         <v>1</v>
       </c>
-      <c r="N14" s="59">
+      <c r="N14" s="143">
         <v>50</v>
       </c>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="64" t="str">
+      <c r="O14" s="143"/>
+      <c r="P14" s="143"/>
+      <c r="Q14" s="144"/>
+      <c r="R14" s="145" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C14," del objeto dominio ",B14,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S14" s="109"/>
-    </row>
-    <row r="15" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="107"/>
-      <c r="B15" s="111" t="s">
+      <c r="S14" s="107"/>
+    </row>
+    <row r="15" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="105"/>
+      <c r="B15" s="109" t="s">
         <v>61</v>
       </c>
       <c r="C15" s="32" t="s">
@@ -4124,7 +4906,7 @@
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32" t="str">
-        <f>_xlfn.CONCAT(C7,$B$15)</f>
+        <f>_xlfn.CONCAT(C8,$B$15)</f>
         <v>identificadorConjuntoResidencial</v>
       </c>
       <c r="K15" s="32" t="s">
@@ -4142,15 +4924,15 @@
       <c r="O15" s="32"/>
       <c r="P15" s="32"/>
       <c r="Q15" s="54"/>
-      <c r="R15" s="65" t="str">
+      <c r="R15" s="61" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C15," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S15" s="109"/>
-    </row>
-    <row r="16" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="108"/>
-      <c r="B16" s="111"/>
+      <c r="S15" s="107"/>
+    </row>
+    <row r="16" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="106"/>
+      <c r="B16" s="109"/>
       <c r="C16" s="32" t="s">
         <v>57</v>
       </c>
@@ -4167,7 +4949,7 @@
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32" t="str">
-        <f>_xlfn.CONCAT(C8,$B$15)</f>
+        <f>_xlfn.CONCAT(C9,$B$15)</f>
         <v>nombreConjuntoResidencial</v>
       </c>
       <c r="K16" s="32" t="s">
@@ -4185,11 +4967,14 @@
       <c r="O16" s="32"/>
       <c r="P16" s="32"/>
       <c r="Q16" s="54"/>
-      <c r="R16" s="65" t="str">
+      <c r="R16" s="61" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S16" s="110"/>
+      <c r="S16" s="108"/>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4202,11 +4987,17 @@
     <mergeCell ref="A5:A16"/>
     <mergeCell ref="S5:S16"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B9"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B10:B12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D7" location="'Residente ConjutosResidenciales'!B8" display="TipoInmueble" xr:uid="{7D0F26B2-16BB-4D32-9316-813C92F956E5}"/>
+    <hyperlink ref="D11" location="'Conjuntos Residenciales'!B13" display="TipoZonaInmueble" xr:uid="{34181B3B-B9AE-4560-8F56-BDA0D6B05CD0}"/>
+    <hyperlink ref="D12" location="'Conjuntos Residenciales'!B16" display="ConjuntoResidencial" xr:uid="{A2395E41-D8AC-474A-BE9C-32FCADDD0F2C}"/>
+    <hyperlink ref="D6" location="'Conjuntos Residenciales'!B10" display="ZonaInmueble" xr:uid="{E001D96D-791E-43A6-B8BA-893283B14284}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4214,114 +5005,114 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAA1C796-BDF1-44E4-8EC8-5B53FD905390}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="38.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="38.28515625" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="64" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="13"/>
+    <col min="7" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="96" t="str">
+      <c r="B1" s="94" t="str">
         <f>Contextos!B12</f>
         <v>Agendas</v>
       </c>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="97"/>
-    </row>
-    <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="95"/>
+    </row>
+    <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="98" t="str">
+      <c r="B2" s="96" t="str">
         <f>Contextos!D12</f>
         <v>Contexto cuya motivación es la de gestionar la estructura de la agenda que va a tener una zona común durante un un tiempo estimado y sus diferentes turnos.</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="99"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="97"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="100" t="str">
+      <c r="B3" s="98" t="str">
         <f>Contextos!A12</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="101"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="102" t="s">
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="99"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="102"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="105" t="s">
+      <c r="D5" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="105"/>
-      <c r="F5" s="106" t="s">
+      <c r="E5" s="103"/>
+      <c r="F5" s="104" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="106"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="104"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="105"/>
+      <c r="C7" s="103"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="106"/>
-    </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F7" s="104"/>
+    </row>
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>64</v>
@@ -4331,17 +5122,17 @@
       </c>
       <c r="D8" s="45" t="str">
         <f>B8&amp;" "&amp;A8&amp;"-0001"</f>
-        <v>Agenda ZonaComun-0001</v>
+        <v>Agenda ConjuntosResidenciales-0001</v>
       </c>
       <c r="E8" s="39" t="str">
         <f>_xlfn.CONCAT(A8," de ",B8)</f>
-        <v>ZonaComun de Agenda</v>
+        <v>ConjuntosResidenciales de Agenda</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>64</v>
       </c>
@@ -4394,108 +5185,108 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{285DCF13-A122-49FD-BB4E-83BC928CCAC1}">
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="31" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="58" style="26" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.44140625" style="13"/>
+    <col min="19" max="19" width="17.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="112" t="str">
+      <c r="B1" s="118" t="str">
         <f>Agendas!D8</f>
-        <v>Agenda ZonaComun-0001</v>
-      </c>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="113"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="102"/>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="104"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="114" t="s">
+        <v>Agenda ConjuntosResidenciales-0001</v>
+      </c>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="119"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="102"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115" t="s">
+      <c r="B3" s="121"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="116" t="s">
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="118" t="s">
+      <c r="S3" s="124" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>28</v>
       </c>
@@ -4547,14 +5338,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="120"/>
-      <c r="S4" s="119"/>
-    </row>
-    <row r="5" spans="1:19" ht="28.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="121" t="s">
+      <c r="R4" s="123"/>
+      <c r="S4" s="125"/>
+    </row>
+    <row r="5" spans="1:19" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="127" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="126" t="s">
+      <c r="B5" s="130" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -4590,18 +5381,18 @@
       </c>
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="122" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B7," en el contexto de ",A5," asociado al residente con el identificador' ",J9,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un  en el contexto de Conjuntos Residenciales asociado al residente con el identificador' unidadTiempoUsoZonaComun'.</v>
-      </c>
-      <c r="S5" s="124" t="s">
+      <c r="Q5" s="52"/>
+      <c r="R5" s="154" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaComun  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S5" s="163" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="107"/>
-      <c r="B6" s="127"/>
+    <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="105"/>
+      <c r="B6" s="131"/>
       <c r="C6" s="51" t="s">
         <v>4</v>
       </c>
@@ -4609,7 +5400,7 @@
         <v>58</v>
       </c>
       <c r="E6" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="51">
         <v>50</v>
@@ -4618,7 +5409,7 @@
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
       <c r="J6" s="51" t="str">
-        <f t="shared" ref="J6:J9" si="0">_xlfn.CONCAT(C6,$B$5)</f>
+        <f t="shared" ref="J6:J15" si="0">_xlfn.CONCAT(C6,$B$5)</f>
         <v>NombreZonaComun</v>
       </c>
       <c r="K6" s="51" t="s">
@@ -4635,21 +5426,28 @@
       </c>
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="123"/>
-      <c r="S6" s="125"/>
-    </row>
-    <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="107"/>
-      <c r="B7" s="127"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="154" t="str">
+        <f t="shared" ref="R6:R9" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S6" s="163"/>
+    </row>
+    <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="105"/>
+      <c r="B7" s="131"/>
       <c r="C7" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
+        <v>93</v>
+      </c>
+      <c r="E7" s="51">
+        <v>1</v>
+      </c>
+      <c r="F7" s="51">
+        <v>4</v>
+      </c>
       <c r="G7" s="51"/>
       <c r="H7" s="51"/>
       <c r="I7" s="51"/>
@@ -4657,174 +5455,424 @@
         <f t="shared" si="0"/>
         <v>capacidadPersonasZonaComun</v>
       </c>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
+      <c r="K7" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="M7" s="51">
+        <v>1</v>
+      </c>
+      <c r="N7" s="51">
+        <v>4</v>
+      </c>
       <c r="O7" s="51"/>
       <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="122" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B9," en el contexto de ",A7," asociado al residente con el identificador' ",J11,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' nombreConjuntoResidencial'.</v>
-      </c>
-      <c r="S7" s="125"/>
-    </row>
-    <row r="8" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="107"/>
-      <c r="B8" s="127"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del capacidadPersonas del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S7" s="163"/>
+    </row>
+    <row r="8" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="105"/>
+      <c r="B8" s="131"/>
       <c r="C8" s="51" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
+        <v>58</v>
+      </c>
+      <c r="E8" s="51">
+        <v>0</v>
+      </c>
+      <c r="F8" s="51">
+        <v>255</v>
+      </c>
       <c r="G8" s="51"/>
       <c r="H8" s="51"/>
       <c r="I8" s="51"/>
       <c r="J8" s="51" t="str">
         <f t="shared" si="0"/>
-        <v>tiempoUsoZonaComun</v>
-      </c>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
+        <v>descripcionZonaComun</v>
+      </c>
+      <c r="K8" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="51">
+        <v>0</v>
+      </c>
+      <c r="N8" s="51">
+        <v>255</v>
+      </c>
       <c r="O8" s="51"/>
       <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="129"/>
-      <c r="S8" s="125"/>
-    </row>
-    <row r="9" spans="1:19" ht="61.8" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="107"/>
-      <c r="B9" s="128"/>
+      <c r="Q8" s="52"/>
+      <c r="R8" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del descripcion del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S8" s="163"/>
+    </row>
+    <row r="9" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="105"/>
+      <c r="B9" s="131"/>
       <c r="C9" s="51" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
+        <v>93</v>
+      </c>
+      <c r="E9" s="51">
+        <v>1</v>
+      </c>
+      <c r="F9" s="51">
+        <v>3</v>
+      </c>
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
       <c r="I9" s="51"/>
       <c r="J9" s="51" t="str">
         <f t="shared" si="0"/>
-        <v>unidadTiempoUsoZonaComun</v>
-      </c>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
+        <v>tiempoUsoZonaComun</v>
+      </c>
+      <c r="K9" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="M9" s="51">
+        <v>1</v>
+      </c>
+      <c r="N9" s="51">
+        <v>3</v>
+      </c>
       <c r="O9" s="51"/>
       <c r="P9" s="51"/>
       <c r="Q9" s="52"/>
-      <c r="R9" s="57" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B11," en el contexto de ",A9," asociado al residente con el identificador' ",J13,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado al residente con el identificador' '.</v>
-      </c>
-      <c r="S9" s="125"/>
-    </row>
-    <row r="10" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="107"/>
-      <c r="B10" s="111" t="s">
+      <c r="R9" s="154" t="str">
+        <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del tiempoUso del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S9" s="163"/>
+    </row>
+    <row r="10" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="105"/>
+      <c r="B10" s="131"/>
+      <c r="C10" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="155" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="52"/>
+      <c r="R10" s="154"/>
+      <c r="S10" s="163"/>
+    </row>
+    <row r="11" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="105"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="155" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="154"/>
+      <c r="S11" s="163"/>
+    </row>
+    <row r="12" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="105"/>
+      <c r="B12" s="158" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="159" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D12" s="159" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E12" s="159">
         <v>32</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F12" s="159">
         <v>32</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32" t="str">
-        <f>_xlfn.CONCAT(C10,$B$10)</f>
+      <c r="G12" s="159"/>
+      <c r="H12" s="159"/>
+      <c r="I12" s="159"/>
+      <c r="J12" s="159" t="str">
+        <f t="shared" si="0"/>
+        <v>identificadorZonaComun</v>
+      </c>
+      <c r="K12" s="159"/>
+      <c r="L12" s="159" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="159">
+        <v>32</v>
+      </c>
+      <c r="N12" s="159">
+        <v>32</v>
+      </c>
+      <c r="O12" s="159"/>
+      <c r="P12" s="159"/>
+      <c r="Q12" s="160"/>
+      <c r="R12" s="164" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C12," del objeto dominio ",B12,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio UnidadTiempoUso  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S12" s="163"/>
+    </row>
+    <row r="13" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="105"/>
+      <c r="B13" s="161"/>
+      <c r="C13" s="159" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="159" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="159">
+        <v>3</v>
+      </c>
+      <c r="F13" s="159">
+        <v>50</v>
+      </c>
+      <c r="G13" s="159"/>
+      <c r="H13" s="159"/>
+      <c r="I13" s="159"/>
+      <c r="J13" s="159" t="str">
+        <f t="shared" si="0"/>
+        <v>nombreZonaComun</v>
+      </c>
+      <c r="K13" s="159"/>
+      <c r="L13" s="159" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="159">
+        <v>3</v>
+      </c>
+      <c r="N13" s="159">
+        <v>50</v>
+      </c>
+      <c r="O13" s="159"/>
+      <c r="P13" s="159"/>
+      <c r="Q13" s="160"/>
+      <c r="R13" s="164" t="str">
+        <f t="shared" ref="R13:R15" si="2">_xlfn.CONCAT("Atributo que contiene la informacion del ",C13," del objeto dominio ",B13,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S13" s="163"/>
+    </row>
+    <row r="14" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="105"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="159" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="159" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="159">
+        <v>1</v>
+      </c>
+      <c r="F14" s="159">
+        <v>6</v>
+      </c>
+      <c r="G14" s="159"/>
+      <c r="H14" s="159"/>
+      <c r="I14" s="159"/>
+      <c r="J14" s="159" t="str">
+        <f t="shared" si="0"/>
+        <v>abreviaturaZonaComun</v>
+      </c>
+      <c r="K14" s="159"/>
+      <c r="L14" s="159" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="159">
+        <v>1</v>
+      </c>
+      <c r="N14" s="159">
+        <v>6</v>
+      </c>
+      <c r="O14" s="159"/>
+      <c r="P14" s="159"/>
+      <c r="Q14" s="160"/>
+      <c r="R14" s="164" t="str">
+        <f t="shared" si="2"/>
+        <v>Atributo que contiene la informacion del abreviatura del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S14" s="163"/>
+    </row>
+    <row r="15" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="105"/>
+      <c r="B15" s="162"/>
+      <c r="C15" s="159" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="159" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="159">
+        <v>1</v>
+      </c>
+      <c r="F15" s="159">
+        <v>10</v>
+      </c>
+      <c r="G15" s="159"/>
+      <c r="H15" s="159"/>
+      <c r="I15" s="159"/>
+      <c r="J15" s="159" t="str">
+        <f t="shared" si="0"/>
+        <v>enBaseZonaComun</v>
+      </c>
+      <c r="K15" s="159"/>
+      <c r="L15" s="159" t="s">
+        <v>107</v>
+      </c>
+      <c r="M15" s="159">
+        <v>1</v>
+      </c>
+      <c r="N15" s="159">
+        <v>10</v>
+      </c>
+      <c r="O15" s="159"/>
+      <c r="P15" s="159"/>
+      <c r="Q15" s="160"/>
+      <c r="R15" s="164" t="str">
+        <f t="shared" si="2"/>
+        <v>Atributo que contiene la informacion del enBase del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S15" s="163"/>
+    </row>
+    <row r="16" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="105"/>
+      <c r="B16" s="109" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="32">
+        <v>32</v>
+      </c>
+      <c r="F16" s="32">
+        <v>32</v>
+      </c>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32" t="str">
+        <f>_xlfn.CONCAT(C16,$B$16)</f>
         <v>identificadorConjuntoResidencial</v>
       </c>
-      <c r="K10" s="32" t="s">
+      <c r="K16" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="32" t="s">
+      <c r="L16" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="M10" s="32">
+      <c r="M16" s="32">
         <v>32</v>
       </c>
-      <c r="N10" s="32">
+      <c r="N16" s="32">
         <v>32</v>
       </c>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="56" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B10," en el contexto de ",A10," asociado a la reserva con el identificador' ",J10,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un ConjuntoResidencial en el contexto de  asociado a la reserva con el identificador' identificadorConjuntoResidencial'.</v>
-      </c>
-      <c r="S10" s="125"/>
-    </row>
-    <row r="11" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="108"/>
-      <c r="B11" s="111"/>
-      <c r="C11" s="32" t="s">
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="61" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S16" s="163"/>
+    </row>
+    <row r="17" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="106"/>
+      <c r="B17" s="109"/>
+      <c r="C17" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D17" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E17" s="32">
         <v>1</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F17" s="32">
         <v>50</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32" t="str">
-        <f>_xlfn.CONCAT(C11,$B$10)</f>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32" t="str">
+        <f>_xlfn.CONCAT(C17,$B$16)</f>
         <v>nombreConjuntoResidencial</v>
       </c>
-      <c r="K11" s="32" t="s">
+      <c r="K17" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="32" t="s">
+      <c r="L17" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="32">
+      <c r="M17" s="32">
         <v>1</v>
       </c>
-      <c r="N11" s="32">
+      <c r="N17" s="32">
         <v>50</v>
       </c>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="55" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la información del nombre de un ",B11," en el contexto de ",A11," asociado a la reserva con el identificador' ",J11,"'.")</f>
-        <v>Atributo que contiene la información del nombre de un  en el contexto de  asociado a la reserva con el identificador' nombreConjuntoResidencial'.</v>
-      </c>
-      <c r="S11" s="125"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="61" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S17" s="163"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A5:A11"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="S5:S11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="R7:R8"/>
+  <mergeCells count="11">
+    <mergeCell ref="A5:A17"/>
+    <mergeCell ref="S5:S17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B5:B11"/>
+    <mergeCell ref="B12:B15"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
@@ -4832,6 +5880,10 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D10" location="'Agenda ConjuntosResidenciales-0'!B12" display="UnidadTiempoUso" xr:uid="{7145F6A3-A24A-4F31-B98A-658FB31AEB42}"/>
+    <hyperlink ref="D11" location="'Agenda ConjuntosResidenciales-0'!B16" display="ConjuntoResidencial" xr:uid="{C0CAC5E7-0ED2-485E-BFD1-A6C07FEF9C49}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4839,115 +5891,115 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C088BE7-88A8-46E0-AF18-6F40B3F602F8}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.28515625" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="64" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="13"/>
+    <col min="7" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="96" t="str">
+      <c r="B1" s="94" t="str">
         <f>Contextos!B15</f>
         <v>Reservas</v>
       </c>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="97"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="95"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="98" t="str">
+      <c r="B2" s="96" t="str">
         <f>Contextos!D15</f>
         <v>Contexto cuya intención enfocarse en la gestión del proceso de reservas de los recursos, incluyendo la disponibilidad de los recursos y las reservas que los residentes realizan.</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="99"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="97"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="100" t="str">
+      <c r="B3" s="98" t="str">
         <f>Contextos!A15</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="101"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="102" t="s">
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="99"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="102"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="105" t="s">
+      <c r="D5" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="105"/>
-      <c r="F5" s="106" t="s">
+      <c r="E5" s="103"/>
+      <c r="F5" s="104" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="106"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="104"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="105"/>
+      <c r="C7" s="103"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="106"/>
-    </row>
-    <row r="8" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="104"/>
+    </row>
+    <row r="8" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>25</v>
@@ -4961,15 +6013,15 @@
       </c>
       <c r="E8" s="49" t="str">
         <f t="shared" ref="E8:E9" si="0">_xlfn.CONCAT(A8," de ",B8)</f>
-        <v>Turno de Reserva</v>
+        <v>Agendas de Reserva</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>25</v>
@@ -4983,7 +6035,7 @@
       </c>
       <c r="E9" s="21" t="str">
         <f t="shared" si="0"/>
-        <v>Residente de Reserva</v>
+        <v>Residentes de Reserva</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>78</v>

--- a/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E636CC19-D5C4-402C-B0F8-7C9B6589C008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FFAD58-FB04-4752-8E45-C710A4F23B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="7" activeTab="9" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
+    <workbookView xWindow="21285" yWindow="2625" windowWidth="18345" windowHeight="15345" firstSheet="5" activeTab="5" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="136">
   <si>
     <t>Problema/Dominio:</t>
   </si>
@@ -451,6 +451,9 @@
   </si>
   <si>
     <t>Lógico</t>
+  </si>
+  <si>
+    <t>numeroZonaInmueble</t>
   </si>
 </sst>
 </file>
@@ -1020,39 +1023,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1068,6 +1038,41 @@
       </right>
       <top/>
       <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1077,7 +1082,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1268,6 +1273,51 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1391,55 +1441,106 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1454,134 +1555,23 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1592,7 +1582,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1604,10 +1597,13 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2047,10 +2043,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="65"/>
+      <c r="B1" s="80"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -2177,75 +2173,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="118" t="str">
+      <c r="B1" s="122" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="119"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="123"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="100"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="102"/>
+      <c r="A2" s="115"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="117"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121" t="s">
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="121"/>
-      <c r="R3" s="122" t="s">
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="124" t="s">
+      <c r="S3" s="156" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2301,14 +2297,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="126"/>
-      <c r="S4" s="125"/>
+      <c r="R4" s="161"/>
+      <c r="S4" s="157"/>
     </row>
     <row r="5" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="135" t="s">
+      <c r="A5" s="139" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="137" t="s">
+      <c r="B5" s="141" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -2345,17 +2341,17 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="51"/>
-      <c r="R5" s="154" t="str">
+      <c r="R5" s="69" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificadorConjuntoResidencial del objeto dominio ZonaComun  en el contexto de Agendas.</v>
       </c>
-      <c r="S5" s="129" t="s">
+      <c r="S5" s="158" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="135"/>
-      <c r="B6" s="177"/>
+      <c r="A6" s="139"/>
+      <c r="B6" s="142"/>
       <c r="C6" s="51" t="s">
         <v>119</v>
       </c>
@@ -2390,15 +2386,15 @@
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="154" t="str">
+      <c r="R6" s="69" t="str">
         <f t="shared" ref="R6:R15" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombreConjuntoResidencial del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S6" s="129"/>
+      <c r="S6" s="158"/>
     </row>
     <row r="7" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="135"/>
-      <c r="B7" s="177"/>
+      <c r="A7" s="139"/>
+      <c r="B7" s="142"/>
       <c r="C7" s="51" t="s">
         <v>120</v>
       </c>
@@ -2433,15 +2429,15 @@
       <c r="O7" s="51"/>
       <c r="P7" s="51"/>
       <c r="Q7" s="51"/>
-      <c r="R7" s="154" t="str">
+      <c r="R7" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del identificadorUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S7" s="129"/>
+      <c r="S7" s="158"/>
     </row>
     <row r="8" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="135"/>
-      <c r="B8" s="177"/>
+      <c r="A8" s="139"/>
+      <c r="B8" s="142"/>
       <c r="C8" s="51" t="s">
         <v>121</v>
       </c>
@@ -2476,15 +2472,15 @@
       <c r="O8" s="51"/>
       <c r="P8" s="51"/>
       <c r="Q8" s="51"/>
-      <c r="R8" s="154" t="str">
+      <c r="R8" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del nombreUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S8" s="129"/>
+      <c r="S8" s="158"/>
     </row>
     <row r="9" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="135"/>
-      <c r="B9" s="177"/>
+      <c r="A9" s="139"/>
+      <c r="B9" s="142"/>
       <c r="C9" s="51" t="s">
         <v>122</v>
       </c>
@@ -2519,16 +2515,16 @@
       <c r="O9" s="51"/>
       <c r="P9" s="51"/>
       <c r="Q9" s="51"/>
-      <c r="R9" s="154" t="str">
+      <c r="R9" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del abreviaturaUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S9" s="129"/>
+      <c r="S9" s="158"/>
     </row>
     <row r="10" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="135"/>
-      <c r="B10" s="177"/>
-      <c r="C10" s="166" t="s">
+      <c r="A10" s="139"/>
+      <c r="B10" s="142"/>
+      <c r="C10" s="76" t="s">
         <v>123</v>
       </c>
       <c r="D10" s="51" t="s">
@@ -2562,16 +2558,16 @@
       <c r="O10" s="51"/>
       <c r="P10" s="51"/>
       <c r="Q10" s="51"/>
-      <c r="R10" s="154" t="str">
+      <c r="R10" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del enBaseUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S10" s="129"/>
+      <c r="S10" s="158"/>
     </row>
     <row r="11" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="135"/>
-      <c r="B11" s="177"/>
-      <c r="C11" s="166" t="s">
+      <c r="A11" s="139"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="76" t="s">
         <v>124</v>
       </c>
       <c r="D11" s="51" t="s">
@@ -2605,16 +2601,16 @@
       <c r="O11" s="51"/>
       <c r="P11" s="51"/>
       <c r="Q11" s="51"/>
-      <c r="R11" s="154" t="str">
+      <c r="R11" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del IdentificadorZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S11" s="129"/>
+      <c r="S11" s="158"/>
     </row>
     <row r="12" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="135"/>
-      <c r="B12" s="177"/>
-      <c r="C12" s="166" t="s">
+      <c r="A12" s="139"/>
+      <c r="B12" s="142"/>
+      <c r="C12" s="76" t="s">
         <v>125</v>
       </c>
       <c r="D12" s="51" t="s">
@@ -2648,16 +2644,16 @@
       <c r="O12" s="51"/>
       <c r="P12" s="51"/>
       <c r="Q12" s="51"/>
-      <c r="R12" s="154" t="str">
+      <c r="R12" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del nombreZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S12" s="129"/>
+      <c r="S12" s="158"/>
     </row>
     <row r="13" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="135"/>
-      <c r="B13" s="177"/>
-      <c r="C13" s="166" t="s">
+      <c r="A13" s="139"/>
+      <c r="B13" s="142"/>
+      <c r="C13" s="76" t="s">
         <v>126</v>
       </c>
       <c r="D13" s="51" t="s">
@@ -2691,16 +2687,16 @@
       <c r="O13" s="51"/>
       <c r="P13" s="51"/>
       <c r="Q13" s="51"/>
-      <c r="R13" s="154" t="str">
+      <c r="R13" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del capacidadPersonasZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S13" s="129"/>
+      <c r="S13" s="158"/>
     </row>
     <row r="14" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="135"/>
-      <c r="B14" s="177"/>
-      <c r="C14" s="166" t="s">
+      <c r="A14" s="139"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="76" t="s">
         <v>127</v>
       </c>
       <c r="D14" s="51" t="s">
@@ -2734,16 +2730,16 @@
       <c r="O14" s="51"/>
       <c r="P14" s="51"/>
       <c r="Q14" s="51"/>
-      <c r="R14" s="154" t="str">
+      <c r="R14" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del decripcionZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S14" s="129"/>
+      <c r="S14" s="158"/>
     </row>
     <row r="15" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="135"/>
-      <c r="B15" s="165"/>
-      <c r="C15" s="166" t="s">
+      <c r="A15" s="139"/>
+      <c r="B15" s="143"/>
+      <c r="C15" s="76" t="s">
         <v>128</v>
       </c>
       <c r="D15" s="51" t="s">
@@ -2785,15 +2781,15 @@
       <c r="Q15" s="51">
         <v>3600</v>
       </c>
-      <c r="R15" s="154" t="str">
+      <c r="R15" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del tiempoUsoZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S15" s="129"/>
-    </row>
-    <row r="16" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="135"/>
-      <c r="B16" s="176" t="s">
+      <c r="S15" s="158"/>
+    </row>
+    <row r="16" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="139"/>
+      <c r="B16" s="163" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="50" t="s">
@@ -2834,11 +2830,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Agenda  en el contexto de Agendas.</v>
       </c>
-      <c r="S16" s="129"/>
+      <c r="S16" s="158"/>
     </row>
     <row r="17" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="135"/>
-      <c r="B17" s="176"/>
+      <c r="A17" s="139"/>
+      <c r="B17" s="163"/>
       <c r="C17" s="50" t="s">
         <v>4</v>
       </c>
@@ -2855,7 +2851,7 @@
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
       <c r="J17" s="31" t="str">
-        <f t="shared" ref="J17:J20" si="2">_xlfn.CONCAT(C17,$B$16)</f>
+        <f t="shared" ref="J17:J19" si="2">_xlfn.CONCAT(C17,$B$16)</f>
         <v>NombreAgenda</v>
       </c>
       <c r="K17" s="31" t="s">
@@ -2874,14 +2870,14 @@
       <c r="P17" s="31"/>
       <c r="Q17" s="31"/>
       <c r="R17" s="40" t="str">
-        <f t="shared" ref="R17:R20" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
+        <f t="shared" ref="R17:R19" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S17" s="129"/>
+      <c r="S17" s="158"/>
     </row>
     <row r="18" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="135"/>
-      <c r="B18" s="176"/>
+      <c r="A18" s="139"/>
+      <c r="B18" s="163"/>
       <c r="C18" s="31" t="s">
         <v>90</v>
       </c>
@@ -2912,11 +2908,11 @@
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del fechaHoraInicio del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S18" s="129"/>
+      <c r="S18" s="158"/>
     </row>
     <row r="19" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="135"/>
-      <c r="B19" s="176"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="163"/>
       <c r="C19" s="31" t="s">
         <v>94</v>
       </c>
@@ -2947,15 +2943,15 @@
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del fechaHoraFin del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S19" s="129"/>
+      <c r="S19" s="158"/>
     </row>
     <row r="20" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="135"/>
-      <c r="B20" s="176"/>
+      <c r="A20" s="139"/>
+      <c r="B20" s="163"/>
       <c r="C20" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="167" t="s">
+      <c r="D20" s="77" t="s">
         <v>41</v>
       </c>
       <c r="E20" s="31"/>
@@ -2972,11 +2968,11 @@
       <c r="P20" s="31"/>
       <c r="Q20" s="31"/>
       <c r="R20" s="40"/>
-      <c r="S20" s="129"/>
+      <c r="S20" s="158"/>
     </row>
     <row r="21" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="135"/>
-      <c r="B21" s="134" t="s">
+      <c r="A21" s="139"/>
+      <c r="B21" s="160" t="s">
         <v>65</v>
       </c>
       <c r="C21" s="32" t="s">
@@ -3017,11 +3013,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C21," del objeto dominio ",B21,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Turno  en el contexto de Agendas.</v>
       </c>
-      <c r="S21" s="129"/>
+      <c r="S21" s="158"/>
     </row>
     <row r="22" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="135"/>
-      <c r="B22" s="134"/>
+      <c r="A22" s="139"/>
+      <c r="B22" s="160"/>
       <c r="C22" s="32" t="s">
         <v>129</v>
       </c>
@@ -3057,14 +3053,14 @@
       <c r="P22" s="32"/>
       <c r="Q22" s="32"/>
       <c r="R22" s="41" t="str">
-        <f t="shared" ref="R22:R26" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C22," del objeto dominio ",B22,"  en el contexto de ",$A$5,".")</f>
+        <f t="shared" ref="R22:R25" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C22," del objeto dominio ",B22,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del numeroTurno del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S22" s="129"/>
+      <c r="S22" s="158"/>
     </row>
     <row r="23" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="135"/>
-      <c r="B23" s="134"/>
+      <c r="A23" s="139"/>
+      <c r="B23" s="160"/>
       <c r="C23" s="32" t="s">
         <v>130</v>
       </c>
@@ -3093,11 +3089,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del horaInicio del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S23" s="129"/>
+      <c r="S23" s="158"/>
     </row>
     <row r="24" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="135"/>
-      <c r="B24" s="134"/>
+      <c r="A24" s="139"/>
+      <c r="B24" s="160"/>
       <c r="C24" s="32" t="s">
         <v>132</v>
       </c>
@@ -3126,11 +3122,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del horaFin del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S24" s="129"/>
+      <c r="S24" s="158"/>
     </row>
     <row r="25" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="135"/>
-      <c r="B25" s="134"/>
+      <c r="A25" s="139"/>
+      <c r="B25" s="160"/>
       <c r="C25" s="32" t="s">
         <v>133</v>
       </c>
@@ -3159,15 +3155,15 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del estado del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S25" s="129"/>
+      <c r="S25" s="158"/>
     </row>
     <row r="26" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="136"/>
-      <c r="B26" s="134"/>
+      <c r="A26" s="162"/>
+      <c r="B26" s="160"/>
       <c r="C26" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D26" s="168" t="s">
+      <c r="D26" s="78" t="s">
         <v>64</v>
       </c>
       <c r="E26" s="32"/>
@@ -3184,7 +3180,7 @@
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
       <c r="R26" s="41"/>
-      <c r="S26" s="133"/>
+      <c r="S26" s="159"/>
     </row>
     <row r="27" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3240,75 +3236,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="118" t="str">
+      <c r="B1" s="122" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="119"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="123"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="100"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="102"/>
+      <c r="A2" s="115"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="117"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121" t="s">
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="121"/>
-      <c r="R3" s="122" t="s">
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="124" t="s">
+      <c r="S3" s="156" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3364,14 +3360,14 @@
       <c r="Q4" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="123"/>
-      <c r="S4" s="125"/>
+      <c r="R4" s="155"/>
+      <c r="S4" s="157"/>
     </row>
     <row r="5" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="164" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="138" t="s">
+      <c r="B5" s="172" t="s">
         <v>82</v>
       </c>
       <c r="C5" s="31" t="s">
@@ -3412,14 +3408,14 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del TipoInmueble(Nombre) del objeto dominio Inmueble  en el contexto de Residentes.</v>
       </c>
-      <c r="S5" s="128" t="str">
+      <c r="S5" s="167" t="str">
         <f>B9</f>
         <v>Residente</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="170"/>
-      <c r="B6" s="139"/>
+      <c r="A6" s="165"/>
+      <c r="B6" s="173"/>
       <c r="C6" s="31" t="s">
         <v>112</v>
       </c>
@@ -3458,11 +3454,11 @@
         <f t="shared" ref="R6:R8" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del TipoZonaInmueble(Identificador) del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S6" s="129"/>
+      <c r="S6" s="158"/>
     </row>
     <row r="7" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="170"/>
-      <c r="B7" s="139"/>
+      <c r="A7" s="165"/>
+      <c r="B7" s="173"/>
       <c r="C7" s="31" t="s">
         <v>113</v>
       </c>
@@ -3501,11 +3497,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del TipoZonaInmueble(Nombre) del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S7" s="129"/>
+      <c r="S7" s="158"/>
     </row>
     <row r="8" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="170"/>
-      <c r="B8" s="140"/>
+      <c r="A8" s="165"/>
+      <c r="B8" s="174"/>
       <c r="C8" s="31" t="s">
         <v>114</v>
       </c>
@@ -3552,11 +3548,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del ZonaInmueble(NumeroZonaInmueble) del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S8" s="129"/>
+      <c r="S8" s="158"/>
     </row>
     <row r="9" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="170"/>
-      <c r="B9" s="173" t="s">
+      <c r="A9" s="165"/>
+      <c r="B9" s="169" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="32" t="s">
@@ -3597,11 +3593,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C9," del objeto dominio ",B9,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Residente  en el contexto de Residentes.</v>
       </c>
-      <c r="S9" s="129"/>
+      <c r="S9" s="158"/>
     </row>
     <row r="10" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="170"/>
-      <c r="B10" s="174"/>
+      <c r="A10" s="165"/>
+      <c r="B10" s="170"/>
       <c r="C10" s="32" t="s">
         <v>57</v>
       </c>
@@ -3640,11 +3636,11 @@
         <f t="shared" ref="R10:R11" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S10" s="129"/>
+      <c r="S10" s="158"/>
     </row>
     <row r="11" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="170"/>
-      <c r="B11" s="174"/>
+      <c r="A11" s="165"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="32" t="s">
         <v>117</v>
       </c>
@@ -3683,11 +3679,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del numeroDocumento del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S11" s="129"/>
+      <c r="S11" s="158"/>
     </row>
     <row r="12" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="171"/>
-      <c r="B12" s="175"/>
+      <c r="A12" s="166"/>
+      <c r="B12" s="171"/>
       <c r="C12" s="32" t="s">
         <v>115</v>
       </c>
@@ -3708,7 +3704,7 @@
       <c r="P12" s="32"/>
       <c r="Q12" s="32"/>
       <c r="R12" s="41"/>
-      <c r="S12" s="172"/>
+      <c r="S12" s="168"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3753,29 +3749,29 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="76"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="91"/>
     </row>
     <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="94"/>
     </row>
     <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="82"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="97"/>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -3792,132 +3788,132 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="86" t="s">
+      <c r="B5" s="101" t="s">
         <v>79</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="102" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="85"/>
-      <c r="B6" s="86"/>
+      <c r="A6" s="100"/>
+      <c r="B6" s="101"/>
       <c r="C6" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="87"/>
+      <c r="D6" s="102"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="85"/>
-      <c r="B7" s="86"/>
+      <c r="A7" s="100"/>
+      <c r="B7" s="101"/>
       <c r="C7" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="87"/>
+      <c r="D7" s="102"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="85"/>
-      <c r="B8" s="86"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="101"/>
       <c r="C8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="87"/>
+      <c r="D8" s="102"/>
     </row>
     <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="85"/>
-      <c r="B9" s="86"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="101"/>
       <c r="C9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="87"/>
+      <c r="D9" s="102"/>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="99" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="83" t="s">
+      <c r="D10" s="98" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83"/>
-      <c r="B11" s="84"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
       <c r="C11" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="83"/>
+      <c r="D11" s="98"/>
     </row>
     <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="91" t="s">
+      <c r="A12" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="103" t="s">
         <v>83</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="91" t="s">
+      <c r="D12" s="106" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="89"/>
+      <c r="A13" s="107"/>
+      <c r="B13" s="104"/>
       <c r="C13" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="92"/>
+      <c r="D13" s="107"/>
     </row>
     <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="93"/>
-      <c r="B14" s="90"/>
+      <c r="A14" s="108"/>
+      <c r="B14" s="105"/>
       <c r="C14" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="93"/>
+      <c r="D14" s="108"/>
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="84" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="87" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="67"/>
-      <c r="B16" s="70"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="85"/>
       <c r="C16" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="73"/>
+      <c r="D16" s="88"/>
     </row>
     <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="68"/>
-      <c r="B17" s="71"/>
+      <c r="A17" s="83"/>
+      <c r="B17" s="86"/>
       <c r="C17" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="74"/>
+      <c r="D17" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3989,50 +3985,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="94" t="str">
+      <c r="B1" s="109" t="str">
         <f>Contextos!B5</f>
         <v xml:space="preserve"> Conjuntos residenciales</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="110"/>
     </row>
     <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="96" t="str">
+      <c r="B2" s="111" t="str">
         <f>Contextos!D5</f>
         <v>Contexto cuya motivación es Gestionar la estructura física y los recursos disponibles en cada conjunto residencial. Aquí se manejan los datos sobre qué conjuntos existen, dónde están ubicados, qué recursos ofrecen según una Agenda con respectivos turnos para cada zona.</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="98" t="str">
+      <c r="B3" s="113" t="str">
         <f>Contextos!A5</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="99"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="114"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="117"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -4041,14 +4037,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="103" t="s">
+      <c r="C5" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="D5" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104" t="s">
+      <c r="E5" s="118"/>
+      <c r="F5" s="119" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4059,10 +4055,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="104"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="119"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
@@ -4071,14 +4067,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="103"/>
+      <c r="C7" s="118"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="104"/>
+      <c r="F7" s="119"/>
     </row>
     <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
@@ -4212,50 +4208,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="94" t="str">
+      <c r="B1" s="109" t="str">
         <f>Contextos!B10</f>
         <v>Residentes</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="110"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="96" t="str">
+      <c r="B2" s="111" t="str">
         <f>Contextos!D10</f>
         <v>Contexto cuya motivación es encargarce de manejar la información de los residentes, incluidas sus identificaciones, contacto, y la relación entre el residente y su residencia dentro del conjunto.</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="98" t="str">
+      <c r="B3" s="113" t="str">
         <f>Contextos!A10</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="99"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="114"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="117"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -4264,14 +4260,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="103" t="s">
+      <c r="C5" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="D5" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104" t="s">
+      <c r="E5" s="118"/>
+      <c r="F5" s="119" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4282,10 +4278,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="104"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="119"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
@@ -4294,14 +4290,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="103"/>
+      <c r="C7" s="118"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="104"/>
+      <c r="F7" s="119"/>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
@@ -4356,7 +4352,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59635CF3-0DE6-45E6-A198-1E7042F5E8F9}">
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" style="13" customWidth="1"/>
@@ -4385,75 +4381,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="118" t="str">
+      <c r="B1" s="122" t="str">
         <f>Residentes!D8</f>
         <v>Residente ConjutosResidenciales-0001</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="119"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="123"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="151"/>
-      <c r="S2" s="102"/>
+      <c r="A2" s="115"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="117"/>
     </row>
     <row r="3" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121" t="s">
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="147"/>
-      <c r="R3" s="152" t="s">
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="128" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="149" t="s">
+      <c r="S3" s="130" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4506,94 +4502,112 @@
       <c r="P4" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="148" t="s">
+      <c r="Q4" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="153"/>
-      <c r="S4" s="150"/>
+      <c r="R4" s="129"/>
+      <c r="S4" s="131"/>
     </row>
     <row r="5" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="105" t="s">
+      <c r="A5" s="139" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="141" t="s">
         <v>82</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="E5" s="51">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F5" s="51">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G5" s="51"/>
       <c r="H5" s="51"/>
       <c r="I5" s="51"/>
       <c r="J5" s="51" t="str">
         <f>_xlfn.CONCAT(C5,$B$5)</f>
-        <v>numeroViviendaInmueble</v>
+        <v>identificadorInmueble</v>
       </c>
       <c r="K5" s="51" t="s">
         <v>59</v>
       </c>
       <c r="L5" s="51" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="M5" s="51">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N5" s="51">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="52"/>
-      <c r="R5" s="154" t="str">
+      <c r="R5" s="69" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del numeroVivienda del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S5" s="107" t="s">
+        <v>Atributo que contiene la informacion del identificador del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S5" s="120" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="105"/>
-      <c r="B6" s="111"/>
-      <c r="C6" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="155" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
+    <row r="6" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="139"/>
+      <c r="B6" s="142"/>
+      <c r="C6" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="51">
+        <v>1</v>
+      </c>
+      <c r="F6" s="51">
+        <v>50</v>
+      </c>
       <c r="G6" s="51"/>
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
+      <c r="J6" s="51" t="str">
+        <f>_xlfn.CONCAT(C6,$B$5)</f>
+        <v>numeroViviendaInmueble</v>
+      </c>
+      <c r="K6" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="M6" s="51">
+        <v>1</v>
+      </c>
+      <c r="N6" s="51">
+        <v>50</v>
+      </c>
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="52"/>
-      <c r="R6" s="154"/>
-      <c r="S6" s="107"/>
+      <c r="R6" s="69" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B5,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del numeroVivienda del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S6" s="120"/>
     </row>
     <row r="7" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="105"/>
-      <c r="B7" s="112"/>
+      <c r="A7" s="139"/>
+      <c r="B7" s="142"/>
       <c r="C7" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="155" t="s">
-        <v>98</v>
+        <v>101</v>
+      </c>
+      <c r="D7" s="70" t="s">
+        <v>81</v>
       </c>
       <c r="E7" s="51"/>
       <c r="F7" s="51"/>
@@ -4608,395 +4622,468 @@
       <c r="O7" s="51"/>
       <c r="P7" s="51"/>
       <c r="Q7" s="52"/>
-      <c r="R7" s="154"/>
-      <c r="S7" s="107"/>
-    </row>
-    <row r="8" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="105"/>
-      <c r="B8" s="113" t="s">
+      <c r="R7" s="69"/>
+      <c r="S7" s="120"/>
+    </row>
+    <row r="8" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="139"/>
+      <c r="B8" s="143"/>
+      <c r="C8" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="52"/>
+      <c r="R8" s="69"/>
+      <c r="S8" s="120"/>
+    </row>
+    <row r="9" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="139"/>
+      <c r="B9" s="133" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D9" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="31">
-        <v>32</v>
-      </c>
-      <c r="F8" s="31">
-        <v>32</v>
-      </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31" t="str">
-        <f t="shared" ref="J8:J14" si="0">_xlfn.CONCAT(C8,$B$8)</f>
-        <v>identificadorTipoInmueble</v>
-      </c>
-      <c r="K8" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="31">
-        <v>32</v>
-      </c>
-      <c r="N8" s="31">
-        <v>32</v>
-      </c>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="53"/>
-      <c r="R8" s="63" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C8," del objeto dominio ",B8,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S8" s="107"/>
-    </row>
-    <row r="9" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="105"/>
-      <c r="B9" s="114"/>
-      <c r="C9" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>58</v>
-      </c>
       <c r="E9" s="31">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F9" s="31">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G9" s="31"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="J9" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>nombreTipoInmueble</v>
+        <f>_xlfn.CONCAT(C9,$B$9)</f>
+        <v>identificadorTipoInmueble</v>
       </c>
       <c r="K9" s="31" t="s">
         <v>59</v>
       </c>
       <c r="L9" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M9" s="31">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N9" s="31">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O9" s="31"/>
       <c r="P9" s="31"/>
       <c r="Q9" s="53"/>
-      <c r="R9" s="59" t="str">
+      <c r="R9" s="63" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C9," del objeto dominio ",B9,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S9" s="120"/>
+    </row>
+    <row r="10" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="139"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="31">
+        <v>1</v>
+      </c>
+      <c r="F10" s="31">
+        <v>50</v>
+      </c>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31" t="str">
+        <f t="shared" ref="J9:J16" si="0">_xlfn.CONCAT(C10,$B$9)</f>
+        <v>nombreTipoInmueble</v>
+      </c>
+      <c r="K10" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="31">
+        <v>1</v>
+      </c>
+      <c r="N10" s="31">
+        <v>50</v>
+      </c>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="59" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S9" s="107"/>
-    </row>
-    <row r="10" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="105"/>
-      <c r="B10" s="115" t="s">
+      <c r="S10" s="120"/>
+    </row>
+    <row r="11" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="139"/>
+      <c r="B11" s="136" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C11" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D11" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="56">
-        <v>32</v>
-      </c>
-      <c r="F10" s="56">
-        <v>32</v>
-      </c>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56" t="str">
-        <f t="shared" si="0"/>
-        <v>identificadorTipoInmueble</v>
-      </c>
-      <c r="K10" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="M10" s="56">
-        <v>32</v>
-      </c>
-      <c r="N10" s="56">
-        <v>32</v>
-      </c>
-      <c r="O10" s="56"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="57"/>
-      <c r="R10" s="60" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",A3,".")</f>
-        <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Caracterización Origen.</v>
-      </c>
-      <c r="S10" s="107"/>
-    </row>
-    <row r="11" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="105"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="156" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
+      <c r="E11" s="56">
+        <v>32</v>
+      </c>
+      <c r="F11" s="56">
+        <v>32</v>
+      </c>
       <c r="G11" s="56"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="56"/>
-      <c r="N11" s="56"/>
+      <c r="J11" s="56" t="str">
+        <f>_xlfn.CONCAT(C11,$B$11)</f>
+        <v>identificadorZonaInmueble</v>
+      </c>
+      <c r="K11" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="56">
+        <v>32</v>
+      </c>
+      <c r="N11" s="56">
+        <v>32</v>
+      </c>
       <c r="O11" s="56"/>
       <c r="P11" s="56"/>
       <c r="Q11" s="57"/>
       <c r="R11" s="60" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C11," del objeto dominio ",B11,"  en el contexto de ",A3,".")</f>
-        <v>Atributo que contiene la informacion del tipoZonaInmueble del objeto dominio   en el contexto de Caracterización Origen.</v>
-      </c>
-      <c r="S11" s="107"/>
-    </row>
-    <row r="12" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="105"/>
-      <c r="B12" s="117"/>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Caracterización Origen.</v>
+      </c>
+      <c r="S11" s="120"/>
+    </row>
+    <row r="12" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="139"/>
+      <c r="B12" s="137"/>
       <c r="C12" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="56">
+        <v>1</v>
+      </c>
+      <c r="F12" s="56">
+        <v>20</v>
+      </c>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56">
+        <v>1</v>
+      </c>
+      <c r="I12" s="56">
+        <v>200</v>
+      </c>
+      <c r="J12" s="56" t="str">
+        <f>_xlfn.CONCAT(C12,$B$11)</f>
+        <v>numeroZonaInmuebleZonaInmueble</v>
+      </c>
+      <c r="K12" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="M12" s="56">
+        <v>1</v>
+      </c>
+      <c r="N12" s="56">
+        <v>20</v>
+      </c>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="57">
+        <v>200</v>
+      </c>
+      <c r="R12" s="60" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C12," del objeto dominio ",B12,"  en el contexto de ",A4,".")</f>
+        <v>Atributo que contiene la informacion del numeroZonaInmueble del objeto dominio   en el contexto de Contexto.</v>
+      </c>
+      <c r="S12" s="120"/>
+    </row>
+    <row r="13" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="139"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="120"/>
+    </row>
+    <row r="14" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="139"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="156" t="s">
+      <c r="D14" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="56"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="56"/>
-      <c r="P12" s="56"/>
-      <c r="Q12" s="57"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="107"/>
-    </row>
-    <row r="13" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="105"/>
-      <c r="B13" s="141" t="s">
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+      <c r="N14" s="56"/>
+      <c r="O14" s="56"/>
+      <c r="P14" s="56"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="120"/>
+    </row>
+    <row r="15" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="139"/>
+      <c r="B15" s="134" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C15" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="143" t="s">
+      <c r="D15" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="143">
-        <v>32</v>
-      </c>
-      <c r="F13" s="143">
-        <v>32</v>
-      </c>
-      <c r="G13" s="143"/>
-      <c r="H13" s="143"/>
-      <c r="I13" s="143"/>
-      <c r="J13" s="143" t="str">
-        <f t="shared" si="0"/>
-        <v>identificadorTipoInmueble</v>
-      </c>
-      <c r="K13" s="143" t="s">
+      <c r="E15" s="65">
+        <v>32</v>
+      </c>
+      <c r="F15" s="65">
+        <v>32</v>
+      </c>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65" t="str">
+        <f>_xlfn.CONCAT(C15,$B$15)</f>
+        <v>identificadorTipoZonaInmueble</v>
+      </c>
+      <c r="K15" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="143" t="s">
+      <c r="L15" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="M13" s="143">
-        <v>32</v>
-      </c>
-      <c r="N13" s="143">
-        <v>32</v>
-      </c>
-      <c r="O13" s="143"/>
-      <c r="P13" s="143"/>
-      <c r="Q13" s="144"/>
-      <c r="R13" s="145" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C13," del objeto dominio ",B13,"  en el contexto de ",A5,".")</f>
+      <c r="M15" s="65">
+        <v>32</v>
+      </c>
+      <c r="N15" s="65">
+        <v>32</v>
+      </c>
+      <c r="O15" s="65"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="67" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C15," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio TipoZonaInmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S13" s="107"/>
-    </row>
-    <row r="14" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="105"/>
-      <c r="B14" s="146"/>
-      <c r="C14" s="142" t="s">
+      <c r="S15" s="120"/>
+    </row>
+    <row r="16" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="139"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="143" t="s">
+      <c r="D16" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="143">
+      <c r="E16" s="65">
         <v>1</v>
       </c>
-      <c r="F14" s="143">
+      <c r="F16" s="65">
         <v>50</v>
       </c>
-      <c r="G14" s="143"/>
-      <c r="H14" s="143"/>
-      <c r="I14" s="143"/>
-      <c r="J14" s="143" t="str">
-        <f t="shared" si="0"/>
-        <v>nombreTipoInmueble</v>
-      </c>
-      <c r="K14" s="143" t="s">
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65" t="str">
+        <f>_xlfn.CONCAT(C16,$B$15)</f>
+        <v>nombreTipoZonaInmueble</v>
+      </c>
+      <c r="K16" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="L14" s="143" t="s">
+      <c r="L16" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="143">
+      <c r="M16" s="65">
         <v>1</v>
       </c>
-      <c r="N14" s="143">
+      <c r="N16" s="65">
         <v>50</v>
       </c>
-      <c r="O14" s="143"/>
-      <c r="P14" s="143"/>
-      <c r="Q14" s="144"/>
-      <c r="R14" s="145" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C14," del objeto dominio ",B14,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S14" s="107"/>
-    </row>
-    <row r="15" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="105"/>
-      <c r="B15" s="109" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="32">
-        <v>32</v>
-      </c>
-      <c r="F15" s="32">
-        <v>32</v>
-      </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32" t="str">
-        <f>_xlfn.CONCAT(C8,$B$15)</f>
-        <v>identificadorConjuntoResidencial</v>
-      </c>
-      <c r="K15" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="M15" s="32">
-        <v>32</v>
-      </c>
-      <c r="N15" s="32">
-        <v>32</v>
-      </c>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="61" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C15," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
-        <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S15" s="107"/>
-    </row>
-    <row r="16" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="106"/>
-      <c r="B16" s="109"/>
-      <c r="C16" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="32">
-        <v>1</v>
-      </c>
-      <c r="F16" s="32">
-        <v>50</v>
-      </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32" t="str">
-        <f>_xlfn.CONCAT(C9,$B$15)</f>
-        <v>nombreConjuntoResidencial</v>
-      </c>
-      <c r="K16" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="M16" s="32">
-        <v>1</v>
-      </c>
-      <c r="N16" s="32">
-        <v>50</v>
-      </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="61" t="str">
+      <c r="O16" s="65"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="67" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S16" s="108"/>
-    </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23" s="157"/>
+      <c r="S16" s="120"/>
+    </row>
+    <row r="17" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="139"/>
+      <c r="B17" s="132" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="32">
+        <v>32</v>
+      </c>
+      <c r="F17" s="32">
+        <v>32</v>
+      </c>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32" t="str">
+        <f>_xlfn.CONCAT(C9,$B$17)</f>
+        <v>identificadorConjuntoResidencial</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="32">
+        <v>32</v>
+      </c>
+      <c r="N17" s="32">
+        <v>32</v>
+      </c>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="61" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S17" s="120"/>
+    </row>
+    <row r="18" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="140"/>
+      <c r="B18" s="132"/>
+      <c r="C18" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="32">
+        <v>1</v>
+      </c>
+      <c r="F18" s="32">
+        <v>50</v>
+      </c>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32" t="str">
+        <f>_xlfn.CONCAT(C10,$B$17)</f>
+        <v>nombreConjuntoResidencial</v>
+      </c>
+      <c r="K18" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="32">
+        <v>1</v>
+      </c>
+      <c r="N18" s="32">
+        <v>50</v>
+      </c>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="61" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C18," del objeto dominio ",B18,"  en el contexto de ",A5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S18" s="121"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E25" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="S5:S18"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
-    <mergeCell ref="A5:A16"/>
-    <mergeCell ref="S5:S16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B9:B10"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="A5:A18"/>
+    <mergeCell ref="B5:B8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D7" location="'Residente ConjutosResidenciales'!B8" display="TipoInmueble" xr:uid="{7D0F26B2-16BB-4D32-9316-813C92F956E5}"/>
-    <hyperlink ref="D11" location="'Conjuntos Residenciales'!B13" display="TipoZonaInmueble" xr:uid="{34181B3B-B9AE-4560-8F56-BDA0D6B05CD0}"/>
-    <hyperlink ref="D12" location="'Conjuntos Residenciales'!B16" display="ConjuntoResidencial" xr:uid="{A2395E41-D8AC-474A-BE9C-32FCADDD0F2C}"/>
-    <hyperlink ref="D6" location="'Conjuntos Residenciales'!B10" display="ZonaInmueble" xr:uid="{E001D96D-791E-43A6-B8BA-893283B14284}"/>
+    <hyperlink ref="D8" location="'Residente ConjutosResidenciales'!B8" display="TipoInmueble" xr:uid="{7D0F26B2-16BB-4D32-9316-813C92F956E5}"/>
+    <hyperlink ref="D13" location="'Conjuntos Residenciales'!B13" display="TipoZonaInmueble" xr:uid="{34181B3B-B9AE-4560-8F56-BDA0D6B05CD0}"/>
+    <hyperlink ref="D14" location="'Conjuntos Residenciales'!B16" display="ConjuntoResidencial" xr:uid="{A2395E41-D8AC-474A-BE9C-32FCADDD0F2C}"/>
+    <hyperlink ref="D7" location="'Conjuntos Residenciales'!B10" display="ZonaInmueble" xr:uid="{E001D96D-791E-43A6-B8BA-893283B14284}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5019,50 +5106,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="94" t="str">
+      <c r="B1" s="109" t="str">
         <f>Contextos!B12</f>
         <v>Agendas</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="110"/>
     </row>
     <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="96" t="str">
+      <c r="B2" s="111" t="str">
         <f>Contextos!D12</f>
         <v>Contexto cuya motivación es la de gestionar la estructura de la agenda que va a tener una zona común durante un un tiempo estimado y sus diferentes turnos.</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="98" t="str">
+      <c r="B3" s="113" t="str">
         <f>Contextos!A12</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="99"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="114"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="117"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -5071,14 +5158,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="103" t="s">
+      <c r="C5" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="D5" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104" t="s">
+      <c r="E5" s="118"/>
+      <c r="F5" s="119" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5089,10 +5176,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="104"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="119"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
@@ -5101,14 +5188,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="103"/>
+      <c r="C7" s="118"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="104"/>
+      <c r="F7" s="119"/>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
@@ -5214,75 +5301,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="118" t="str">
+      <c r="B1" s="122" t="str">
         <f>Agendas!D8</f>
         <v>Agenda ConjuntosResidenciales-0001</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="119"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="123"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="100"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="102"/>
+      <c r="A2" s="115"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="117"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121" t="s">
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="121"/>
-      <c r="R3" s="122" t="s">
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="124" t="s">
+      <c r="S3" s="156" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5338,14 +5425,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="123"/>
-      <c r="S4" s="125"/>
+      <c r="R4" s="155"/>
+      <c r="S4" s="157"/>
     </row>
     <row r="5" spans="1:19" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="144" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="130" t="s">
+      <c r="B5" s="148" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -5382,17 +5469,17 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="52"/>
-      <c r="R5" s="154" t="str">
+      <c r="R5" s="69" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaComun  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S5" s="163" t="s">
+      <c r="S5" s="147" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="105"/>
-      <c r="B6" s="131"/>
+      <c r="A6" s="145"/>
+      <c r="B6" s="149"/>
       <c r="C6" s="51" t="s">
         <v>4</v>
       </c>
@@ -5427,15 +5514,15 @@
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="52"/>
-      <c r="R6" s="154" t="str">
+      <c r="R6" s="69" t="str">
         <f t="shared" ref="R6:R9" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S6" s="163"/>
+      <c r="S6" s="147"/>
     </row>
     <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="105"/>
-      <c r="B7" s="131"/>
+      <c r="A7" s="145"/>
+      <c r="B7" s="149"/>
       <c r="C7" s="51" t="s">
         <v>95</v>
       </c>
@@ -5470,15 +5557,15 @@
       <c r="O7" s="51"/>
       <c r="P7" s="51"/>
       <c r="Q7" s="52"/>
-      <c r="R7" s="154" t="str">
+      <c r="R7" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del capacidadPersonas del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S7" s="163"/>
+      <c r="S7" s="147"/>
     </row>
     <row r="8" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="105"/>
-      <c r="B8" s="131"/>
+      <c r="A8" s="145"/>
+      <c r="B8" s="149"/>
       <c r="C8" s="51" t="s">
         <v>108</v>
       </c>
@@ -5513,15 +5600,15 @@
       <c r="O8" s="51"/>
       <c r="P8" s="51"/>
       <c r="Q8" s="52"/>
-      <c r="R8" s="154" t="str">
+      <c r="R8" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del descripcion del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S8" s="163"/>
+      <c r="S8" s="147"/>
     </row>
     <row r="9" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="105"/>
-      <c r="B9" s="131"/>
+      <c r="A9" s="145"/>
+      <c r="B9" s="149"/>
       <c r="C9" s="51" t="s">
         <v>96</v>
       </c>
@@ -5556,19 +5643,19 @@
       <c r="O9" s="51"/>
       <c r="P9" s="51"/>
       <c r="Q9" s="52"/>
-      <c r="R9" s="154" t="str">
+      <c r="R9" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del tiempoUso del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S9" s="163"/>
+      <c r="S9" s="147"/>
     </row>
     <row r="10" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="105"/>
-      <c r="B10" s="131"/>
+      <c r="A10" s="145"/>
+      <c r="B10" s="149"/>
       <c r="C10" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="155" t="s">
+      <c r="D10" s="70" t="s">
         <v>104</v>
       </c>
       <c r="E10" s="51"/>
@@ -5584,16 +5671,16 @@
       <c r="O10" s="51"/>
       <c r="P10" s="51"/>
       <c r="Q10" s="52"/>
-      <c r="R10" s="154"/>
-      <c r="S10" s="163"/>
+      <c r="R10" s="69"/>
+      <c r="S10" s="147"/>
     </row>
     <row r="11" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="105"/>
-      <c r="B11" s="132"/>
+      <c r="A11" s="145"/>
+      <c r="B11" s="150"/>
       <c r="C11" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="155" t="s">
+      <c r="D11" s="70" t="s">
         <v>61</v>
       </c>
       <c r="E11" s="51"/>
@@ -5609,178 +5696,178 @@
       <c r="O11" s="51"/>
       <c r="P11" s="51"/>
       <c r="Q11" s="52"/>
-      <c r="R11" s="154"/>
-      <c r="S11" s="163"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="147"/>
     </row>
     <row r="12" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="105"/>
-      <c r="B12" s="158" t="s">
+      <c r="A12" s="145"/>
+      <c r="B12" s="151" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="159" t="s">
+      <c r="C12" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="159" t="s">
+      <c r="D12" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="159">
-        <v>32</v>
-      </c>
-      <c r="F12" s="159">
-        <v>32</v>
-      </c>
-      <c r="G12" s="159"/>
-      <c r="H12" s="159"/>
-      <c r="I12" s="159"/>
-      <c r="J12" s="159" t="str">
+      <c r="E12" s="73">
+        <v>32</v>
+      </c>
+      <c r="F12" s="73">
+        <v>32</v>
+      </c>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73" t="str">
         <f t="shared" si="0"/>
         <v>identificadorZonaComun</v>
       </c>
-      <c r="K12" s="159"/>
-      <c r="L12" s="159" t="s">
+      <c r="K12" s="73"/>
+      <c r="L12" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="M12" s="159">
-        <v>32</v>
-      </c>
-      <c r="N12" s="159">
-        <v>32</v>
-      </c>
-      <c r="O12" s="159"/>
-      <c r="P12" s="159"/>
-      <c r="Q12" s="160"/>
-      <c r="R12" s="164" t="str">
+      <c r="M12" s="73">
+        <v>32</v>
+      </c>
+      <c r="N12" s="73">
+        <v>32</v>
+      </c>
+      <c r="O12" s="73"/>
+      <c r="P12" s="73"/>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="75" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C12," del objeto dominio ",B12,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio UnidadTiempoUso  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S12" s="163"/>
+      <c r="S12" s="147"/>
     </row>
     <row r="13" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="105"/>
-      <c r="B13" s="161"/>
-      <c r="C13" s="159" t="s">
+      <c r="A13" s="145"/>
+      <c r="B13" s="152"/>
+      <c r="C13" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="159" t="s">
+      <c r="D13" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="159">
+      <c r="E13" s="73">
         <v>3</v>
       </c>
-      <c r="F13" s="159">
+      <c r="F13" s="73">
         <v>50</v>
       </c>
-      <c r="G13" s="159"/>
-      <c r="H13" s="159"/>
-      <c r="I13" s="159"/>
-      <c r="J13" s="159" t="str">
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73" t="str">
         <f t="shared" si="0"/>
         <v>nombreZonaComun</v>
       </c>
-      <c r="K13" s="159"/>
-      <c r="L13" s="159" t="s">
+      <c r="K13" s="73"/>
+      <c r="L13" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="M13" s="159">
+      <c r="M13" s="73">
         <v>3</v>
       </c>
-      <c r="N13" s="159">
+      <c r="N13" s="73">
         <v>50</v>
       </c>
-      <c r="O13" s="159"/>
-      <c r="P13" s="159"/>
-      <c r="Q13" s="160"/>
-      <c r="R13" s="164" t="str">
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="75" t="str">
         <f t="shared" ref="R13:R15" si="2">_xlfn.CONCAT("Atributo que contiene la informacion del ",C13," del objeto dominio ",B13,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S13" s="163"/>
+      <c r="S13" s="147"/>
     </row>
     <row r="14" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="105"/>
-      <c r="B14" s="161"/>
-      <c r="C14" s="159" t="s">
+      <c r="A14" s="145"/>
+      <c r="B14" s="152"/>
+      <c r="C14" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="159" t="s">
+      <c r="D14" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="159">
+      <c r="E14" s="73">
         <v>1</v>
       </c>
-      <c r="F14" s="159">
+      <c r="F14" s="73">
         <v>6</v>
       </c>
-      <c r="G14" s="159"/>
-      <c r="H14" s="159"/>
-      <c r="I14" s="159"/>
-      <c r="J14" s="159" t="str">
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73" t="str">
         <f t="shared" si="0"/>
         <v>abreviaturaZonaComun</v>
       </c>
-      <c r="K14" s="159"/>
-      <c r="L14" s="159" t="s">
+      <c r="K14" s="73"/>
+      <c r="L14" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="73">
         <v>1</v>
       </c>
-      <c r="N14" s="159">
+      <c r="N14" s="73">
         <v>6</v>
       </c>
-      <c r="O14" s="159"/>
-      <c r="P14" s="159"/>
-      <c r="Q14" s="160"/>
-      <c r="R14" s="164" t="str">
+      <c r="O14" s="73"/>
+      <c r="P14" s="73"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="75" t="str">
         <f t="shared" si="2"/>
         <v>Atributo que contiene la informacion del abreviatura del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S14" s="163"/>
+      <c r="S14" s="147"/>
     </row>
     <row r="15" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="105"/>
-      <c r="B15" s="162"/>
-      <c r="C15" s="159" t="s">
+      <c r="A15" s="145"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="159" t="s">
+      <c r="D15" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="159">
+      <c r="E15" s="73">
         <v>1</v>
       </c>
-      <c r="F15" s="159">
+      <c r="F15" s="73">
         <v>10</v>
       </c>
-      <c r="G15" s="159"/>
-      <c r="H15" s="159"/>
-      <c r="I15" s="159"/>
-      <c r="J15" s="159" t="str">
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73" t="str">
         <f t="shared" si="0"/>
         <v>enBaseZonaComun</v>
       </c>
-      <c r="K15" s="159"/>
-      <c r="L15" s="159" t="s">
+      <c r="K15" s="73"/>
+      <c r="L15" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="M15" s="159">
+      <c r="M15" s="73">
         <v>1</v>
       </c>
-      <c r="N15" s="159">
+      <c r="N15" s="73">
         <v>10</v>
       </c>
-      <c r="O15" s="159"/>
-      <c r="P15" s="159"/>
-      <c r="Q15" s="160"/>
-      <c r="R15" s="164" t="str">
+      <c r="O15" s="73"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="75" t="str">
         <f t="shared" si="2"/>
         <v>Atributo que contiene la informacion del enBase del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S15" s="163"/>
+      <c r="S15" s="147"/>
     </row>
     <row r="16" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="105"/>
-      <c r="B16" s="109" t="s">
+      <c r="A16" s="145"/>
+      <c r="B16" s="132" t="s">
         <v>61</v>
       </c>
       <c r="C16" s="32" t="s">
@@ -5821,11 +5908,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S16" s="163"/>
+      <c r="S16" s="147"/>
     </row>
     <row r="17" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="106"/>
-      <c r="B17" s="109"/>
+      <c r="A17" s="146"/>
+      <c r="B17" s="132"/>
       <c r="C17" s="32" t="s">
         <v>57</v>
       </c>
@@ -5864,21 +5951,21 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S17" s="163"/>
+      <c r="S17" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A5:A17"/>
-    <mergeCell ref="S5:S17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B5:B11"/>
-    <mergeCell ref="B12:B15"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
+    <mergeCell ref="A5:A17"/>
+    <mergeCell ref="S5:S17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B5:B11"/>
+    <mergeCell ref="B12:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D10" location="'Agenda ConjuntosResidenciales-0'!B12" display="UnidadTiempoUso" xr:uid="{7145F6A3-A24A-4F31-B98A-658FB31AEB42}"/>
@@ -5906,50 +5993,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="94" t="str">
+      <c r="B1" s="109" t="str">
         <f>Contextos!B15</f>
         <v>Reservas</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="110"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="96" t="str">
+      <c r="B2" s="111" t="str">
         <f>Contextos!D15</f>
         <v>Contexto cuya intención enfocarse en la gestión del proceso de reservas de los recursos, incluyendo la disponibilidad de los recursos y las reservas que los residentes realizan.</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="98" t="str">
+      <c r="B3" s="113" t="str">
         <f>Contextos!A15</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="99"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="114"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="117"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -5958,14 +6045,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="103" t="s">
+      <c r="C5" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="D5" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="104" t="s">
+      <c r="E5" s="118"/>
+      <c r="F5" s="119" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5976,10 +6063,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="104"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="119"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
@@ -5988,14 +6075,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="103"/>
+      <c r="C7" s="118"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="104"/>
+      <c r="F7" s="119"/>
     </row>
     <row r="8" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">

--- a/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FFAD58-FB04-4752-8E45-C710A4F23B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F790329D-8B2D-4316-A77F-82627FBE3309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21285" yWindow="2625" windowWidth="18345" windowHeight="15345" firstSheet="5" activeTab="5" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
+    <workbookView xWindow="1050" yWindow="2970" windowWidth="17340" windowHeight="15345" firstSheet="6" activeTab="7" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="137">
   <si>
     <t>Problema/Dominio:</t>
   </si>
@@ -454,6 +454,9 @@
   </si>
   <si>
     <t>numeroZonaInmueble</t>
+  </si>
+  <si>
+    <t>normas</t>
   </si>
 </sst>
 </file>
@@ -1513,6 +1516,18 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1541,18 +1556,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2238,10 +2241,10 @@
       <c r="O3" s="126"/>
       <c r="P3" s="126"/>
       <c r="Q3" s="126"/>
-      <c r="R3" s="154" t="s">
+      <c r="R3" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="156" t="s">
+      <c r="S3" s="146" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2298,7 +2301,7 @@
         <v>52</v>
       </c>
       <c r="R4" s="161"/>
-      <c r="S4" s="157"/>
+      <c r="S4" s="147"/>
     </row>
     <row r="5" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="139" t="s">
@@ -3301,10 +3304,10 @@
       <c r="O3" s="126"/>
       <c r="P3" s="126"/>
       <c r="Q3" s="126"/>
-      <c r="R3" s="154" t="s">
+      <c r="R3" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="156" t="s">
+      <c r="S3" s="146" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3360,8 +3363,8 @@
       <c r="Q4" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="155"/>
-      <c r="S4" s="157"/>
+      <c r="R4" s="145"/>
+      <c r="S4" s="147"/>
     </row>
     <row r="5" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="164" t="s">
@@ -4714,7 +4717,7 @@
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="J10" s="31" t="str">
-        <f t="shared" ref="J9:J16" si="0">_xlfn.CONCAT(C10,$B$9)</f>
+        <f t="shared" ref="J10" si="0">_xlfn.CONCAT(C10,$B$9)</f>
         <v>nombreTipoInmueble</v>
       </c>
       <c r="K10" s="31" t="s">
@@ -5272,7 +5275,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{285DCF13-A122-49FD-BB4E-83BC928CCAC1}">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="13" customWidth="1"/>
@@ -5366,10 +5369,10 @@
       <c r="O3" s="126"/>
       <c r="P3" s="126"/>
       <c r="Q3" s="126"/>
-      <c r="R3" s="154" t="s">
+      <c r="R3" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="156" t="s">
+      <c r="S3" s="146" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5425,14 +5428,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="155"/>
-      <c r="S4" s="157"/>
+      <c r="R4" s="145"/>
+      <c r="S4" s="147"/>
     </row>
     <row r="5" spans="1:19" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="148" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="148" t="s">
+      <c r="B5" s="152" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -5473,13 +5476,13 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaComun  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S5" s="147" t="s">
+      <c r="S5" s="151" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="145"/>
-      <c r="B6" s="149"/>
+      <c r="A6" s="149"/>
+      <c r="B6" s="153"/>
       <c r="C6" s="51" t="s">
         <v>4</v>
       </c>
@@ -5496,7 +5499,7 @@
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
       <c r="J6" s="51" t="str">
-        <f t="shared" ref="J6:J15" si="0">_xlfn.CONCAT(C6,$B$5)</f>
+        <f t="shared" ref="J6:J16" si="0">_xlfn.CONCAT(C6,$B$5)</f>
         <v>NombreZonaComun</v>
       </c>
       <c r="K6" s="51" t="s">
@@ -5506,7 +5509,7 @@
         <v>58</v>
       </c>
       <c r="M6" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N6" s="51">
         <v>50</v>
@@ -5515,14 +5518,14 @@
       <c r="P6" s="51"/>
       <c r="Q6" s="52"/>
       <c r="R6" s="69" t="str">
-        <f t="shared" ref="R6:R9" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
+        <f t="shared" ref="R6:R10" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S6" s="147"/>
+      <c r="S6" s="151"/>
     </row>
     <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="145"/>
-      <c r="B7" s="149"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="153"/>
       <c r="C7" s="51" t="s">
         <v>95</v>
       </c>
@@ -5561,11 +5564,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del capacidadPersonas del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S7" s="147"/>
+      <c r="S7" s="151"/>
     </row>
     <row r="8" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="145"/>
-      <c r="B8" s="149"/>
+      <c r="A8" s="149"/>
+      <c r="B8" s="153"/>
       <c r="C8" s="51" t="s">
         <v>108</v>
       </c>
@@ -5604,84 +5607,110 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del descripcion del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S8" s="147"/>
+      <c r="S8" s="151"/>
     </row>
     <row r="9" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="145"/>
-      <c r="B9" s="149"/>
+      <c r="A9" s="149"/>
+      <c r="B9" s="153"/>
       <c r="C9" s="51" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="E9" s="51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="51">
-        <v>3</v>
+        <v>5000</v>
       </c>
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
       <c r="I9" s="51"/>
       <c r="J9" s="51" t="str">
         <f t="shared" si="0"/>
-        <v>tiempoUsoZonaComun</v>
+        <v>normasZonaComun</v>
       </c>
       <c r="K9" s="51" t="s">
         <v>59</v>
       </c>
       <c r="L9" s="51" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="M9" s="51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="51">
-        <v>3</v>
+        <v>5000</v>
       </c>
       <c r="O9" s="51"/>
       <c r="P9" s="51"/>
       <c r="Q9" s="52"/>
       <c r="R9" s="69" t="str">
         <f t="shared" si="1"/>
+        <v>Atributo que contiene la informacion del normas del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S9" s="151"/>
+    </row>
+    <row r="10" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="149"/>
+      <c r="B10" s="153"/>
+      <c r="C10" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="51">
+        <v>1</v>
+      </c>
+      <c r="F10" s="51">
+        <v>5</v>
+      </c>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51">
+        <v>0</v>
+      </c>
+      <c r="I10" s="51">
+        <v>3600</v>
+      </c>
+      <c r="J10" s="51" t="str">
+        <f t="shared" si="0"/>
+        <v>tiempoUsoZonaComun</v>
+      </c>
+      <c r="K10" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="M10" s="51">
+        <v>1</v>
+      </c>
+      <c r="N10" s="51">
+        <v>5</v>
+      </c>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="52">
+        <v>3600</v>
+      </c>
+      <c r="R10" s="69" t="str">
+        <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del tiempoUso del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S9" s="147"/>
-    </row>
-    <row r="10" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="145"/>
-      <c r="B10" s="149"/>
-      <c r="C10" s="51" t="s">
+      <c r="S10" s="151"/>
+    </row>
+    <row r="11" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="149"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D11" s="70" t="s">
         <v>104</v>
-      </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="147"/>
-    </row>
-    <row r="11" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="145"/>
-      <c r="B11" s="150"/>
-      <c r="C11" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="70" t="s">
-        <v>61</v>
       </c>
       <c r="E11" s="51"/>
       <c r="F11" s="51"/>
@@ -5697,279 +5726,312 @@
       <c r="P11" s="51"/>
       <c r="Q11" s="52"/>
       <c r="R11" s="69"/>
-      <c r="S11" s="147"/>
-    </row>
-    <row r="12" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="145"/>
-      <c r="B12" s="151" t="s">
+      <c r="S11" s="151"/>
+    </row>
+    <row r="12" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="149"/>
+      <c r="B12" s="154"/>
+      <c r="C12" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="52"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="151"/>
+    </row>
+    <row r="13" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="149"/>
+      <c r="B13" s="155" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C13" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="73" t="s">
+      <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="73">
-        <v>32</v>
-      </c>
-      <c r="F12" s="73">
-        <v>32</v>
-      </c>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="73" t="str">
-        <f t="shared" si="0"/>
-        <v>identificadorZonaComun</v>
-      </c>
-      <c r="K12" s="73"/>
-      <c r="L12" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="73">
-        <v>32</v>
-      </c>
-      <c r="N12" s="73">
-        <v>32</v>
-      </c>
-      <c r="O12" s="73"/>
-      <c r="P12" s="73"/>
-      <c r="Q12" s="74"/>
-      <c r="R12" s="75" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C12," del objeto dominio ",B12,"  en el contexto de ",$A$5,".")</f>
-        <v>Atributo que contiene la informacion del identificador del objeto dominio UnidadTiempoUso  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S12" s="147"/>
-    </row>
-    <row r="13" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="145"/>
-      <c r="B13" s="152"/>
-      <c r="C13" s="73" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="73" t="s">
-        <v>58</v>
-      </c>
       <c r="E13" s="73">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F13" s="73">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G13" s="73"/>
       <c r="H13" s="73"/>
       <c r="I13" s="73"/>
       <c r="J13" s="73" t="str">
-        <f t="shared" si="0"/>
-        <v>nombreZonaComun</v>
-      </c>
-      <c r="K13" s="73"/>
+        <f>_xlfn.CONCAT(C13,$B$13)</f>
+        <v>identificadorUnidadTiempoUso</v>
+      </c>
+      <c r="K13" s="73" t="s">
+        <v>59</v>
+      </c>
       <c r="L13" s="73" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M13" s="73">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="N13" s="73">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O13" s="73"/>
       <c r="P13" s="73"/>
       <c r="Q13" s="74"/>
       <c r="R13" s="75" t="str">
-        <f t="shared" ref="R13:R15" si="2">_xlfn.CONCAT("Atributo que contiene la informacion del ",C13," del objeto dominio ",B13,"  en el contexto de ",$A$5,".")</f>
-        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S13" s="147"/>
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C13," del objeto dominio ",B13,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio UnidadTiempoUso  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S13" s="151"/>
     </row>
     <row r="14" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="145"/>
-      <c r="B14" s="152"/>
+      <c r="A14" s="149"/>
+      <c r="B14" s="156"/>
       <c r="C14" s="73" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="D14" s="73" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="73">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="G14" s="73"/>
       <c r="H14" s="73"/>
       <c r="I14" s="73"/>
       <c r="J14" s="73" t="str">
-        <f t="shared" si="0"/>
-        <v>abreviaturaZonaComun</v>
-      </c>
-      <c r="K14" s="73"/>
+        <f t="shared" ref="J14:J16" si="2">_xlfn.CONCAT(C14,$B$13)</f>
+        <v>nombreUnidadTiempoUso</v>
+      </c>
+      <c r="K14" s="73" t="s">
+        <v>59</v>
+      </c>
       <c r="L14" s="73" t="s">
         <v>58</v>
       </c>
       <c r="M14" s="73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N14" s="73">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="O14" s="73"/>
       <c r="P14" s="73"/>
       <c r="Q14" s="74"/>
       <c r="R14" s="75" t="str">
-        <f t="shared" si="2"/>
-        <v>Atributo que contiene la informacion del abreviatura del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S14" s="147"/>
+        <f t="shared" ref="R14:R16" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C14," del objeto dominio ",B14,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S14" s="151"/>
     </row>
     <row r="15" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="145"/>
-      <c r="B15" s="153"/>
+      <c r="A15" s="149"/>
+      <c r="B15" s="156"/>
       <c r="C15" s="73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D15" s="73" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="E15" s="73">
         <v>1</v>
       </c>
       <c r="F15" s="73">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G15" s="73"/>
       <c r="H15" s="73"/>
       <c r="I15" s="73"/>
       <c r="J15" s="73" t="str">
-        <f t="shared" si="0"/>
-        <v>enBaseZonaComun</v>
-      </c>
-      <c r="K15" s="73"/>
+        <f t="shared" si="2"/>
+        <v>abreviaturaUnidadTiempoUso</v>
+      </c>
+      <c r="K15" s="73" t="s">
+        <v>59</v>
+      </c>
       <c r="L15" s="73" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="M15" s="73">
         <v>1</v>
       </c>
       <c r="N15" s="73">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O15" s="73"/>
       <c r="P15" s="73"/>
       <c r="Q15" s="74"/>
       <c r="R15" s="75" t="str">
+        <f t="shared" si="3"/>
+        <v>Atributo que contiene la informacion del abreviatura del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S15" s="151"/>
+    </row>
+    <row r="16" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="149"/>
+      <c r="B16" s="157"/>
+      <c r="C16" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="73">
+        <v>4</v>
+      </c>
+      <c r="F16" s="73">
+        <v>5</v>
+      </c>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="73" t="str">
         <f t="shared" si="2"/>
+        <v>enBaseUnidadTiempoUso</v>
+      </c>
+      <c r="K16" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="M16" s="73">
+        <v>4</v>
+      </c>
+      <c r="N16" s="73">
+        <v>5</v>
+      </c>
+      <c r="O16" s="73"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="75" t="str">
+        <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del enBase del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S15" s="147"/>
-    </row>
-    <row r="16" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="145"/>
-      <c r="B16" s="132" t="s">
+      <c r="S16" s="151"/>
+    </row>
+    <row r="17" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="149"/>
+      <c r="B17" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C17" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D17" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="32">
-        <v>32</v>
-      </c>
-      <c r="F16" s="32">
-        <v>32</v>
-      </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32" t="str">
-        <f>_xlfn.CONCAT(C16,$B$16)</f>
-        <v>identificadorConjuntoResidencial</v>
-      </c>
-      <c r="K16" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="M16" s="32">
-        <v>32</v>
-      </c>
-      <c r="N16" s="32">
-        <v>32</v>
-      </c>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="61" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",$A$5,".")</f>
-        <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
-      </c>
-      <c r="S16" s="147"/>
-    </row>
-    <row r="17" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="146"/>
-      <c r="B17" s="132"/>
-      <c r="C17" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>58</v>
-      </c>
       <c r="E17" s="32">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F17" s="32">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32" t="str">
-        <f>_xlfn.CONCAT(C17,$B$16)</f>
-        <v>nombreConjuntoResidencial</v>
+        <f>_xlfn.CONCAT(C17,$B$17)</f>
+        <v>identificadorConjuntoResidencial</v>
       </c>
       <c r="K17" s="32" t="s">
         <v>59</v>
       </c>
       <c r="L17" s="32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M17" s="32">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N17" s="32">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O17" s="32"/>
       <c r="P17" s="32"/>
       <c r="Q17" s="54"/>
       <c r="R17" s="61" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
+      </c>
+      <c r="S17" s="151"/>
+    </row>
+    <row r="18" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="150"/>
+      <c r="B18" s="132"/>
+      <c r="C18" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="32">
+        <v>1</v>
+      </c>
+      <c r="F18" s="32">
+        <v>50</v>
+      </c>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32" t="str">
+        <f>_xlfn.CONCAT(C18,$B$17)</f>
+        <v>nombreConjuntoResidencial</v>
+      </c>
+      <c r="K18" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="32">
+        <v>1</v>
+      </c>
+      <c r="N18" s="32">
+        <v>50</v>
+      </c>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="61" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C18," del objeto dominio ",B18,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S17" s="147"/>
+      <c r="S18" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A5:A18"/>
+    <mergeCell ref="S5:S18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B5:B12"/>
+    <mergeCell ref="B13:B16"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
-    <mergeCell ref="A5:A17"/>
-    <mergeCell ref="S5:S17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B5:B11"/>
-    <mergeCell ref="B12:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D10" location="'Agenda ConjuntosResidenciales-0'!B12" display="UnidadTiempoUso" xr:uid="{7145F6A3-A24A-4F31-B98A-658FB31AEB42}"/>
-    <hyperlink ref="D11" location="'Agenda ConjuntosResidenciales-0'!B16" display="ConjuntoResidencial" xr:uid="{C0CAC5E7-0ED2-485E-BFD1-A6C07FEF9C49}"/>
+    <hyperlink ref="D11" location="'Agenda ConjuntosResidenciales-0'!B13" display="UnidadTiempoUso" xr:uid="{7145F6A3-A24A-4F31-B98A-658FB31AEB42}"/>
+    <hyperlink ref="D12" location="'Agenda ConjuntosResidenciales-0'!B17" display="ConjuntoResidencial" xr:uid="{C0CAC5E7-0ED2-485E-BFD1-A6C07FEF9C49}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F790329D-8B2D-4316-A77F-82627FBE3309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C3761F-3DAB-485F-9781-84D5F338B409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="2970" windowWidth="17340" windowHeight="15345" firstSheet="6" activeTab="7" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="3" r:id="rId1"/>
@@ -18,12 +18,13 @@
     <sheet name="Contextos" sheetId="2" r:id="rId3"/>
     <sheet name="Conjuntos Residenciales" sheetId="4" r:id="rId4"/>
     <sheet name="Residentes" sheetId="5" r:id="rId5"/>
-    <sheet name="Residente ConjutosResidenciales" sheetId="12" r:id="rId6"/>
+    <sheet name="Conjuntos.R Residentes-0001" sheetId="12" r:id="rId6"/>
     <sheet name="Agendas" sheetId="11" r:id="rId7"/>
-    <sheet name="Agenda ConjuntosResidenciales-0" sheetId="13" r:id="rId8"/>
-    <sheet name="Reservas" sheetId="6" r:id="rId9"/>
-    <sheet name="Reserva-0001" sheetId="8" r:id="rId10"/>
-    <sheet name="Reserva-0002" sheetId="10" r:id="rId11"/>
+    <sheet name="Turno Agenda-0001" sheetId="16" r:id="rId8"/>
+    <sheet name="Agenda ConjuntosResidenciales-0" sheetId="13" r:id="rId9"/>
+    <sheet name="Reservas" sheetId="6" r:id="rId10"/>
+    <sheet name="Reserva-0001" sheetId="8" r:id="rId11"/>
+    <sheet name="Reserva-0002" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="167">
   <si>
     <t>Problema/Dominio:</t>
   </si>
@@ -457,13 +458,103 @@
   </si>
   <si>
     <t>normas</t>
+  </si>
+  <si>
+    <t>Alfanumerico</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada turno sea único.</t>
+  </si>
+  <si>
+    <t>Este dato representa el nombre y número con el que se va a concoer el turno por defecto la palabra "Turno" y luego un numero consecutivo</t>
+  </si>
+  <si>
+    <t>Es un dato que representa la hora de inicio del turno.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa la hora de finalización del turno.</t>
+  </si>
+  <si>
+    <t>Este dato es de tipo logico el cual dice si esta disponible o no disponible un turno</t>
+  </si>
+  <si>
+    <t>Este dato representa con que agenda está relacionada el turno.</t>
+  </si>
+  <si>
+    <t>disponibilidad</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada agenda residencial sea único.</t>
+  </si>
+  <si>
+    <t>Este es un dato tipo texto que representa el nombre de como se llama la agenda que se esta programando</t>
+  </si>
+  <si>
+    <t>Este dato es un tipo logico que representa si esta disponible o no la agenda</t>
+  </si>
+  <si>
+    <t>Este dato representa la fecha de hora de inicio en la cual empieza la agenda.</t>
+  </si>
+  <si>
+    <t>Este dato representa la fecha de hora final en la cual finaliza una agenda.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa la zona común con la que está relacionada la agenda especifica.</t>
+  </si>
+  <si>
+    <t>apellido</t>
+  </si>
+  <si>
+    <t>tipoDocumento</t>
+  </si>
+  <si>
+    <t>fechaNacimiento</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>numeroContacto</t>
+  </si>
+  <si>
+    <t>correoElectronico</t>
+  </si>
+  <si>
+    <t>contraseña</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada residente sea único.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el nombre del residente.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el apellido de un residente</t>
+  </si>
+  <si>
+    <t>este dato representa en forma textual , que tipo de documento tiene el residente como TI, CC, RC, PASS.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el numero único del documento de un residente.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa la fecha de nacimiento que tiene un residente.</t>
+  </si>
+  <si>
+    <t>Este dato representa el número de contacto de un residente.</t>
+  </si>
+  <si>
+    <t>Este dato representa el correo electrónico de un residente</t>
+  </si>
+  <si>
+    <t>este dato representa la contraseña con la que ingresa el residente</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,8 +607,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -596,8 +700,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="38">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -1022,17 +1138,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1076,6 +1181,99 @@
       </right>
       <top/>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1085,7 +1283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1288,18 +1486,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1444,12 +1636,12 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1465,27 +1657,15 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1504,7 +1684,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1516,6 +1696,36 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1528,36 +1738,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1588,7 +1768,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1607,6 +1787,160 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2038,20 +2372,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0E5666-F6A5-49FF-B12A-1FE829F0A68B}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="79.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="80"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="78"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
@@ -2059,7 +2393,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
@@ -2067,7 +2401,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
@@ -2075,13 +2409,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>16</v>
       </c>
@@ -2089,7 +2423,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>17</v>
       </c>
@@ -2097,7 +2431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
         <v>18</v>
       </c>
@@ -2105,7 +2439,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34" t="s">
         <v>19</v>
       </c>
@@ -2113,7 +2447,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>20</v>
       </c>
@@ -2121,7 +2455,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34" t="s">
         <v>21</v>
       </c>
@@ -2129,7 +2463,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>22</v>
       </c>
@@ -2146,109 +2480,292 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C088BE7-88A8-46E0-AF18-6F40B3F602F8}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="107" t="str">
+        <f>Contextos!B15</f>
+        <v>Reservas</v>
+      </c>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="108"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="109" t="str">
+        <f>Contextos!D15</f>
+        <v>Contexto cuya intención enfocarse en la gestión del proceso de reservas de los recursos, incluyendo la disponibilidad de los recursos y las reservas que los residentes realizan.</v>
+      </c>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="110"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="111" t="str">
+        <f>Contextos!A15</f>
+        <v>Core/Básico</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="115"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="116" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="116" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="116"/>
+      <c r="F5" s="117" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="116"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="117"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="116"/>
+      <c r="D7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="117"/>
+    </row>
+    <row r="8" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="48" t="str">
+        <f>B8&amp;"-0001"</f>
+        <v>Reserva-0001</v>
+      </c>
+      <c r="E8" s="49" t="str">
+        <f t="shared" ref="E8:E9" si="0">_xlfn.CONCAT(A8," de ",B8)</f>
+        <v>Agendas de Reserva</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="20" t="str">
+        <f>B9&amp;"-0002"</f>
+        <v>Reserva-0002</v>
+      </c>
+      <c r="E9" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>Residentes de Reserva</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F5:F7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D8" location="'Reserva-0001'!A1" display="'Reserva-0001'!A1" xr:uid="{2CD27129-3F8D-4A69-AE6D-74455A97C54B}"/>
+    <hyperlink ref="D9" location="'Reserva-0002'!A1" display="'Reserva-0002'!A1" xr:uid="{6CE586E2-B2DF-423C-BBAA-EB08E79D1E9C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E124A45D-ECAC-4EEC-9BB6-8B4657FFF3C6}">
+          <x14:formula1>
+            <xm:f>Valores!$A$7:$A$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>C8:C9</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3888799-E6A1-4FAB-A09B-AF9FE652AF52}">
   <dimension ref="A1:S27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" style="13" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" style="13" customWidth="1"/>
     <col min="3" max="3" width="31" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="42.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="58" style="26" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="13"/>
+    <col min="19" max="19" width="17.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.44140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122" t="str">
+      <c r="B1" s="120" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="123"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="117"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="125" t="s">
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="121"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="113"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="115"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="144" t="s">
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="124"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="148" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="146" t="s">
+      <c r="S3" s="150" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>28</v>
       </c>
@@ -2300,14 +2817,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="161"/>
-      <c r="S4" s="147"/>
-    </row>
-    <row r="5" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="139" t="s">
+      <c r="R4" s="155"/>
+      <c r="S4" s="151"/>
+    </row>
+    <row r="5" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="133" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="141" t="s">
+      <c r="B5" s="135" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -2344,17 +2861,17 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="51"/>
-      <c r="R5" s="69" t="str">
+      <c r="R5" s="68" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificadorConjuntoResidencial del objeto dominio ZonaComun  en el contexto de Agendas.</v>
       </c>
-      <c r="S5" s="158" t="s">
+      <c r="S5" s="152" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="139"/>
-      <c r="B6" s="142"/>
+    <row r="6" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="133"/>
+      <c r="B6" s="136"/>
       <c r="C6" s="51" t="s">
         <v>119</v>
       </c>
@@ -2389,15 +2906,15 @@
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="51"/>
-      <c r="R6" s="69" t="str">
+      <c r="R6" s="68" t="str">
         <f t="shared" ref="R6:R15" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombreConjuntoResidencial del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S6" s="158"/>
-    </row>
-    <row r="7" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="139"/>
-      <c r="B7" s="142"/>
+      <c r="S6" s="152"/>
+    </row>
+    <row r="7" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="133"/>
+      <c r="B7" s="136"/>
       <c r="C7" s="51" t="s">
         <v>120</v>
       </c>
@@ -2432,15 +2949,15 @@
       <c r="O7" s="51"/>
       <c r="P7" s="51"/>
       <c r="Q7" s="51"/>
-      <c r="R7" s="69" t="str">
+      <c r="R7" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del identificadorUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S7" s="158"/>
-    </row>
-    <row r="8" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="139"/>
-      <c r="B8" s="142"/>
+      <c r="S7" s="152"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="133"/>
+      <c r="B8" s="136"/>
       <c r="C8" s="51" t="s">
         <v>121</v>
       </c>
@@ -2475,15 +2992,15 @@
       <c r="O8" s="51"/>
       <c r="P8" s="51"/>
       <c r="Q8" s="51"/>
-      <c r="R8" s="69" t="str">
+      <c r="R8" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del nombreUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S8" s="158"/>
-    </row>
-    <row r="9" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="139"/>
-      <c r="B9" s="142"/>
+      <c r="S8" s="152"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="133"/>
+      <c r="B9" s="136"/>
       <c r="C9" s="51" t="s">
         <v>122</v>
       </c>
@@ -2518,16 +3035,16 @@
       <c r="O9" s="51"/>
       <c r="P9" s="51"/>
       <c r="Q9" s="51"/>
-      <c r="R9" s="69" t="str">
+      <c r="R9" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del abreviaturaUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S9" s="158"/>
-    </row>
-    <row r="10" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="139"/>
-      <c r="B10" s="142"/>
-      <c r="C10" s="76" t="s">
+      <c r="S9" s="152"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="133"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="74" t="s">
         <v>123</v>
       </c>
       <c r="D10" s="51" t="s">
@@ -2561,16 +3078,16 @@
       <c r="O10" s="51"/>
       <c r="P10" s="51"/>
       <c r="Q10" s="51"/>
-      <c r="R10" s="69" t="str">
+      <c r="R10" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del enBaseUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S10" s="158"/>
-    </row>
-    <row r="11" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="139"/>
-      <c r="B11" s="142"/>
-      <c r="C11" s="76" t="s">
+      <c r="S10" s="152"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="133"/>
+      <c r="B11" s="136"/>
+      <c r="C11" s="74" t="s">
         <v>124</v>
       </c>
       <c r="D11" s="51" t="s">
@@ -2604,16 +3121,16 @@
       <c r="O11" s="51"/>
       <c r="P11" s="51"/>
       <c r="Q11" s="51"/>
-      <c r="R11" s="69" t="str">
+      <c r="R11" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del IdentificadorZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S11" s="158"/>
-    </row>
-    <row r="12" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="139"/>
-      <c r="B12" s="142"/>
-      <c r="C12" s="76" t="s">
+      <c r="S11" s="152"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="133"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="74" t="s">
         <v>125</v>
       </c>
       <c r="D12" s="51" t="s">
@@ -2647,16 +3164,16 @@
       <c r="O12" s="51"/>
       <c r="P12" s="51"/>
       <c r="Q12" s="51"/>
-      <c r="R12" s="69" t="str">
+      <c r="R12" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del nombreZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S12" s="158"/>
-    </row>
-    <row r="13" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="139"/>
-      <c r="B13" s="142"/>
-      <c r="C13" s="76" t="s">
+      <c r="S12" s="152"/>
+    </row>
+    <row r="13" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="133"/>
+      <c r="B13" s="136"/>
+      <c r="C13" s="74" t="s">
         <v>126</v>
       </c>
       <c r="D13" s="51" t="s">
@@ -2690,16 +3207,16 @@
       <c r="O13" s="51"/>
       <c r="P13" s="51"/>
       <c r="Q13" s="51"/>
-      <c r="R13" s="69" t="str">
+      <c r="R13" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del capacidadPersonasZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S13" s="158"/>
-    </row>
-    <row r="14" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="139"/>
-      <c r="B14" s="142"/>
-      <c r="C14" s="76" t="s">
+      <c r="S13" s="152"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="133"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="74" t="s">
         <v>127</v>
       </c>
       <c r="D14" s="51" t="s">
@@ -2733,16 +3250,16 @@
       <c r="O14" s="51"/>
       <c r="P14" s="51"/>
       <c r="Q14" s="51"/>
-      <c r="R14" s="69" t="str">
+      <c r="R14" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del decripcionZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S14" s="158"/>
-    </row>
-    <row r="15" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="139"/>
-      <c r="B15" s="143"/>
-      <c r="C15" s="76" t="s">
+      <c r="S14" s="152"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="133"/>
+      <c r="B15" s="137"/>
+      <c r="C15" s="74" t="s">
         <v>128</v>
       </c>
       <c r="D15" s="51" t="s">
@@ -2784,15 +3301,15 @@
       <c r="Q15" s="51">
         <v>3600</v>
       </c>
-      <c r="R15" s="69" t="str">
+      <c r="R15" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del tiempoUsoZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S15" s="158"/>
-    </row>
-    <row r="16" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="139"/>
-      <c r="B16" s="163" t="s">
+      <c r="S15" s="152"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="133"/>
+      <c r="B16" s="157" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="50" t="s">
@@ -2833,11 +3350,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Agenda  en el contexto de Agendas.</v>
       </c>
-      <c r="S16" s="158"/>
-    </row>
-    <row r="17" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="139"/>
-      <c r="B17" s="163"/>
+      <c r="S16" s="152"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="133"/>
+      <c r="B17" s="157"/>
       <c r="C17" s="50" t="s">
         <v>4</v>
       </c>
@@ -2876,11 +3393,11 @@
         <f t="shared" ref="R17:R19" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S17" s="158"/>
-    </row>
-    <row r="18" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="139"/>
-      <c r="B18" s="163"/>
+      <c r="S17" s="152"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="133"/>
+      <c r="B18" s="157"/>
       <c r="C18" s="31" t="s">
         <v>90</v>
       </c>
@@ -2911,11 +3428,11 @@
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del fechaHoraInicio del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S18" s="158"/>
-    </row>
-    <row r="19" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="139"/>
-      <c r="B19" s="163"/>
+      <c r="S18" s="152"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="133"/>
+      <c r="B19" s="157"/>
       <c r="C19" s="31" t="s">
         <v>94</v>
       </c>
@@ -2946,15 +3463,15 @@
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del fechaHoraFin del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S19" s="158"/>
-    </row>
-    <row r="20" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="139"/>
-      <c r="B20" s="163"/>
+      <c r="S19" s="152"/>
+    </row>
+    <row r="20" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="133"/>
+      <c r="B20" s="157"/>
       <c r="C20" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="77" t="s">
+      <c r="D20" s="75" t="s">
         <v>41</v>
       </c>
       <c r="E20" s="31"/>
@@ -2971,11 +3488,11 @@
       <c r="P20" s="31"/>
       <c r="Q20" s="31"/>
       <c r="R20" s="40"/>
-      <c r="S20" s="158"/>
-    </row>
-    <row r="21" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="139"/>
-      <c r="B21" s="160" t="s">
+      <c r="S20" s="152"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="133"/>
+      <c r="B21" s="154" t="s">
         <v>65</v>
       </c>
       <c r="C21" s="32" t="s">
@@ -3016,11 +3533,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C21," del objeto dominio ",B21,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Turno  en el contexto de Agendas.</v>
       </c>
-      <c r="S21" s="158"/>
-    </row>
-    <row r="22" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="139"/>
-      <c r="B22" s="160"/>
+      <c r="S21" s="152"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="133"/>
+      <c r="B22" s="154"/>
       <c r="C22" s="32" t="s">
         <v>129</v>
       </c>
@@ -3059,11 +3576,11 @@
         <f t="shared" ref="R22:R25" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C22," del objeto dominio ",B22,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del numeroTurno del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S22" s="158"/>
-    </row>
-    <row r="23" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="139"/>
-      <c r="B23" s="160"/>
+      <c r="S22" s="152"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="133"/>
+      <c r="B23" s="154"/>
       <c r="C23" s="32" t="s">
         <v>130</v>
       </c>
@@ -3092,11 +3609,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del horaInicio del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S23" s="158"/>
-    </row>
-    <row r="24" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="139"/>
-      <c r="B24" s="160"/>
+      <c r="S23" s="152"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="133"/>
+      <c r="B24" s="154"/>
       <c r="C24" s="32" t="s">
         <v>132</v>
       </c>
@@ -3125,11 +3642,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del horaFin del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S24" s="158"/>
-    </row>
-    <row r="25" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="139"/>
-      <c r="B25" s="160"/>
+      <c r="S24" s="152"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="133"/>
+      <c r="B25" s="154"/>
       <c r="C25" s="32" t="s">
         <v>133</v>
       </c>
@@ -3158,15 +3675,15 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del estado del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S25" s="158"/>
-    </row>
-    <row r="26" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="162"/>
-      <c r="B26" s="160"/>
+      <c r="S25" s="152"/>
+    </row>
+    <row r="26" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="156"/>
+      <c r="B26" s="154"/>
       <c r="C26" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D26" s="78" t="s">
+      <c r="D26" s="76" t="s">
         <v>64</v>
       </c>
       <c r="E26" s="32"/>
@@ -3183,9 +3700,9 @@
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
       <c r="R26" s="41"/>
-      <c r="S26" s="159"/>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="S26" s="153"/>
+    </row>
+    <row r="27" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="S5:S26"/>
@@ -3208,110 +3725,110 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4E4C5E7-072D-46C9-A943-F12FD1E94927}">
   <dimension ref="A1:S13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" style="13" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="13" customWidth="1"/>
     <col min="2" max="2" width="21" style="13" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" style="13" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="58" style="26" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="13"/>
+    <col min="19" max="19" width="17.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.44140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122" t="str">
+      <c r="B1" s="120" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="123"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="117"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="125" t="s">
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="121"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="113"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="115"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="144" t="s">
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="124"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="148" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="146" t="s">
+      <c r="S3" s="150" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="29" t="s">
         <v>28</v>
       </c>
@@ -3363,14 +3880,14 @@
       <c r="Q4" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="145"/>
-      <c r="S4" s="147"/>
-    </row>
-    <row r="5" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="164" t="s">
+      <c r="R4" s="149"/>
+      <c r="S4" s="151"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="166" t="s">
         <v>82</v>
       </c>
       <c r="C5" s="31" t="s">
@@ -3411,14 +3928,14 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del TipoInmueble(Nombre) del objeto dominio Inmueble  en el contexto de Residentes.</v>
       </c>
-      <c r="S5" s="167" t="str">
+      <c r="S5" s="161" t="str">
         <f>B9</f>
         <v>Residente</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="165"/>
-      <c r="B6" s="173"/>
+    <row r="6" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="159"/>
+      <c r="B6" s="167"/>
       <c r="C6" s="31" t="s">
         <v>112</v>
       </c>
@@ -3457,11 +3974,11 @@
         <f t="shared" ref="R6:R8" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del TipoZonaInmueble(Identificador) del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S6" s="158"/>
-    </row>
-    <row r="7" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="165"/>
-      <c r="B7" s="173"/>
+      <c r="S6" s="152"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="159"/>
+      <c r="B7" s="167"/>
       <c r="C7" s="31" t="s">
         <v>113</v>
       </c>
@@ -3500,11 +4017,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del TipoZonaInmueble(Nombre) del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S7" s="158"/>
-    </row>
-    <row r="8" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="165"/>
-      <c r="B8" s="174"/>
+      <c r="S7" s="152"/>
+    </row>
+    <row r="8" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="159"/>
+      <c r="B8" s="168"/>
       <c r="C8" s="31" t="s">
         <v>114</v>
       </c>
@@ -3551,11 +4068,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del ZonaInmueble(NumeroZonaInmueble) del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S8" s="158"/>
-    </row>
-    <row r="9" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="165"/>
-      <c r="B9" s="169" t="s">
+      <c r="S8" s="152"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="159"/>
+      <c r="B9" s="163" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="32" t="s">
@@ -3596,11 +4113,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C9," del objeto dominio ",B9,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Residente  en el contexto de Residentes.</v>
       </c>
-      <c r="S9" s="158"/>
-    </row>
-    <row r="10" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="165"/>
-      <c r="B10" s="170"/>
+      <c r="S9" s="152"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="159"/>
+      <c r="B10" s="164"/>
       <c r="C10" s="32" t="s">
         <v>57</v>
       </c>
@@ -3639,11 +4156,11 @@
         <f t="shared" ref="R10:R11" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S10" s="158"/>
-    </row>
-    <row r="11" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="165"/>
-      <c r="B11" s="170"/>
+      <c r="S10" s="152"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="159"/>
+      <c r="B11" s="164"/>
       <c r="C11" s="32" t="s">
         <v>117</v>
       </c>
@@ -3682,11 +4199,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del numeroDocumento del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S11" s="158"/>
-    </row>
-    <row r="12" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="166"/>
-      <c r="B12" s="171"/>
+      <c r="S11" s="152"/>
+    </row>
+    <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="160"/>
+      <c r="B12" s="165"/>
       <c r="C12" s="32" t="s">
         <v>115</v>
       </c>
@@ -3707,9 +4224,9 @@
       <c r="P12" s="32"/>
       <c r="Q12" s="32"/>
       <c r="R12" s="41"/>
-      <c r="S12" s="168"/>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="S12" s="162"/>
+    </row>
+    <row r="13" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A5:A12"/>
@@ -3730,7 +4247,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1464EB49-FF8E-46BB-B8BB-A3B13262BCA8}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3740,43 +4257,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825409BB-6EDF-4233-9680-0DFD77A9FF39}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="22.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.7109375" style="7" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="36.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="22.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.6640625" style="7" customWidth="1"/>
+    <col min="5" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="91"/>
-    </row>
-    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="88"/>
+      <c r="D1" s="89"/>
+    </row>
+    <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="94"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="95" t="s">
+      <c r="C2" s="91"/>
+      <c r="D2" s="92"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -3790,133 +4307,133 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="100" t="s">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="99" t="s">
         <v>79</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="102" t="s">
+      <c r="D5" s="100" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="100"/>
-      <c r="B6" s="101"/>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="98"/>
+      <c r="B6" s="99"/>
       <c r="C6" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="102"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="100"/>
-      <c r="B7" s="101"/>
+      <c r="D6" s="100"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="98"/>
+      <c r="B7" s="99"/>
       <c r="C7" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="102"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="100"/>
-      <c r="B8" s="101"/>
+      <c r="D7" s="100"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
       <c r="C8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="102"/>
-    </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="100"/>
-      <c r="B9" s="101"/>
+      <c r="D8" s="100"/>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
       <c r="C9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="102"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="98" t="s">
+      <c r="D9" s="100"/>
+    </row>
+    <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="97" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="96" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
+    <row r="11" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="96"/>
+      <c r="B11" s="97"/>
       <c r="C11" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="98"/>
-    </row>
-    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="106" t="s">
+      <c r="D11" s="96"/>
+    </row>
+    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="103" t="s">
+      <c r="B12" s="101" t="s">
         <v>83</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="106" t="s">
+      <c r="D12" s="104" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="107"/>
-      <c r="B13" s="104"/>
+    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="105"/>
+      <c r="B13" s="102"/>
       <c r="C13" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="107"/>
-    </row>
-    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="108"/>
-      <c r="B14" s="105"/>
+      <c r="D13" s="105"/>
+    </row>
+    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="106"/>
+      <c r="B14" s="103"/>
       <c r="C14" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="108"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
+      <c r="D14" s="106"/>
+    </row>
+    <row r="15" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="82" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="87" t="s">
+      <c r="D15" s="85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="82"/>
-      <c r="B16" s="85"/>
+    <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="80"/>
+      <c r="B16" s="83"/>
       <c r="C16" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="88"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="83"/>
-      <c r="B17" s="86"/>
+      <c r="D16" s="86"/>
+    </row>
+    <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="81"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="89"/>
+      <c r="D17" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3974,112 +4491,112 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450F8E16-67C6-432D-A5AA-BF67F960EE18}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="38.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="38.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="64" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="13"/>
+    <col min="7" max="16384" width="11.44140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="109" t="str">
+      <c r="B1" s="107" t="str">
         <f>Contextos!B5</f>
         <v xml:space="preserve"> Conjuntos residenciales</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="110"/>
-    </row>
-    <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="108"/>
+    </row>
+    <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="111" t="str">
+      <c r="B2" s="109" t="str">
         <f>Contextos!D5</f>
         <v>Contexto cuya motivación es Gestionar la estructura física y los recursos disponibles en cada conjunto residencial. Aquí se manejan los datos sobre qué conjuntos existen, dónde están ubicados, qué recursos ofrecen según una Agenda con respectivos turnos para cada zona.</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="112"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="110"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="113" t="str">
+      <c r="B3" s="111" t="str">
         <f>Contextos!A5</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="114"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="115" t="s">
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="117"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="115"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="118" t="s">
+      <c r="C5" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="118"/>
-      <c r="F5" s="119" t="s">
+      <c r="E5" s="116"/>
+      <c r="F5" s="117" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="119"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="116"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="117"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="118"/>
+      <c r="C7" s="116"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="119"/>
-    </row>
-    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="F7" s="117"/>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>40</v>
       </c>
@@ -4101,7 +4618,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>40</v>
       </c>
@@ -4123,7 +4640,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
         <v>40</v>
       </c>
@@ -4145,7 +4662,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>81</v>
       </c>
@@ -4196,113 +4713,113 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D386A343-6D12-4FEA-AEEF-63E15D63FE79}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="64" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="13"/>
+    <col min="7" max="16384" width="11.44140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="109" t="str">
+      <c r="B1" s="107" t="str">
         <f>Contextos!B10</f>
         <v>Residentes</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="110"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="108"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="111" t="str">
+      <c r="B2" s="109" t="str">
         <f>Contextos!D10</f>
         <v>Contexto cuya motivación es encargarce de manejar la información de los residentes, incluidas sus identificaciones, contacto, y la relación entre el residente y su residencia dentro del conjunto.</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="112"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="110"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="113" t="str">
+      <c r="B3" s="111" t="str">
         <f>Contextos!A10</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="114"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="115" t="s">
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="117"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="115"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="118" t="s">
+      <c r="C5" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="118"/>
-      <c r="F5" s="119" t="s">
+      <c r="E5" s="116"/>
+      <c r="F5" s="117" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="119"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="116"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="117"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="118"/>
+      <c r="C7" s="116"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="119"/>
-    </row>
-    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F7" s="117"/>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>100</v>
       </c>
@@ -4355,738 +4872,1122 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59635CF3-0DE6-45E6-A198-1E7042F5E8F9}">
-  <dimension ref="A1:S25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" style="13" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="31" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="58" style="26" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="13"/>
+    <col min="19" max="19" width="17.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.44140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122" t="str">
+      <c r="B1" s="120" t="str">
         <f>Residentes!D8</f>
         <v>Residente ConjutosResidenciales-0001</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="123"/>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="117"/>
-    </row>
-    <row r="3" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="125" t="s">
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="121"/>
+    </row>
+    <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="113"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="115"/>
+    </row>
+    <row r="3" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="195" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126" t="s">
+      <c r="B3" s="196"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="196"/>
+      <c r="I3" s="196"/>
+      <c r="J3" s="196" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="127"/>
-      <c r="R3" s="128" t="s">
+      <c r="K3" s="196"/>
+      <c r="L3" s="196"/>
+      <c r="M3" s="196"/>
+      <c r="N3" s="196"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="196"/>
+      <c r="Q3" s="197"/>
+      <c r="R3" s="125" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="130" t="s">
+      <c r="S3" s="219" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+    <row r="4" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="199" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="199" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="199" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="199"/>
+      <c r="E4" s="199" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="199" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="199" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="199" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="199" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="199" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" s="199" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" s="199" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="M4" s="199" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="N4" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="O4" s="199" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="P4" s="199" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="Q4" s="200" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="N4" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="O4" s="16" t="s">
+      <c r="R4" s="126"/>
+      <c r="S4" s="220"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="201" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="210" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="211" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="212" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="211">
+        <v>32</v>
+      </c>
+      <c r="F5" s="211">
+        <v>32</v>
+      </c>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="212" t="str">
+        <f>_xlfn.CONCAT(C5,$B$5)</f>
+        <v>identificadorResidente</v>
+      </c>
+      <c r="K5" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="212" t="s">
+        <v>137</v>
+      </c>
+      <c r="M5" s="211">
+        <v>32</v>
+      </c>
+      <c r="N5" s="211">
+        <v>32</v>
+      </c>
+      <c r="O5" s="213"/>
+      <c r="P5" s="213"/>
+      <c r="Q5" s="214"/>
+      <c r="R5" s="215" t="s">
+        <v>158</v>
+      </c>
+      <c r="S5" s="118" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="133"/>
+      <c r="B6" s="216"/>
+      <c r="C6" s="211" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="212" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="211">
+        <v>1</v>
+      </c>
+      <c r="F6" s="211">
         <v>50</v>
       </c>
-      <c r="P4" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q4" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="R4" s="129"/>
-      <c r="S4" s="131"/>
-    </row>
-    <row r="5" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="139" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="141" t="s">
+      <c r="G6" s="211"/>
+      <c r="H6" s="211"/>
+      <c r="I6" s="211"/>
+      <c r="J6" s="212" t="str">
+        <f t="shared" ref="J6:J14" si="0">_xlfn.CONCAT(C6,$B$5)</f>
+        <v>nombreResidente</v>
+      </c>
+      <c r="K6" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="212" t="s">
+        <v>58</v>
+      </c>
+      <c r="M6" s="211">
+        <v>1</v>
+      </c>
+      <c r="N6" s="211">
+        <v>50</v>
+      </c>
+      <c r="O6" s="213"/>
+      <c r="P6" s="213"/>
+      <c r="Q6" s="214"/>
+      <c r="R6" s="215" t="s">
+        <v>159</v>
+      </c>
+      <c r="S6" s="118"/>
+    </row>
+    <row r="7" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="133"/>
+      <c r="B7" s="216"/>
+      <c r="C7" s="211" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="212" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="211">
+        <v>1</v>
+      </c>
+      <c r="F7" s="211">
+        <v>50</v>
+      </c>
+      <c r="G7" s="211"/>
+      <c r="H7" s="211"/>
+      <c r="I7" s="211"/>
+      <c r="J7" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>apellidoResidente</v>
+      </c>
+      <c r="K7" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="212" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="211">
+        <v>1</v>
+      </c>
+      <c r="N7" s="211">
+        <v>50</v>
+      </c>
+      <c r="O7" s="213"/>
+      <c r="P7" s="213"/>
+      <c r="Q7" s="214"/>
+      <c r="R7" s="215" t="s">
+        <v>160</v>
+      </c>
+      <c r="S7" s="118"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="133"/>
+      <c r="B8" s="216"/>
+      <c r="C8" s="211" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="212" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="211">
+        <v>1</v>
+      </c>
+      <c r="F8" s="211">
+        <v>50</v>
+      </c>
+      <c r="G8" s="211"/>
+      <c r="H8" s="211"/>
+      <c r="I8" s="211"/>
+      <c r="J8" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>tipoDocumentoResidente</v>
+      </c>
+      <c r="K8" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="212" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="211">
+        <v>1</v>
+      </c>
+      <c r="N8" s="211">
+        <v>50</v>
+      </c>
+      <c r="O8" s="213"/>
+      <c r="P8" s="213"/>
+      <c r="Q8" s="214"/>
+      <c r="R8" s="215" t="s">
+        <v>161</v>
+      </c>
+      <c r="S8" s="118"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="133"/>
+      <c r="B9" s="216"/>
+      <c r="C9" s="211" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="212" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="211"/>
+      <c r="F9" s="211"/>
+      <c r="G9" s="211"/>
+      <c r="H9" s="211"/>
+      <c r="I9" s="211"/>
+      <c r="J9" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>numeroDocumentoResidente</v>
+      </c>
+      <c r="K9" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="212" t="s">
+        <v>116</v>
+      </c>
+      <c r="M9" s="211"/>
+      <c r="N9" s="211"/>
+      <c r="O9" s="213"/>
+      <c r="P9" s="213"/>
+      <c r="Q9" s="214"/>
+      <c r="R9" s="215" t="s">
+        <v>162</v>
+      </c>
+      <c r="S9" s="118"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="133"/>
+      <c r="B10" s="216"/>
+      <c r="C10" s="211" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="212" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" s="211"/>
+      <c r="F10" s="211"/>
+      <c r="G10" s="211"/>
+      <c r="H10" s="211"/>
+      <c r="I10" s="211"/>
+      <c r="J10" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>fechaNacimientoResidente</v>
+      </c>
+      <c r="K10" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="212" t="s">
+        <v>154</v>
+      </c>
+      <c r="M10" s="211"/>
+      <c r="N10" s="211"/>
+      <c r="O10" s="213"/>
+      <c r="P10" s="213"/>
+      <c r="Q10" s="214"/>
+      <c r="R10" s="215" t="s">
+        <v>163</v>
+      </c>
+      <c r="S10" s="118"/>
+    </row>
+    <row r="11" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="133"/>
+      <c r="B11" s="216"/>
+      <c r="C11" s="211" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="212" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="211"/>
+      <c r="F11" s="211"/>
+      <c r="G11" s="211"/>
+      <c r="H11" s="211"/>
+      <c r="I11" s="211"/>
+      <c r="J11" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>numeroContactoResidente</v>
+      </c>
+      <c r="K11" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="212" t="s">
+        <v>116</v>
+      </c>
+      <c r="M11" s="211"/>
+      <c r="N11" s="211"/>
+      <c r="O11" s="213"/>
+      <c r="P11" s="213"/>
+      <c r="Q11" s="214"/>
+      <c r="R11" s="215" t="s">
+        <v>164</v>
+      </c>
+      <c r="S11" s="118"/>
+    </row>
+    <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="133"/>
+      <c r="B12" s="216"/>
+      <c r="C12" s="211" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="212" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="211">
+        <v>6</v>
+      </c>
+      <c r="F12" s="211">
+        <v>50</v>
+      </c>
+      <c r="G12" s="211"/>
+      <c r="H12" s="211"/>
+      <c r="I12" s="211"/>
+      <c r="J12" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>correoElectronicoResidente</v>
+      </c>
+      <c r="K12" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="212" t="s">
+        <v>137</v>
+      </c>
+      <c r="M12" s="211">
+        <v>6</v>
+      </c>
+      <c r="N12" s="211">
+        <v>50</v>
+      </c>
+      <c r="O12" s="213"/>
+      <c r="P12" s="213"/>
+      <c r="Q12" s="214"/>
+      <c r="R12" s="215" t="s">
+        <v>165</v>
+      </c>
+      <c r="S12" s="118"/>
+    </row>
+    <row r="13" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="133"/>
+      <c r="B13" s="216"/>
+      <c r="C13" s="211" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="212" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="211">
+        <v>8</v>
+      </c>
+      <c r="F13" s="211">
+        <v>30</v>
+      </c>
+      <c r="G13" s="211"/>
+      <c r="H13" s="211"/>
+      <c r="I13" s="211"/>
+      <c r="J13" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>contraseñaResidente</v>
+      </c>
+      <c r="K13" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="212" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" s="211">
+        <v>8</v>
+      </c>
+      <c r="N13" s="211">
+        <v>30</v>
+      </c>
+      <c r="O13" s="213"/>
+      <c r="P13" s="213"/>
+      <c r="Q13" s="214"/>
+      <c r="R13" s="215" t="s">
+        <v>166</v>
+      </c>
+      <c r="S13" s="118"/>
+    </row>
+    <row r="14" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="133"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="211" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="E14" s="211"/>
+      <c r="F14" s="211"/>
+      <c r="G14" s="211"/>
+      <c r="H14" s="211"/>
+      <c r="I14" s="211"/>
+      <c r="J14" s="212" t="str">
+        <f t="shared" si="0"/>
+        <v>inmuebleResidente</v>
+      </c>
+      <c r="K14" s="212"/>
+      <c r="L14" s="213"/>
+      <c r="M14" s="213"/>
+      <c r="N14" s="213"/>
+      <c r="O14" s="213"/>
+      <c r="P14" s="213"/>
+      <c r="Q14" s="214"/>
+      <c r="R14" s="215"/>
+      <c r="S14" s="118"/>
+    </row>
+    <row r="15" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="133"/>
+      <c r="B15" s="136" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D15" s="202" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="51">
-        <v>32</v>
-      </c>
-      <c r="F5" s="51">
-        <v>32</v>
-      </c>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51" t="str">
-        <f>_xlfn.CONCAT(C5,$B$5)</f>
+      <c r="E15" s="74">
+        <v>32</v>
+      </c>
+      <c r="F15" s="74">
+        <v>32</v>
+      </c>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74" t="str">
+        <f>_xlfn.CONCAT(C15,$B$15)</f>
         <v>identificadorInmueble</v>
       </c>
-      <c r="K5" s="51" t="s">
+      <c r="K15" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="51" t="s">
+      <c r="L15" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="M5" s="51">
-        <v>32</v>
-      </c>
-      <c r="N5" s="51">
-        <v>32</v>
-      </c>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="69" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",A5,".")</f>
+      <c r="M15" s="74">
+        <v>32</v>
+      </c>
+      <c r="N15" s="74">
+        <v>32</v>
+      </c>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="198"/>
+      <c r="R15" s="68" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C15," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S5" s="120" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="139"/>
-      <c r="B6" s="142"/>
-      <c r="C6" s="58" t="s">
+      <c r="S15" s="118"/>
+    </row>
+    <row r="16" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="133"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D16" s="203" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E16" s="51">
         <v>1</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F16" s="51">
         <v>50</v>
       </c>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51" t="str">
-        <f>_xlfn.CONCAT(C6,$B$5)</f>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51" t="str">
+        <f>_xlfn.CONCAT(C16,$B$15)</f>
         <v>numeroViviendaInmueble</v>
       </c>
-      <c r="K6" s="51" t="s">
+      <c r="K16" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="L6" s="51" t="s">
+      <c r="L16" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="M6" s="51">
+      <c r="M16" s="51">
         <v>1</v>
       </c>
-      <c r="N6" s="51">
+      <c r="N16" s="51">
         <v>50</v>
       </c>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="69" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B5,"  en el contexto de ",A5,".")</f>
+      <c r="O16" s="51"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="52"/>
+      <c r="R16" s="68" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del numeroVivienda del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S6" s="120"/>
-    </row>
-    <row r="7" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="139"/>
-      <c r="B7" s="142"/>
-      <c r="C7" s="62" t="s">
+      <c r="S16" s="118"/>
+    </row>
+    <row r="17" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="133"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D17" s="204" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="120"/>
-    </row>
-    <row r="8" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="139"/>
-      <c r="B8" s="143"/>
-      <c r="C8" s="62" t="s">
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="51"/>
+      <c r="M17" s="51"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="51"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="52"/>
+      <c r="R17" s="68"/>
+      <c r="S17" s="118"/>
+    </row>
+    <row r="18" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="133"/>
+      <c r="B18" s="137"/>
+      <c r="C18" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D18" s="204" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="52"/>
-      <c r="R8" s="69"/>
-      <c r="S8" s="120"/>
-    </row>
-    <row r="9" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="139"/>
-      <c r="B9" s="133" t="s">
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="51"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="51"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="52"/>
+      <c r="R18" s="68"/>
+      <c r="S18" s="118"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="133"/>
+      <c r="B19" s="193" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C19" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D19" s="205" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="31">
-        <v>32</v>
-      </c>
-      <c r="F9" s="31">
-        <v>32</v>
-      </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31" t="str">
-        <f>_xlfn.CONCAT(C9,$B$9)</f>
+      <c r="E19" s="31">
+        <v>32</v>
+      </c>
+      <c r="F19" s="31">
+        <v>32</v>
+      </c>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31" t="str">
+        <f>_xlfn.CONCAT(C19,$B$19)</f>
         <v>identificadorTipoInmueble</v>
       </c>
-      <c r="K9" s="31" t="s">
+      <c r="K19" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="31" t="s">
+      <c r="L19" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="M9" s="31">
-        <v>32</v>
-      </c>
-      <c r="N9" s="31">
-        <v>32</v>
-      </c>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="53"/>
-      <c r="R9" s="63" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C9," del objeto dominio ",B9,"  en el contexto de ",A5,".")</f>
+      <c r="M19" s="31">
+        <v>32</v>
+      </c>
+      <c r="N19" s="31">
+        <v>32</v>
+      </c>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="63" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C19," del objeto dominio ",B19,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S9" s="120"/>
-    </row>
-    <row r="10" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="139"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="50" t="s">
+      <c r="S19" s="118"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="133"/>
+      <c r="B20" s="194"/>
+      <c r="C20" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D20" s="205" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E20" s="31">
         <v>1</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F20" s="31">
         <v>50</v>
       </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31" t="str">
-        <f t="shared" ref="J10" si="0">_xlfn.CONCAT(C10,$B$9)</f>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31" t="str">
+        <f t="shared" ref="J20" si="1">_xlfn.CONCAT(C20,$B$19)</f>
         <v>nombreTipoInmueble</v>
       </c>
-      <c r="K10" s="31" t="s">
+      <c r="K20" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="31" t="s">
+      <c r="L20" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="31">
+      <c r="M20" s="31">
         <v>1</v>
       </c>
-      <c r="N10" s="31">
+      <c r="N20" s="31">
         <v>50</v>
       </c>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="59" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",A5,".")</f>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="59" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C20," del objeto dominio ",B20,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S10" s="120"/>
-    </row>
-    <row r="11" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="139"/>
-      <c r="B11" s="136" t="s">
+      <c r="S20" s="118"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="133"/>
+      <c r="B21" s="130" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C21" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="56" t="s">
+      <c r="D21" s="206" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="56">
-        <v>32</v>
-      </c>
-      <c r="F11" s="56">
-        <v>32</v>
-      </c>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="56" t="str">
-        <f>_xlfn.CONCAT(C11,$B$11)</f>
+      <c r="E21" s="56">
+        <v>32</v>
+      </c>
+      <c r="F21" s="56">
+        <v>32</v>
+      </c>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56" t="str">
+        <f>_xlfn.CONCAT(C21,$B$21)</f>
         <v>identificadorZonaInmueble</v>
       </c>
-      <c r="K11" s="56" t="s">
+      <c r="K21" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="56" t="s">
+      <c r="L21" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="56">
-        <v>32</v>
-      </c>
-      <c r="N11" s="56">
-        <v>32</v>
-      </c>
-      <c r="O11" s="56"/>
-      <c r="P11" s="56"/>
-      <c r="Q11" s="57"/>
-      <c r="R11" s="60" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C11," del objeto dominio ",B11,"  en el contexto de ",A3,".")</f>
+      <c r="M21" s="56">
+        <v>32</v>
+      </c>
+      <c r="N21" s="56">
+        <v>32</v>
+      </c>
+      <c r="O21" s="56"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="60" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C21," del objeto dominio ",B21,"  en el contexto de ",A3,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Caracterización Origen.</v>
       </c>
-      <c r="S11" s="120"/>
-    </row>
-    <row r="12" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="139"/>
-      <c r="B12" s="137"/>
-      <c r="C12" s="55" t="s">
+      <c r="S21" s="118"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="133"/>
+      <c r="B22" s="131"/>
+      <c r="C22" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="D22" s="206" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E22" s="56">
         <v>1</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F22" s="56">
         <v>20</v>
       </c>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56">
+      <c r="G22" s="56"/>
+      <c r="H22" s="56">
         <v>1</v>
       </c>
-      <c r="I12" s="56">
+      <c r="I22" s="56">
         <v>200</v>
       </c>
-      <c r="J12" s="56" t="str">
-        <f>_xlfn.CONCAT(C12,$B$11)</f>
+      <c r="J22" s="56" t="str">
+        <f>_xlfn.CONCAT(C22,$B$21)</f>
         <v>numeroZonaInmuebleZonaInmueble</v>
       </c>
-      <c r="K12" s="56" t="s">
+      <c r="K22" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="56" t="s">
+      <c r="L22" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="M12" s="56">
+      <c r="M22" s="56">
         <v>1</v>
       </c>
-      <c r="N12" s="56">
+      <c r="N22" s="56">
         <v>20</v>
       </c>
-      <c r="O12" s="56"/>
-      <c r="P12" s="56">
+      <c r="O22" s="56"/>
+      <c r="P22" s="56">
         <v>1</v>
       </c>
-      <c r="Q12" s="57">
+      <c r="Q22" s="57">
         <v>200</v>
       </c>
-      <c r="R12" s="60" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C12," del objeto dominio ",B12,"  en el contexto de ",A4,".")</f>
+      <c r="R22" s="60" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C22," del objeto dominio ",B22,"  en el contexto de ",A4,".")</f>
         <v>Atributo que contiene la informacion del numeroZonaInmueble del objeto dominio   en el contexto de Contexto.</v>
       </c>
-      <c r="S12" s="120"/>
-    </row>
-    <row r="13" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="139"/>
-      <c r="B13" s="137"/>
-      <c r="C13" s="55" t="s">
+      <c r="S22" s="118"/>
+    </row>
+    <row r="23" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="133"/>
+      <c r="B23" s="131"/>
+      <c r="C23" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="D23" s="207" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="56"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="56"/>
-      <c r="Q13" s="57"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="120"/>
-    </row>
-    <row r="14" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="139"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="55" t="s">
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="118"/>
+    </row>
+    <row r="24" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="133"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="71" t="s">
+      <c r="D24" s="207" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="56"/>
-      <c r="L14" s="56"/>
-      <c r="M14" s="56"/>
-      <c r="N14" s="56"/>
-      <c r="O14" s="56"/>
-      <c r="P14" s="56"/>
-      <c r="Q14" s="57"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="120"/>
-    </row>
-    <row r="15" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="139"/>
-      <c r="B15" s="134" t="s">
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="56"/>
+      <c r="Q24" s="57"/>
+      <c r="R24" s="60"/>
+      <c r="S24" s="118"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="133"/>
+      <c r="B25" s="128" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C25" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="65" t="s">
+      <c r="D25" s="208" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="65">
-        <v>32</v>
-      </c>
-      <c r="F15" s="65">
-        <v>32</v>
-      </c>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="65" t="str">
-        <f>_xlfn.CONCAT(C15,$B$15)</f>
+      <c r="E25" s="65">
+        <v>32</v>
+      </c>
+      <c r="F25" s="65">
+        <v>32</v>
+      </c>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65" t="str">
+        <f>_xlfn.CONCAT(C25,$B$25)</f>
         <v>identificadorTipoZonaInmueble</v>
       </c>
-      <c r="K15" s="65" t="s">
+      <c r="K25" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="65" t="s">
+      <c r="L25" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="M15" s="65">
-        <v>32</v>
-      </c>
-      <c r="N15" s="65">
-        <v>32</v>
-      </c>
-      <c r="O15" s="65"/>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="67" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C15," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
+      <c r="M25" s="65">
+        <v>32</v>
+      </c>
+      <c r="N25" s="65">
+        <v>32</v>
+      </c>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="67" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C25," del objeto dominio ",B25,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio TipoZonaInmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S15" s="120"/>
-    </row>
-    <row r="16" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="139"/>
-      <c r="B16" s="135"/>
-      <c r="C16" s="64" t="s">
+      <c r="S25" s="118"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="133"/>
+      <c r="B26" s="129"/>
+      <c r="C26" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D26" s="208" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E26" s="65">
         <v>1</v>
       </c>
-      <c r="F16" s="65">
+      <c r="F26" s="65">
         <v>50</v>
       </c>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="65" t="str">
-        <f>_xlfn.CONCAT(C16,$B$15)</f>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65" t="str">
+        <f>_xlfn.CONCAT(C26,$B$25)</f>
         <v>nombreTipoZonaInmueble</v>
       </c>
-      <c r="K16" s="65" t="s">
+      <c r="K26" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="L16" s="65" t="s">
+      <c r="L26" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="65">
+      <c r="M26" s="65">
         <v>1</v>
       </c>
-      <c r="N16" s="65">
+      <c r="N26" s="65">
         <v>50</v>
       </c>
-      <c r="O16" s="65"/>
-      <c r="P16" s="65"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="67" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",A5,".")</f>
+      <c r="O26" s="65"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="67" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C26," del objeto dominio ",B26,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S16" s="120"/>
-    </row>
-    <row r="17" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="139"/>
-      <c r="B17" s="132" t="s">
+      <c r="S26" s="118"/>
+    </row>
+    <row r="27" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="133"/>
+      <c r="B27" s="154" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C27" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D27" s="209" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="32">
-        <v>32</v>
-      </c>
-      <c r="F17" s="32">
-        <v>32</v>
-      </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32" t="str">
-        <f>_xlfn.CONCAT(C9,$B$17)</f>
+      <c r="E27" s="32">
+        <v>32</v>
+      </c>
+      <c r="F27" s="32">
+        <v>32</v>
+      </c>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32" t="str">
+        <f>_xlfn.CONCAT(C19,$B$27)</f>
         <v>identificadorConjuntoResidencial</v>
       </c>
-      <c r="K17" s="32" t="s">
+      <c r="K27" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L17" s="32" t="s">
+      <c r="L27" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="M17" s="32">
-        <v>32</v>
-      </c>
-      <c r="N17" s="32">
-        <v>32</v>
-      </c>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="61" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",A5,".")</f>
+      <c r="M27" s="32">
+        <v>32</v>
+      </c>
+      <c r="N27" s="32">
+        <v>32</v>
+      </c>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="54"/>
+      <c r="R27" s="61" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C27," del objeto dominio ",B27,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S17" s="120"/>
-    </row>
-    <row r="18" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="140"/>
-      <c r="B18" s="132"/>
-      <c r="C18" s="32" t="s">
+      <c r="S27" s="118"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="134"/>
+      <c r="B28" s="154"/>
+      <c r="C28" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D28" s="209" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E28" s="32">
         <v>1</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F28" s="32">
         <v>50</v>
       </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32" t="str">
-        <f>_xlfn.CONCAT(C10,$B$17)</f>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32" t="str">
+        <f>_xlfn.CONCAT(C20,$B$27)</f>
         <v>nombreConjuntoResidencial</v>
       </c>
-      <c r="K18" s="32" t="s">
+      <c r="K28" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="L18" s="32" t="s">
+      <c r="L28" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="M18" s="32">
+      <c r="M28" s="32">
         <v>1</v>
       </c>
-      <c r="N18" s="32">
+      <c r="N28" s="32">
         <v>50</v>
       </c>
-      <c r="O18" s="32"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="54"/>
-      <c r="R18" s="61" t="str">
-        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C18," del objeto dominio ",B18,"  en el contexto de ",A5,".")</f>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="61" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C28," del objeto dominio ",B28,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S18" s="121"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="E25" s="72"/>
+      <c r="S28" s="119"/>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E35" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="S5:S18"/>
+  <mergeCells count="14">
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="A5:A18"/>
-    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="A5:A28"/>
+    <mergeCell ref="S5:S28"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D8" location="'Residente ConjutosResidenciales'!B8" display="TipoInmueble" xr:uid="{7D0F26B2-16BB-4D32-9316-813C92F956E5}"/>
-    <hyperlink ref="D13" location="'Conjuntos Residenciales'!B13" display="TipoZonaInmueble" xr:uid="{34181B3B-B9AE-4560-8F56-BDA0D6B05CD0}"/>
-    <hyperlink ref="D14" location="'Conjuntos Residenciales'!B16" display="ConjuntoResidencial" xr:uid="{A2395E41-D8AC-474A-BE9C-32FCADDD0F2C}"/>
-    <hyperlink ref="D7" location="'Conjuntos Residenciales'!B10" display="ZonaInmueble" xr:uid="{E001D96D-791E-43A6-B8BA-893283B14284}"/>
+    <hyperlink ref="D18" location="'Residente ConjutosResidenciales'!B8" display="TipoInmueble" xr:uid="{7D0F26B2-16BB-4D32-9316-813C92F956E5}"/>
+    <hyperlink ref="D23" location="'Conjuntos Residenciales'!B13" display="TipoZonaInmueble" xr:uid="{34181B3B-B9AE-4560-8F56-BDA0D6B05CD0}"/>
+    <hyperlink ref="D24" location="'Conjuntos Residenciales'!B16" display="ConjuntoResidencial" xr:uid="{A2395E41-D8AC-474A-BE9C-32FCADDD0F2C}"/>
+    <hyperlink ref="D17" location="'Conjuntos Residenciales'!B10" display="ZonaInmueble" xr:uid="{E001D96D-791E-43A6-B8BA-893283B14284}"/>
+    <hyperlink ref="D14" location="'Conjuntos.R Residentes-0001'!B18" display="Inmueble" xr:uid="{ABDB1C96-86D5-49B8-9762-2546EB75E837}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5095,112 +5996,112 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAA1C796-BDF1-44E4-8EC8-5B53FD905390}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="38.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="38.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="64" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="13"/>
+    <col min="7" max="16384" width="11.44140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="109" t="str">
+      <c r="B1" s="107" t="str">
         <f>Contextos!B12</f>
         <v>Agendas</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="110"/>
-    </row>
-    <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="108"/>
+    </row>
+    <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="111" t="str">
+      <c r="B2" s="109" t="str">
         <f>Contextos!D12</f>
         <v>Contexto cuya motivación es la de gestionar la estructura de la agenda que va a tener una zona común durante un un tiempo estimado y sus diferentes turnos.</v>
       </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="112"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="110"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="113" t="str">
+      <c r="B3" s="111" t="str">
         <f>Contextos!A12</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="114"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="115" t="s">
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="117"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="115"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="118" t="s">
+      <c r="C5" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="118"/>
-      <c r="F5" s="119" t="s">
+      <c r="E5" s="116"/>
+      <c r="F5" s="117" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="119"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="116"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="117"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="118"/>
+      <c r="C7" s="116"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="119"/>
-    </row>
-    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F7" s="117"/>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>103</v>
       </c>
@@ -5222,7 +6123,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>64</v>
       </c>
@@ -5274,109 +6175,1322 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C7A5B2-A8EA-4155-AEAF-F8A5FDEA4D7E}">
+  <dimension ref="A1:S30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="58" style="26" customWidth="1"/>
+    <col min="19" max="19" width="17.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.44140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="120" t="str">
+        <f>Agendas!D9</f>
+        <v>Turno Agenda-0001</v>
+      </c>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="121"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="113"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="115"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="123" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="124"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="148" t="s">
+        <v>29</v>
+      </c>
+      <c r="S3" s="150" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="P4" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" s="149"/>
+      <c r="S4" s="151"/>
+    </row>
+    <row r="5" spans="1:19" ht="28.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="170" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="171" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="172" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="172" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="172">
+        <v>32</v>
+      </c>
+      <c r="F5" s="172">
+        <v>32</v>
+      </c>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="172" t="str">
+        <f>_xlfn.CONCAT(C5,$B$5)</f>
+        <v>identificadorTurno</v>
+      </c>
+      <c r="K5" s="173" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="173" t="s">
+        <v>137</v>
+      </c>
+      <c r="M5" s="173">
+        <v>32</v>
+      </c>
+      <c r="N5" s="173">
+        <v>32</v>
+      </c>
+      <c r="O5" s="173"/>
+      <c r="P5" s="173"/>
+      <c r="Q5" s="173"/>
+      <c r="R5" s="174" t="s">
+        <v>138</v>
+      </c>
+      <c r="S5" s="175" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="170"/>
+      <c r="B6" s="171"/>
+      <c r="C6" s="176" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="172" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="172">
+        <v>1</v>
+      </c>
+      <c r="F6" s="172">
+        <v>50</v>
+      </c>
+      <c r="G6" s="172"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="172"/>
+      <c r="J6" s="172" t="str">
+        <f t="shared" ref="J6:J10" si="0">_xlfn.CONCAT(C6,$B$5)</f>
+        <v>numeroTurnoTurno</v>
+      </c>
+      <c r="K6" s="173" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="173" t="s">
+        <v>58</v>
+      </c>
+      <c r="M6" s="173">
+        <v>1</v>
+      </c>
+      <c r="N6" s="173">
+        <v>50</v>
+      </c>
+      <c r="O6" s="173"/>
+      <c r="P6" s="173"/>
+      <c r="Q6" s="173"/>
+      <c r="R6" s="174" t="s">
+        <v>139</v>
+      </c>
+      <c r="S6" s="175"/>
+    </row>
+    <row r="7" spans="1:19" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="170"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="172" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="172" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="172"/>
+      <c r="F7" s="172"/>
+      <c r="G7" s="172"/>
+      <c r="H7" s="172"/>
+      <c r="I7" s="172"/>
+      <c r="J7" s="172" t="str">
+        <f t="shared" si="0"/>
+        <v>horaInicioTurno</v>
+      </c>
+      <c r="K7" s="173" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="173" t="s">
+        <v>131</v>
+      </c>
+      <c r="M7" s="173"/>
+      <c r="N7" s="173"/>
+      <c r="O7" s="173"/>
+      <c r="P7" s="173"/>
+      <c r="Q7" s="173"/>
+      <c r="R7" s="174" t="s">
+        <v>140</v>
+      </c>
+      <c r="S7" s="175"/>
+    </row>
+    <row r="8" spans="1:19" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="170"/>
+      <c r="B8" s="171"/>
+      <c r="C8" s="172" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="172" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="172"/>
+      <c r="F8" s="172"/>
+      <c r="G8" s="172"/>
+      <c r="H8" s="172"/>
+      <c r="I8" s="172"/>
+      <c r="J8" s="172" t="str">
+        <f t="shared" si="0"/>
+        <v>horaFinTurno</v>
+      </c>
+      <c r="K8" s="173" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="173" t="s">
+        <v>131</v>
+      </c>
+      <c r="M8" s="173"/>
+      <c r="N8" s="173"/>
+      <c r="O8" s="173"/>
+      <c r="P8" s="173"/>
+      <c r="Q8" s="173"/>
+      <c r="R8" s="174" t="s">
+        <v>141</v>
+      </c>
+      <c r="S8" s="175"/>
+    </row>
+    <row r="9" spans="1:19" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="170"/>
+      <c r="B9" s="171"/>
+      <c r="C9" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="172" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="172"/>
+      <c r="F9" s="172"/>
+      <c r="G9" s="172"/>
+      <c r="H9" s="172"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172" t="str">
+        <f t="shared" si="0"/>
+        <v>estadoTurno</v>
+      </c>
+      <c r="K9" s="173" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="173" t="s">
+        <v>134</v>
+      </c>
+      <c r="M9" s="173"/>
+      <c r="N9" s="173"/>
+      <c r="O9" s="173"/>
+      <c r="P9" s="173"/>
+      <c r="Q9" s="173"/>
+      <c r="R9" s="174" t="s">
+        <v>142</v>
+      </c>
+      <c r="S9" s="175"/>
+    </row>
+    <row r="10" spans="1:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="170"/>
+      <c r="B10" s="171"/>
+      <c r="C10" s="177" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="178" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="172"/>
+      <c r="F10" s="172"/>
+      <c r="G10" s="172"/>
+      <c r="H10" s="172"/>
+      <c r="I10" s="172"/>
+      <c r="J10" s="172" t="str">
+        <f>_xlfn.CONCAT(C10,$B$5)</f>
+        <v>agendaTurno</v>
+      </c>
+      <c r="K10" s="173" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="173" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="173"/>
+      <c r="N10" s="173"/>
+      <c r="O10" s="173"/>
+      <c r="P10" s="173"/>
+      <c r="Q10" s="173"/>
+      <c r="R10" s="174" t="s">
+        <v>143</v>
+      </c>
+      <c r="S10" s="175"/>
+    </row>
+    <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="170"/>
+      <c r="B11" s="179" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="169" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="169" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="169">
+        <v>32</v>
+      </c>
+      <c r="F11" s="169">
+        <v>32</v>
+      </c>
+      <c r="G11" s="169"/>
+      <c r="H11" s="169"/>
+      <c r="I11" s="169"/>
+      <c r="J11" s="169" t="str">
+        <f>_xlfn.CONCAT(C11,$B$11)</f>
+        <v>identificadorAgenda</v>
+      </c>
+      <c r="K11" s="169" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="169" t="s">
+        <v>137</v>
+      </c>
+      <c r="M11" s="169">
+        <v>32</v>
+      </c>
+      <c r="N11" s="169">
+        <v>32</v>
+      </c>
+      <c r="O11" s="169"/>
+      <c r="P11" s="169"/>
+      <c r="Q11" s="169"/>
+      <c r="R11" s="169" t="s">
+        <v>145</v>
+      </c>
+      <c r="S11" s="175"/>
+    </row>
+    <row r="12" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="170"/>
+      <c r="B12" s="179"/>
+      <c r="C12" s="169" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="169" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="169">
+        <v>1</v>
+      </c>
+      <c r="F12" s="169">
+        <v>50</v>
+      </c>
+      <c r="G12" s="169"/>
+      <c r="H12" s="169"/>
+      <c r="I12" s="169"/>
+      <c r="J12" s="169" t="str">
+        <f t="shared" ref="J12:J16" si="1">_xlfn.CONCAT(C12,$B$11)</f>
+        <v>nombreAgenda</v>
+      </c>
+      <c r="K12" s="169" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="169" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="169">
+        <v>1</v>
+      </c>
+      <c r="N12" s="169">
+        <v>50</v>
+      </c>
+      <c r="O12" s="169"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="169"/>
+      <c r="R12" s="180" t="s">
+        <v>146</v>
+      </c>
+      <c r="S12" s="175"/>
+    </row>
+    <row r="13" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="170"/>
+      <c r="B13" s="179"/>
+      <c r="C13" s="169" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="169" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="169"/>
+      <c r="F13" s="169"/>
+      <c r="G13" s="169"/>
+      <c r="H13" s="169"/>
+      <c r="I13" s="169"/>
+      <c r="J13" s="169" t="str">
+        <f t="shared" si="1"/>
+        <v>disponibilidadAgenda</v>
+      </c>
+      <c r="K13" s="169" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="169" t="s">
+        <v>134</v>
+      </c>
+      <c r="M13" s="169"/>
+      <c r="N13" s="169"/>
+      <c r="O13" s="169"/>
+      <c r="P13" s="169"/>
+      <c r="Q13" s="169"/>
+      <c r="R13" s="180" t="s">
+        <v>147</v>
+      </c>
+      <c r="S13" s="175"/>
+    </row>
+    <row r="14" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="170"/>
+      <c r="B14" s="179"/>
+      <c r="C14" s="169" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="169" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="169"/>
+      <c r="F14" s="169"/>
+      <c r="G14" s="169"/>
+      <c r="H14" s="169"/>
+      <c r="I14" s="169"/>
+      <c r="J14" s="169" t="str">
+        <f t="shared" si="1"/>
+        <v>fechaHoraInicioAgenda</v>
+      </c>
+      <c r="K14" s="169" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="169" t="s">
+        <v>131</v>
+      </c>
+      <c r="M14" s="169"/>
+      <c r="N14" s="169"/>
+      <c r="O14" s="169"/>
+      <c r="P14" s="191"/>
+      <c r="Q14" s="169"/>
+      <c r="R14" s="180" t="s">
+        <v>148</v>
+      </c>
+      <c r="S14" s="175"/>
+    </row>
+    <row r="15" spans="1:19" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="170"/>
+      <c r="B15" s="179"/>
+      <c r="C15" s="169" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="169" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="169"/>
+      <c r="F15" s="169"/>
+      <c r="G15" s="169"/>
+      <c r="H15" s="169"/>
+      <c r="I15" s="169"/>
+      <c r="J15" s="169" t="str">
+        <f t="shared" si="1"/>
+        <v>fechaHoraFinAgenda</v>
+      </c>
+      <c r="K15" s="169" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="169" t="s">
+        <v>131</v>
+      </c>
+      <c r="M15" s="169"/>
+      <c r="N15" s="169"/>
+      <c r="O15" s="169"/>
+      <c r="P15" s="169"/>
+      <c r="Q15" s="169"/>
+      <c r="R15" s="169" t="s">
+        <v>149</v>
+      </c>
+      <c r="S15" s="175"/>
+    </row>
+    <row r="16" spans="1:19" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="170"/>
+      <c r="B16" s="179"/>
+      <c r="C16" s="169" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="192" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="169"/>
+      <c r="F16" s="169"/>
+      <c r="G16" s="169"/>
+      <c r="H16" s="169"/>
+      <c r="I16" s="169"/>
+      <c r="J16" s="169" t="str">
+        <f t="shared" si="1"/>
+        <v>zonaComunAgenda</v>
+      </c>
+      <c r="K16" s="169" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="169" t="s">
+        <v>41</v>
+      </c>
+      <c r="M16" s="169"/>
+      <c r="N16" s="169"/>
+      <c r="O16" s="169"/>
+      <c r="P16" s="169"/>
+      <c r="Q16" s="169"/>
+      <c r="R16" s="180" t="s">
+        <v>150</v>
+      </c>
+      <c r="S16" s="175"/>
+    </row>
+    <row r="17" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="170"/>
+      <c r="B17" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="182" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="182" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="182">
+        <v>32</v>
+      </c>
+      <c r="F17" s="182">
+        <v>32</v>
+      </c>
+      <c r="G17" s="182"/>
+      <c r="H17" s="182"/>
+      <c r="I17" s="182"/>
+      <c r="J17" s="182" t="str">
+        <f>_xlfn.CONCAT(C17,$B$17)</f>
+        <v>identificadorZonaComun</v>
+      </c>
+      <c r="K17" s="182" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="182" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="182">
+        <v>32</v>
+      </c>
+      <c r="N17" s="182">
+        <v>32</v>
+      </c>
+      <c r="O17" s="182"/>
+      <c r="P17" s="182"/>
+      <c r="Q17" s="182"/>
+      <c r="R17" s="183" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaComun  en el contexto de Agendas.</v>
+      </c>
+      <c r="S17" s="175"/>
+    </row>
+    <row r="18" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="170"/>
+      <c r="B18" s="181"/>
+      <c r="C18" s="182" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="182" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="182">
+        <v>3</v>
+      </c>
+      <c r="F18" s="182">
+        <v>50</v>
+      </c>
+      <c r="G18" s="182"/>
+      <c r="H18" s="182"/>
+      <c r="I18" s="182"/>
+      <c r="J18" s="182" t="str">
+        <f t="shared" ref="J18:J30" si="2">_xlfn.CONCAT(C18,$B$17)</f>
+        <v>NombreZonaComun</v>
+      </c>
+      <c r="K18" s="182" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="182" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="182">
+        <v>3</v>
+      </c>
+      <c r="N18" s="182">
+        <v>50</v>
+      </c>
+      <c r="O18" s="182"/>
+      <c r="P18" s="182"/>
+      <c r="Q18" s="182"/>
+      <c r="R18" s="183" t="str">
+        <f t="shared" ref="R18:R22" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C18," del objeto dominio ",B18,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S18" s="175"/>
+    </row>
+    <row r="19" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="170"/>
+      <c r="B19" s="181"/>
+      <c r="C19" s="182" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="182">
+        <v>1</v>
+      </c>
+      <c r="F19" s="182">
+        <v>4</v>
+      </c>
+      <c r="G19" s="182"/>
+      <c r="H19" s="182"/>
+      <c r="I19" s="182"/>
+      <c r="J19" s="182" t="str">
+        <f t="shared" si="2"/>
+        <v>capacidadPersonasZonaComun</v>
+      </c>
+      <c r="K19" s="182" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="M19" s="182">
+        <v>1</v>
+      </c>
+      <c r="N19" s="182">
+        <v>4</v>
+      </c>
+      <c r="O19" s="182"/>
+      <c r="P19" s="182"/>
+      <c r="Q19" s="182"/>
+      <c r="R19" s="183" t="str">
+        <f t="shared" si="3"/>
+        <v>Atributo que contiene la informacion del capacidadPersonas del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S19" s="175"/>
+    </row>
+    <row r="20" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="170"/>
+      <c r="B20" s="181"/>
+      <c r="C20" s="182" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="182" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="182">
+        <v>0</v>
+      </c>
+      <c r="F20" s="182">
+        <v>255</v>
+      </c>
+      <c r="G20" s="182"/>
+      <c r="H20" s="182"/>
+      <c r="I20" s="182"/>
+      <c r="J20" s="182" t="str">
+        <f t="shared" si="2"/>
+        <v>descripcionZonaComun</v>
+      </c>
+      <c r="K20" s="182" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="182" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="182">
+        <v>0</v>
+      </c>
+      <c r="N20" s="182">
+        <v>255</v>
+      </c>
+      <c r="O20" s="182"/>
+      <c r="P20" s="182"/>
+      <c r="Q20" s="182"/>
+      <c r="R20" s="183" t="str">
+        <f t="shared" si="3"/>
+        <v>Atributo que contiene la informacion del descripcion del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S20" s="175"/>
+    </row>
+    <row r="21" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="170"/>
+      <c r="B21" s="181"/>
+      <c r="C21" s="182" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="182" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="182">
+        <v>0</v>
+      </c>
+      <c r="F21" s="182">
+        <v>5000</v>
+      </c>
+      <c r="G21" s="182"/>
+      <c r="H21" s="182"/>
+      <c r="I21" s="182"/>
+      <c r="J21" s="182" t="str">
+        <f t="shared" si="2"/>
+        <v>normasZonaComun</v>
+      </c>
+      <c r="K21" s="182" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="182" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="182">
+        <v>0</v>
+      </c>
+      <c r="N21" s="182">
+        <v>5000</v>
+      </c>
+      <c r="O21" s="182"/>
+      <c r="P21" s="182"/>
+      <c r="Q21" s="182"/>
+      <c r="R21" s="183" t="str">
+        <f t="shared" si="3"/>
+        <v>Atributo que contiene la informacion del normas del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S21" s="175"/>
+    </row>
+    <row r="22" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="170"/>
+      <c r="B22" s="181"/>
+      <c r="C22" s="182" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="182">
+        <v>1</v>
+      </c>
+      <c r="F22" s="182">
+        <v>5</v>
+      </c>
+      <c r="G22" s="182"/>
+      <c r="H22" s="182">
+        <v>0</v>
+      </c>
+      <c r="I22" s="182">
+        <v>3600</v>
+      </c>
+      <c r="J22" s="182" t="str">
+        <f t="shared" si="2"/>
+        <v>tiempoUsoZonaComun</v>
+      </c>
+      <c r="K22" s="182" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="M22" s="182">
+        <v>1</v>
+      </c>
+      <c r="N22" s="182">
+        <v>5</v>
+      </c>
+      <c r="O22" s="182"/>
+      <c r="P22" s="182">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="182">
+        <v>3600</v>
+      </c>
+      <c r="R22" s="183" t="str">
+        <f t="shared" si="3"/>
+        <v>Atributo que contiene la informacion del tiempoUso del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S22" s="175"/>
+    </row>
+    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="170"/>
+      <c r="B23" s="181"/>
+      <c r="C23" s="182" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="184" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="182"/>
+      <c r="F23" s="182"/>
+      <c r="G23" s="182"/>
+      <c r="H23" s="182"/>
+      <c r="I23" s="182"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="182"/>
+      <c r="L23" s="182"/>
+      <c r="M23" s="182"/>
+      <c r="N23" s="182"/>
+      <c r="O23" s="182"/>
+      <c r="P23" s="182"/>
+      <c r="Q23" s="182"/>
+      <c r="R23" s="183"/>
+      <c r="S23" s="175"/>
+    </row>
+    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="170"/>
+      <c r="B24" s="181"/>
+      <c r="C24" s="182" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="184" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="182"/>
+      <c r="F24" s="182"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="182"/>
+      <c r="I24" s="182"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="182"/>
+      <c r="N24" s="182"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="182"/>
+      <c r="Q24" s="182"/>
+      <c r="R24" s="183"/>
+      <c r="S24" s="175"/>
+    </row>
+    <row r="25" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="170"/>
+      <c r="B25" s="185" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="186" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="186" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="186">
+        <v>32</v>
+      </c>
+      <c r="F25" s="186">
+        <v>32</v>
+      </c>
+      <c r="G25" s="186"/>
+      <c r="H25" s="186"/>
+      <c r="I25" s="186"/>
+      <c r="J25" s="186" t="str">
+        <f>_xlfn.CONCAT(C25,$B$25)</f>
+        <v>identificadorUnidadTiempoUso</v>
+      </c>
+      <c r="K25" s="186" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="186" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="186">
+        <v>32</v>
+      </c>
+      <c r="N25" s="186">
+        <v>32</v>
+      </c>
+      <c r="O25" s="186"/>
+      <c r="P25" s="186"/>
+      <c r="Q25" s="186"/>
+      <c r="R25" s="187" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C25," del objeto dominio ",B25,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio UnidadTiempoUso  en el contexto de Agendas.</v>
+      </c>
+      <c r="S25" s="175"/>
+    </row>
+    <row r="26" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="170"/>
+      <c r="B26" s="185"/>
+      <c r="C26" s="186" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="186" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="186">
+        <v>3</v>
+      </c>
+      <c r="F26" s="186">
+        <v>50</v>
+      </c>
+      <c r="G26" s="186"/>
+      <c r="H26" s="186"/>
+      <c r="I26" s="186"/>
+      <c r="J26" s="186" t="str">
+        <f t="shared" ref="J26:J28" si="4">_xlfn.CONCAT(C26,$B$25)</f>
+        <v>nombreUnidadTiempoUso</v>
+      </c>
+      <c r="K26" s="186" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="186" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26" s="186">
+        <v>3</v>
+      </c>
+      <c r="N26" s="186">
+        <v>50</v>
+      </c>
+      <c r="O26" s="186"/>
+      <c r="P26" s="186"/>
+      <c r="Q26" s="186"/>
+      <c r="R26" s="187" t="str">
+        <f t="shared" ref="R26:R28" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C26," del objeto dominio ",B26,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S26" s="175"/>
+    </row>
+    <row r="27" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="170"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="186" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="186" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="186">
+        <v>1</v>
+      </c>
+      <c r="F27" s="186">
+        <v>3</v>
+      </c>
+      <c r="G27" s="186"/>
+      <c r="H27" s="186"/>
+      <c r="I27" s="186"/>
+      <c r="J27" s="186" t="str">
+        <f t="shared" si="4"/>
+        <v>abreviaturaUnidadTiempoUso</v>
+      </c>
+      <c r="K27" s="186" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="186" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" s="186">
+        <v>1</v>
+      </c>
+      <c r="N27" s="186">
+        <v>3</v>
+      </c>
+      <c r="O27" s="186"/>
+      <c r="P27" s="186"/>
+      <c r="Q27" s="186"/>
+      <c r="R27" s="187" t="str">
+        <f t="shared" si="5"/>
+        <v>Atributo que contiene la informacion del abreviatura del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S27" s="175"/>
+    </row>
+    <row r="28" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="170"/>
+      <c r="B28" s="185"/>
+      <c r="C28" s="186" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="186" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="186">
+        <v>4</v>
+      </c>
+      <c r="F28" s="186">
+        <v>5</v>
+      </c>
+      <c r="G28" s="186"/>
+      <c r="H28" s="186"/>
+      <c r="I28" s="186"/>
+      <c r="J28" s="186" t="str">
+        <f t="shared" si="4"/>
+        <v>enBaseUnidadTiempoUso</v>
+      </c>
+      <c r="K28" s="186" t="s">
+        <v>59</v>
+      </c>
+      <c r="L28" s="186" t="s">
+        <v>107</v>
+      </c>
+      <c r="M28" s="186">
+        <v>4</v>
+      </c>
+      <c r="N28" s="186">
+        <v>5</v>
+      </c>
+      <c r="O28" s="186"/>
+      <c r="P28" s="186"/>
+      <c r="Q28" s="186"/>
+      <c r="R28" s="187" t="str">
+        <f t="shared" si="5"/>
+        <v>Atributo que contiene la informacion del enBase del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S28" s="175"/>
+    </row>
+    <row r="29" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="170"/>
+      <c r="B29" s="188" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="189" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="189" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="189">
+        <v>32</v>
+      </c>
+      <c r="F29" s="189">
+        <v>32</v>
+      </c>
+      <c r="G29" s="189"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="189"/>
+      <c r="J29" s="189" t="str">
+        <f>_xlfn.CONCAT(C29,$B$29)</f>
+        <v>identificadorConjuntoResidencial</v>
+      </c>
+      <c r="K29" s="189" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="189" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="189">
+        <v>32</v>
+      </c>
+      <c r="N29" s="189">
+        <v>32</v>
+      </c>
+      <c r="O29" s="189"/>
+      <c r="P29" s="189"/>
+      <c r="Q29" s="189"/>
+      <c r="R29" s="190" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C29," del objeto dominio ",B29,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Agendas.</v>
+      </c>
+      <c r="S29" s="175"/>
+    </row>
+    <row r="30" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="170"/>
+      <c r="B30" s="188"/>
+      <c r="C30" s="189" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="189" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="189">
+        <v>1</v>
+      </c>
+      <c r="F30" s="189">
+        <v>50</v>
+      </c>
+      <c r="G30" s="189"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="189"/>
+      <c r="J30" s="189" t="str">
+        <f>_xlfn.CONCAT(C30,$B$29)</f>
+        <v>nombreConjuntoResidencial</v>
+      </c>
+      <c r="K30" s="189" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" s="189" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="189">
+        <v>1</v>
+      </c>
+      <c r="N30" s="189">
+        <v>50</v>
+      </c>
+      <c r="O30" s="189"/>
+      <c r="P30" s="189"/>
+      <c r="Q30" s="189"/>
+      <c r="R30" s="190" t="str">
+        <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C30," del objeto dominio ",B30,"  en el contexto de ",$A$5,".")</f>
+        <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Agendas.</v>
+      </c>
+      <c r="S30" s="175"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="A5:A30"/>
+    <mergeCell ref="S5:S30"/>
+    <mergeCell ref="B5:B10"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" location="Residente!A12" display="identificador" xr:uid="{80169430-9A83-40F6-BE78-C9769A7F908B}"/>
+    <hyperlink ref="D10" location="'Turno Agenda-0001'!B16" display="Agenda" xr:uid="{E1929EA4-A6B8-4029-BD9C-AD457B98DF86}"/>
+    <hyperlink ref="D23" location="'Turno Agenda-0001'!B28" display="UnidadTiempoUso" xr:uid="{97677138-903B-4D54-A186-3863CA1355FF}"/>
+    <hyperlink ref="D24" location="'Turno Agenda-0001'!B30" display="ConjuntoResidencial" xr:uid="{556D781E-3892-4B9C-B5A1-AB4E5826C218}"/>
+    <hyperlink ref="D16" location="'Turno Agenda-0001'!B23" display="ZonaComun" xr:uid="{88D75804-7AEF-42DC-949C-FB570282EA2F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{285DCF13-A122-49FD-BB4E-83BC928CCAC1}">
   <dimension ref="A1:S18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="13" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="31" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="13" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="58" style="26" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="13"/>
+    <col min="19" max="19" width="17.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.44140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="122" t="str">
+      <c r="B1" s="120" t="str">
         <f>Agendas!D8</f>
         <v>Agenda ConjuntosResidenciales-0001</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="123"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="117"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="125" t="s">
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="121"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="113"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="115"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="144" t="s">
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="124"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="148" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="146" t="s">
+      <c r="S3" s="150" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="29" t="s">
         <v>28</v>
       </c>
@@ -5428,14 +7542,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="145"/>
-      <c r="S4" s="147"/>
-    </row>
-    <row r="5" spans="1:19" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="R4" s="149"/>
+      <c r="S4" s="151"/>
+    </row>
+    <row r="5" spans="1:19" ht="28.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="138" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="142" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -5472,17 +7586,17 @@
       <c r="O5" s="51"/>
       <c r="P5" s="51"/>
       <c r="Q5" s="52"/>
-      <c r="R5" s="69" t="str">
+      <c r="R5" s="68" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaComun  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S5" s="151" t="s">
+      <c r="S5" s="141" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="149"/>
-      <c r="B6" s="153"/>
+    <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="139"/>
+      <c r="B6" s="143"/>
       <c r="C6" s="51" t="s">
         <v>4</v>
       </c>
@@ -5499,7 +7613,7 @@
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
       <c r="J6" s="51" t="str">
-        <f t="shared" ref="J6:J16" si="0">_xlfn.CONCAT(C6,$B$5)</f>
+        <f t="shared" ref="J6:J10" si="0">_xlfn.CONCAT(C6,$B$5)</f>
         <v>NombreZonaComun</v>
       </c>
       <c r="K6" s="51" t="s">
@@ -5517,15 +7631,15 @@
       <c r="O6" s="51"/>
       <c r="P6" s="51"/>
       <c r="Q6" s="52"/>
-      <c r="R6" s="69" t="str">
+      <c r="R6" s="68" t="str">
         <f t="shared" ref="R6:R10" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S6" s="151"/>
-    </row>
-    <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="149"/>
-      <c r="B7" s="153"/>
+      <c r="S6" s="141"/>
+    </row>
+    <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="139"/>
+      <c r="B7" s="143"/>
       <c r="C7" s="51" t="s">
         <v>95</v>
       </c>
@@ -5560,15 +7674,15 @@
       <c r="O7" s="51"/>
       <c r="P7" s="51"/>
       <c r="Q7" s="52"/>
-      <c r="R7" s="69" t="str">
+      <c r="R7" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del capacidadPersonas del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S7" s="151"/>
-    </row>
-    <row r="8" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="149"/>
-      <c r="B8" s="153"/>
+      <c r="S7" s="141"/>
+    </row>
+    <row r="8" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="139"/>
+      <c r="B8" s="143"/>
       <c r="C8" s="51" t="s">
         <v>108</v>
       </c>
@@ -5603,15 +7717,15 @@
       <c r="O8" s="51"/>
       <c r="P8" s="51"/>
       <c r="Q8" s="52"/>
-      <c r="R8" s="69" t="str">
+      <c r="R8" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del descripcion del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S8" s="151"/>
-    </row>
-    <row r="9" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="149"/>
-      <c r="B9" s="153"/>
+      <c r="S8" s="141"/>
+    </row>
+    <row r="9" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="139"/>
+      <c r="B9" s="143"/>
       <c r="C9" s="51" t="s">
         <v>136</v>
       </c>
@@ -5646,15 +7760,15 @@
       <c r="O9" s="51"/>
       <c r="P9" s="51"/>
       <c r="Q9" s="52"/>
-      <c r="R9" s="69" t="str">
+      <c r="R9" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del normas del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S9" s="151"/>
-    </row>
-    <row r="10" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="149"/>
-      <c r="B10" s="153"/>
+      <c r="S9" s="141"/>
+    </row>
+    <row r="10" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="139"/>
+      <c r="B10" s="143"/>
       <c r="C10" s="51" t="s">
         <v>96</v>
       </c>
@@ -5697,19 +7811,19 @@
       <c r="Q10" s="52">
         <v>3600</v>
       </c>
-      <c r="R10" s="69" t="str">
+      <c r="R10" s="68" t="str">
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del tiempoUso del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S10" s="151"/>
-    </row>
-    <row r="11" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="149"/>
-      <c r="B11" s="153"/>
+      <c r="S10" s="141"/>
+    </row>
+    <row r="11" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="139"/>
+      <c r="B11" s="143"/>
       <c r="C11" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="70" t="s">
+      <c r="D11" s="69" t="s">
         <v>104</v>
       </c>
       <c r="E11" s="51"/>
@@ -5725,16 +7839,16 @@
       <c r="O11" s="51"/>
       <c r="P11" s="51"/>
       <c r="Q11" s="52"/>
-      <c r="R11" s="69"/>
-      <c r="S11" s="151"/>
-    </row>
-    <row r="12" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="149"/>
-      <c r="B12" s="154"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="141"/>
+    </row>
+    <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="139"/>
+      <c r="B12" s="144"/>
       <c r="C12" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="69" t="s">
         <v>61</v>
       </c>
       <c r="E12" s="51"/>
@@ -5750,186 +7864,186 @@
       <c r="O12" s="51"/>
       <c r="P12" s="51"/>
       <c r="Q12" s="52"/>
-      <c r="R12" s="69"/>
-      <c r="S12" s="151"/>
-    </row>
-    <row r="13" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="149"/>
-      <c r="B13" s="155" t="s">
+      <c r="R12" s="68"/>
+      <c r="S12" s="141"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="139"/>
+      <c r="B13" s="145" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="73">
-        <v>32</v>
-      </c>
-      <c r="F13" s="73">
-        <v>32</v>
-      </c>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73" t="str">
+      <c r="E13" s="71">
+        <v>32</v>
+      </c>
+      <c r="F13" s="71">
+        <v>32</v>
+      </c>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71" t="str">
         <f>_xlfn.CONCAT(C13,$B$13)</f>
         <v>identificadorUnidadTiempoUso</v>
       </c>
-      <c r="K13" s="73" t="s">
+      <c r="K13" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="73" t="s">
+      <c r="L13" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="M13" s="73">
-        <v>32</v>
-      </c>
-      <c r="N13" s="73">
-        <v>32</v>
-      </c>
-      <c r="O13" s="73"/>
-      <c r="P13" s="73"/>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="75" t="str">
+      <c r="M13" s="71">
+        <v>32</v>
+      </c>
+      <c r="N13" s="71">
+        <v>32</v>
+      </c>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C13," del objeto dominio ",B13,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio UnidadTiempoUso  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S13" s="151"/>
-    </row>
-    <row r="14" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="149"/>
-      <c r="B14" s="156"/>
-      <c r="C14" s="73" t="s">
+      <c r="S13" s="141"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="139"/>
+      <c r="B14" s="146"/>
+      <c r="C14" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="73">
+      <c r="E14" s="71">
         <v>3</v>
       </c>
-      <c r="F14" s="73">
+      <c r="F14" s="71">
         <v>50</v>
       </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73" t="str">
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71" t="str">
         <f t="shared" ref="J14:J16" si="2">_xlfn.CONCAT(C14,$B$13)</f>
         <v>nombreUnidadTiempoUso</v>
       </c>
-      <c r="K14" s="73" t="s">
+      <c r="K14" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="L14" s="73" t="s">
+      <c r="L14" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="73">
+      <c r="M14" s="71">
         <v>3</v>
       </c>
-      <c r="N14" s="73">
+      <c r="N14" s="71">
         <v>50</v>
       </c>
-      <c r="O14" s="73"/>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="75" t="str">
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73" t="str">
         <f t="shared" ref="R14:R16" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C14," del objeto dominio ",B14,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S14" s="151"/>
-    </row>
-    <row r="15" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="149"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="73" t="s">
+      <c r="S14" s="141"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="139"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="73" t="s">
+      <c r="D15" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="73">
+      <c r="E15" s="71">
         <v>1</v>
       </c>
-      <c r="F15" s="73">
+      <c r="F15" s="71">
         <v>3</v>
       </c>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73" t="str">
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71" t="str">
         <f t="shared" si="2"/>
         <v>abreviaturaUnidadTiempoUso</v>
       </c>
-      <c r="K15" s="73" t="s">
+      <c r="K15" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="73" t="s">
+      <c r="L15" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="M15" s="73">
+      <c r="M15" s="71">
         <v>1</v>
       </c>
-      <c r="N15" s="73">
+      <c r="N15" s="71">
         <v>3</v>
       </c>
-      <c r="O15" s="73"/>
-      <c r="P15" s="73"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="75" t="str">
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del abreviatura del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S15" s="151"/>
-    </row>
-    <row r="16" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="149"/>
-      <c r="B16" s="157"/>
-      <c r="C16" s="73" t="s">
+      <c r="S15" s="141"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="139"/>
+      <c r="B16" s="147"/>
+      <c r="C16" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="73" t="s">
+      <c r="D16" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="73">
+      <c r="E16" s="71">
         <v>4</v>
       </c>
-      <c r="F16" s="73">
+      <c r="F16" s="71">
         <v>5</v>
       </c>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="73" t="str">
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71" t="str">
         <f t="shared" si="2"/>
         <v>enBaseUnidadTiempoUso</v>
       </c>
-      <c r="K16" s="73" t="s">
+      <c r="K16" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="L16" s="73" t="s">
+      <c r="L16" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="M16" s="73">
+      <c r="M16" s="71">
         <v>4</v>
       </c>
-      <c r="N16" s="73">
+      <c r="N16" s="71">
         <v>5</v>
       </c>
-      <c r="O16" s="73"/>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="75" t="str">
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del enBase del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S16" s="151"/>
-    </row>
-    <row r="17" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="149"/>
-      <c r="B17" s="132" t="s">
+      <c r="S16" s="141"/>
+    </row>
+    <row r="17" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="139"/>
+      <c r="B17" s="127" t="s">
         <v>61</v>
       </c>
       <c r="C17" s="32" t="s">
@@ -5970,11 +8084,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S17" s="151"/>
-    </row>
-    <row r="18" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="150"/>
-      <c r="B18" s="132"/>
+      <c r="S17" s="141"/>
+    </row>
+    <row r="18" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="140"/>
+      <c r="B18" s="127"/>
       <c r="C18" s="32" t="s">
         <v>57</v>
       </c>
@@ -6013,21 +8127,21 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C18," del objeto dominio ",B18,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S18" s="151"/>
+      <c r="S18" s="141"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A5:A18"/>
-    <mergeCell ref="S5:S18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B5:B12"/>
-    <mergeCell ref="B13:B16"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
+    <mergeCell ref="A5:A18"/>
+    <mergeCell ref="S5:S18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B5:B12"/>
+    <mergeCell ref="B13:B16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" location="'Agenda ConjuntosResidenciales-0'!B13" display="UnidadTiempoUso" xr:uid="{7145F6A3-A24A-4F31-B98A-658FB31AEB42}"/>
@@ -6035,187 +8149,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C088BE7-88A8-46E0-AF18-6F40B3F602F8}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="109" t="str">
-        <f>Contextos!B15</f>
-        <v>Reservas</v>
-      </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="110"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="111" t="str">
-        <f>Contextos!D15</f>
-        <v>Contexto cuya intención enfocarse en la gestión del proceso de reservas de los recursos, incluyendo la disponibilidad de los recursos y las reservas que los residentes realizan.</v>
-      </c>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="112"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="113" t="str">
-        <f>Contextos!A15</f>
-        <v>Core/Básico</v>
-      </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="114"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="115" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="117"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="118" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="118" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="118"/>
-      <c r="F5" s="119" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="119"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="118"/>
-      <c r="D7" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="119"/>
-    </row>
-    <row r="8" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="48" t="str">
-        <f>B8&amp;"-0001"</f>
-        <v>Reserva-0001</v>
-      </c>
-      <c r="E8" s="49" t="str">
-        <f t="shared" ref="E8:E9" si="0">_xlfn.CONCAT(A8," de ",B8)</f>
-        <v>Agendas de Reserva</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="20" t="str">
-        <f>B9&amp;"-0002"</f>
-        <v>Reserva-0002</v>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v>Residentes de Reserva</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:F7"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="D8" location="'Reserva-0001'!A1" display="'Reserva-0001'!A1" xr:uid="{2CD27129-3F8D-4A69-AE6D-74455A97C54B}"/>
-    <hyperlink ref="D9" location="'Reserva-0002'!A1" display="'Reserva-0002'!A1" xr:uid="{6CE586E2-B2DF-423C-BBAA-EB08E79D1E9C}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E124A45D-ECAC-4EEC-9BB6-8B4657FFF3C6}">
-          <x14:formula1>
-            <xm:f>Valores!$A$7:$A$13</xm:f>
-          </x14:formula1>
-          <xm:sqref>C8:C9</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
 </file>
--- a/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C3761F-3DAB-485F-9781-84D5F338B409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A3C368-59A1-4926-BAFA-AB5BF8B373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
   </bookViews>
@@ -1283,7 +1283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1513,291 +1513,9 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1806,9 +1524,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1818,129 +1533,411 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2380,10 +2377,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="78"/>
+      <c r="B1" s="111"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -2497,50 +2494,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="107" t="str">
+      <c r="B1" s="140" t="str">
         <f>Contextos!B15</f>
         <v>Reservas</v>
       </c>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="141"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="109" t="str">
+      <c r="B2" s="142" t="str">
         <f>Contextos!D15</f>
         <v>Contexto cuya intención enfocarse en la gestión del proceso de reservas de los recursos, incluyendo la disponibilidad de los recursos y las reservas que los residentes realizan.</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="110"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="143"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="111" t="str">
+      <c r="B3" s="144" t="str">
         <f>Contextos!A15</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="112"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="145"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="113" t="s">
+      <c r="A4" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="115"/>
+      <c r="B4" s="147"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="148"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -2549,14 +2546,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117" t="s">
+      <c r="E5" s="149"/>
+      <c r="F5" s="150" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2567,10 +2564,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+      <c r="F6" s="150"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -2579,14 +2576,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="116"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="117"/>
+      <c r="F7" s="150"/>
     </row>
     <row r="8" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
@@ -2693,75 +2690,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="120" t="str">
+      <c r="B1" s="151" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="121"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="152"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="115"/>
+      <c r="A2" s="146"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="148"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="186" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124" t="s">
+      <c r="B3" s="187"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="187"/>
+      <c r="H3" s="187"/>
+      <c r="I3" s="187"/>
+      <c r="J3" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="124"/>
-      <c r="O3" s="124"/>
-      <c r="P3" s="124"/>
-      <c r="Q3" s="124"/>
-      <c r="R3" s="148" t="s">
+      <c r="K3" s="187"/>
+      <c r="L3" s="187"/>
+      <c r="M3" s="187"/>
+      <c r="N3" s="187"/>
+      <c r="O3" s="187"/>
+      <c r="P3" s="187"/>
+      <c r="Q3" s="187"/>
+      <c r="R3" s="188" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="150" t="s">
+      <c r="S3" s="190" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2817,14 +2814,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="155"/>
-      <c r="S4" s="151"/>
+      <c r="R4" s="205"/>
+      <c r="S4" s="191"/>
     </row>
     <row r="5" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="175" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="135" t="s">
+      <c r="B5" s="208" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -2865,13 +2862,13 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificadorConjuntoResidencial del objeto dominio ZonaComun  en el contexto de Agendas.</v>
       </c>
-      <c r="S5" s="152" t="s">
+      <c r="S5" s="203" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="133"/>
-      <c r="B6" s="136"/>
+      <c r="A6" s="175"/>
+      <c r="B6" s="169"/>
       <c r="C6" s="51" t="s">
         <v>119</v>
       </c>
@@ -2910,11 +2907,11 @@
         <f t="shared" ref="R6:R15" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombreConjuntoResidencial del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S6" s="152"/>
+      <c r="S6" s="203"/>
     </row>
     <row r="7" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="133"/>
-      <c r="B7" s="136"/>
+      <c r="A7" s="175"/>
+      <c r="B7" s="169"/>
       <c r="C7" s="51" t="s">
         <v>120</v>
       </c>
@@ -2953,11 +2950,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del identificadorUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S7" s="152"/>
+      <c r="S7" s="203"/>
     </row>
     <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="133"/>
-      <c r="B8" s="136"/>
+      <c r="A8" s="175"/>
+      <c r="B8" s="169"/>
       <c r="C8" s="51" t="s">
         <v>121</v>
       </c>
@@ -2996,11 +2993,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del nombreUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S8" s="152"/>
+      <c r="S8" s="203"/>
     </row>
     <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="133"/>
-      <c r="B9" s="136"/>
+      <c r="A9" s="175"/>
+      <c r="B9" s="169"/>
       <c r="C9" s="51" t="s">
         <v>122</v>
       </c>
@@ -3039,11 +3036,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del abreviaturaUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S9" s="152"/>
+      <c r="S9" s="203"/>
     </row>
     <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="133"/>
-      <c r="B10" s="136"/>
+      <c r="A10" s="175"/>
+      <c r="B10" s="169"/>
       <c r="C10" s="74" t="s">
         <v>123</v>
       </c>
@@ -3082,11 +3079,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del enBaseUnidadTiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S10" s="152"/>
+      <c r="S10" s="203"/>
     </row>
     <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="133"/>
-      <c r="B11" s="136"/>
+      <c r="A11" s="175"/>
+      <c r="B11" s="169"/>
       <c r="C11" s="74" t="s">
         <v>124</v>
       </c>
@@ -3125,11 +3122,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del IdentificadorZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S11" s="152"/>
+      <c r="S11" s="203"/>
     </row>
     <row r="12" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="133"/>
-      <c r="B12" s="136"/>
+      <c r="A12" s="175"/>
+      <c r="B12" s="169"/>
       <c r="C12" s="74" t="s">
         <v>125</v>
       </c>
@@ -3168,11 +3165,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del nombreZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S12" s="152"/>
+      <c r="S12" s="203"/>
     </row>
     <row r="13" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="133"/>
-      <c r="B13" s="136"/>
+      <c r="A13" s="175"/>
+      <c r="B13" s="169"/>
       <c r="C13" s="74" t="s">
         <v>126</v>
       </c>
@@ -3211,11 +3208,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del capacidadPersonasZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S13" s="152"/>
+      <c r="S13" s="203"/>
     </row>
     <row r="14" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="133"/>
-      <c r="B14" s="136"/>
+      <c r="A14" s="175"/>
+      <c r="B14" s="169"/>
       <c r="C14" s="74" t="s">
         <v>127</v>
       </c>
@@ -3254,11 +3251,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del decripcionZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S14" s="152"/>
+      <c r="S14" s="203"/>
     </row>
     <row r="15" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="133"/>
-      <c r="B15" s="137"/>
+      <c r="A15" s="175"/>
+      <c r="B15" s="170"/>
       <c r="C15" s="74" t="s">
         <v>128</v>
       </c>
@@ -3305,11 +3302,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del tiempoUsoZonaComun del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S15" s="152"/>
+      <c r="S15" s="203"/>
     </row>
     <row r="16" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="133"/>
-      <c r="B16" s="157" t="s">
+      <c r="A16" s="175"/>
+      <c r="B16" s="207" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="50" t="s">
@@ -3350,11 +3347,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B16,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Agenda  en el contexto de Agendas.</v>
       </c>
-      <c r="S16" s="152"/>
+      <c r="S16" s="203"/>
     </row>
     <row r="17" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="133"/>
-      <c r="B17" s="157"/>
+      <c r="A17" s="175"/>
+      <c r="B17" s="207"/>
       <c r="C17" s="50" t="s">
         <v>4</v>
       </c>
@@ -3393,11 +3390,11 @@
         <f t="shared" ref="R17:R19" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S17" s="152"/>
+      <c r="S17" s="203"/>
     </row>
     <row r="18" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="133"/>
-      <c r="B18" s="157"/>
+      <c r="A18" s="175"/>
+      <c r="B18" s="207"/>
       <c r="C18" s="31" t="s">
         <v>90</v>
       </c>
@@ -3428,11 +3425,11 @@
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del fechaHoraInicio del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S18" s="152"/>
+      <c r="S18" s="203"/>
     </row>
     <row r="19" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="133"/>
-      <c r="B19" s="157"/>
+      <c r="A19" s="175"/>
+      <c r="B19" s="207"/>
       <c r="C19" s="31" t="s">
         <v>94</v>
       </c>
@@ -3463,11 +3460,11 @@
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del fechaHoraFin del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S19" s="152"/>
+      <c r="S19" s="203"/>
     </row>
     <row r="20" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="133"/>
-      <c r="B20" s="157"/>
+      <c r="A20" s="175"/>
+      <c r="B20" s="207"/>
       <c r="C20" s="31" t="s">
         <v>109</v>
       </c>
@@ -3488,11 +3485,11 @@
       <c r="P20" s="31"/>
       <c r="Q20" s="31"/>
       <c r="R20" s="40"/>
-      <c r="S20" s="152"/>
+      <c r="S20" s="203"/>
     </row>
     <row r="21" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="133"/>
-      <c r="B21" s="154" t="s">
+      <c r="A21" s="175"/>
+      <c r="B21" s="161" t="s">
         <v>65</v>
       </c>
       <c r="C21" s="32" t="s">
@@ -3533,11 +3530,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C21," del objeto dominio ",B21,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Turno  en el contexto de Agendas.</v>
       </c>
-      <c r="S21" s="152"/>
+      <c r="S21" s="203"/>
     </row>
     <row r="22" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="133"/>
-      <c r="B22" s="154"/>
+      <c r="A22" s="175"/>
+      <c r="B22" s="161"/>
       <c r="C22" s="32" t="s">
         <v>129</v>
       </c>
@@ -3576,11 +3573,11 @@
         <f t="shared" ref="R22:R25" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C22," del objeto dominio ",B22,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del numeroTurno del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S22" s="152"/>
+      <c r="S22" s="203"/>
     </row>
     <row r="23" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="133"/>
-      <c r="B23" s="154"/>
+      <c r="A23" s="175"/>
+      <c r="B23" s="161"/>
       <c r="C23" s="32" t="s">
         <v>130</v>
       </c>
@@ -3609,11 +3606,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del horaInicio del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S23" s="152"/>
+      <c r="S23" s="203"/>
     </row>
     <row r="24" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="133"/>
-      <c r="B24" s="154"/>
+      <c r="A24" s="175"/>
+      <c r="B24" s="161"/>
       <c r="C24" s="32" t="s">
         <v>132</v>
       </c>
@@ -3642,11 +3639,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del horaFin del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S24" s="152"/>
+      <c r="S24" s="203"/>
     </row>
     <row r="25" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="133"/>
-      <c r="B25" s="154"/>
+      <c r="A25" s="175"/>
+      <c r="B25" s="161"/>
       <c r="C25" s="32" t="s">
         <v>133</v>
       </c>
@@ -3675,11 +3672,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del estado del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S25" s="152"/>
+      <c r="S25" s="203"/>
     </row>
     <row r="26" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="156"/>
-      <c r="B26" s="154"/>
+      <c r="A26" s="206"/>
+      <c r="B26" s="161"/>
       <c r="C26" s="32" t="s">
         <v>110</v>
       </c>
@@ -3700,7 +3697,7 @@
       <c r="P26" s="32"/>
       <c r="Q26" s="32"/>
       <c r="R26" s="41"/>
-      <c r="S26" s="153"/>
+      <c r="S26" s="204"/>
     </row>
     <row r="27" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -3756,75 +3753,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="120" t="str">
+      <c r="B1" s="151" t="str">
         <f>Reservas!D8</f>
         <v>Reserva-0001</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="121"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="152"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="115"/>
+      <c r="A2" s="146"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="148"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="186" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124" t="s">
+      <c r="B3" s="187"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="187"/>
+      <c r="H3" s="187"/>
+      <c r="I3" s="187"/>
+      <c r="J3" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="124"/>
-      <c r="O3" s="124"/>
-      <c r="P3" s="124"/>
-      <c r="Q3" s="124"/>
-      <c r="R3" s="148" t="s">
+      <c r="K3" s="187"/>
+      <c r="L3" s="187"/>
+      <c r="M3" s="187"/>
+      <c r="N3" s="187"/>
+      <c r="O3" s="187"/>
+      <c r="P3" s="187"/>
+      <c r="Q3" s="187"/>
+      <c r="R3" s="188" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="150" t="s">
+      <c r="S3" s="190" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3880,14 +3877,14 @@
       <c r="Q4" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="149"/>
-      <c r="S4" s="151"/>
+      <c r="R4" s="189"/>
+      <c r="S4" s="191"/>
     </row>
     <row r="5" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="209" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="166" t="s">
+      <c r="B5" s="217" t="s">
         <v>82</v>
       </c>
       <c r="C5" s="31" t="s">
@@ -3928,14 +3925,14 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del TipoInmueble(Nombre) del objeto dominio Inmueble  en el contexto de Residentes.</v>
       </c>
-      <c r="S5" s="161" t="str">
+      <c r="S5" s="212" t="str">
         <f>B9</f>
         <v>Residente</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="159"/>
-      <c r="B6" s="167"/>
+      <c r="A6" s="210"/>
+      <c r="B6" s="218"/>
       <c r="C6" s="31" t="s">
         <v>112</v>
       </c>
@@ -3974,11 +3971,11 @@
         <f t="shared" ref="R6:R8" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del TipoZonaInmueble(Identificador) del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S6" s="152"/>
+      <c r="S6" s="203"/>
     </row>
     <row r="7" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="159"/>
-      <c r="B7" s="167"/>
+      <c r="A7" s="210"/>
+      <c r="B7" s="218"/>
       <c r="C7" s="31" t="s">
         <v>113</v>
       </c>
@@ -4017,11 +4014,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del TipoZonaInmueble(Nombre) del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S7" s="152"/>
+      <c r="S7" s="203"/>
     </row>
     <row r="8" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="159"/>
-      <c r="B8" s="168"/>
+      <c r="A8" s="210"/>
+      <c r="B8" s="219"/>
       <c r="C8" s="31" t="s">
         <v>114</v>
       </c>
@@ -4068,11 +4065,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del ZonaInmueble(NumeroZonaInmueble) del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S8" s="152"/>
+      <c r="S8" s="203"/>
     </row>
     <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="159"/>
-      <c r="B9" s="163" t="s">
+      <c r="A9" s="210"/>
+      <c r="B9" s="214" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="32" t="s">
@@ -4113,11 +4110,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C9," del objeto dominio ",B9,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Residente  en el contexto de Residentes.</v>
       </c>
-      <c r="S9" s="152"/>
+      <c r="S9" s="203"/>
     </row>
     <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="159"/>
-      <c r="B10" s="164"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="215"/>
       <c r="C10" s="32" t="s">
         <v>57</v>
       </c>
@@ -4156,11 +4153,11 @@
         <f t="shared" ref="R10:R11" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C10," del objeto dominio ",B10,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S10" s="152"/>
+      <c r="S10" s="203"/>
     </row>
     <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="159"/>
-      <c r="B11" s="164"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="215"/>
       <c r="C11" s="32" t="s">
         <v>117</v>
       </c>
@@ -4199,11 +4196,11 @@
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del numeroDocumento del objeto dominio   en el contexto de Residentes.</v>
       </c>
-      <c r="S11" s="152"/>
+      <c r="S11" s="203"/>
     </row>
     <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="160"/>
-      <c r="B12" s="165"/>
+      <c r="A12" s="211"/>
+      <c r="B12" s="216"/>
       <c r="C12" s="32" t="s">
         <v>115</v>
       </c>
@@ -4224,7 +4221,7 @@
       <c r="P12" s="32"/>
       <c r="Q12" s="32"/>
       <c r="R12" s="41"/>
-      <c r="S12" s="162"/>
+      <c r="S12" s="213"/>
     </row>
     <row r="13" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -4269,29 +4266,29 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88" t="s">
+      <c r="B1" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="89"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="122"/>
     </row>
     <row r="2" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="125"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="95"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="128"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -4308,132 +4305,132 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="99" t="s">
+      <c r="B5" s="132" t="s">
         <v>79</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="100" t="s">
+      <c r="D5" s="133" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="98"/>
-      <c r="B6" s="99"/>
+      <c r="A6" s="131"/>
+      <c r="B6" s="132"/>
       <c r="C6" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="100"/>
+      <c r="D6" s="133"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="98"/>
-      <c r="B7" s="99"/>
+      <c r="A7" s="131"/>
+      <c r="B7" s="132"/>
       <c r="C7" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="100"/>
+      <c r="D7" s="133"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="98"/>
-      <c r="B8" s="99"/>
+      <c r="A8" s="131"/>
+      <c r="B8" s="132"/>
       <c r="C8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="100"/>
+      <c r="D8" s="133"/>
     </row>
     <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
+      <c r="A9" s="131"/>
+      <c r="B9" s="132"/>
       <c r="C9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="100"/>
+      <c r="D9" s="133"/>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="96" t="s">
+      <c r="A10" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="97" t="s">
+      <c r="B10" s="130" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="D10" s="129" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="96"/>
-      <c r="B11" s="97"/>
+      <c r="A11" s="129"/>
+      <c r="B11" s="130"/>
       <c r="C11" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="96"/>
+      <c r="D11" s="129"/>
     </row>
     <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="137" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="101" t="s">
+      <c r="B12" s="134" t="s">
         <v>83</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="104" t="s">
+      <c r="D12" s="137" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="105"/>
-      <c r="B13" s="102"/>
+      <c r="A13" s="138"/>
+      <c r="B13" s="135"/>
       <c r="C13" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="105"/>
+      <c r="D13" s="138"/>
     </row>
     <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="106"/>
-      <c r="B14" s="103"/>
+      <c r="A14" s="139"/>
+      <c r="B14" s="136"/>
       <c r="C14" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="106"/>
+      <c r="D14" s="139"/>
     </row>
     <row r="15" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="79" t="s">
+      <c r="A15" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="82" t="s">
+      <c r="B15" s="115" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="85" t="s">
+      <c r="D15" s="118" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="80"/>
-      <c r="B16" s="83"/>
+      <c r="A16" s="113"/>
+      <c r="B16" s="116"/>
       <c r="C16" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="86"/>
+      <c r="D16" s="119"/>
     </row>
     <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="81"/>
-      <c r="B17" s="84"/>
+      <c r="A17" s="114"/>
+      <c r="B17" s="117"/>
       <c r="C17" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="87"/>
+      <c r="D17" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4505,50 +4502,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="107" t="str">
+      <c r="B1" s="140" t="str">
         <f>Contextos!B5</f>
         <v xml:space="preserve"> Conjuntos residenciales</v>
       </c>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="141"/>
     </row>
     <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="109" t="str">
+      <c r="B2" s="142" t="str">
         <f>Contextos!D5</f>
         <v>Contexto cuya motivación es Gestionar la estructura física y los recursos disponibles en cada conjunto residencial. Aquí se manejan los datos sobre qué conjuntos existen, dónde están ubicados, qué recursos ofrecen según una Agenda con respectivos turnos para cada zona.</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="110"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="143"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="111" t="str">
+      <c r="B3" s="144" t="str">
         <f>Contextos!A5</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="112"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="145"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="113" t="s">
+      <c r="A4" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="115"/>
+      <c r="B4" s="147"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="148"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -4557,14 +4554,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117" t="s">
+      <c r="E5" s="149"/>
+      <c r="F5" s="150" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4575,10 +4572,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+      <c r="F6" s="150"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -4587,14 +4584,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="116"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="117"/>
+      <c r="F7" s="150"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
@@ -4728,50 +4725,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="107" t="str">
+      <c r="B1" s="140" t="str">
         <f>Contextos!B10</f>
         <v>Residentes</v>
       </c>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="141"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="109" t="str">
+      <c r="B2" s="142" t="str">
         <f>Contextos!D10</f>
         <v>Contexto cuya motivación es encargarce de manejar la información de los residentes, incluidas sus identificaciones, contacto, y la relación entre el residente y su residencia dentro del conjunto.</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="110"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="143"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="111" t="str">
+      <c r="B3" s="144" t="str">
         <f>Contextos!A10</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="112"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="145"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="113" t="s">
+      <c r="A4" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="115"/>
+      <c r="B4" s="147"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="148"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -4780,14 +4777,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117" t="s">
+      <c r="E5" s="149"/>
+      <c r="F5" s="150" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4798,10 +4795,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+      <c r="F6" s="150"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -4810,14 +4807,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="116"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="117"/>
+      <c r="F7" s="150"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
@@ -4901,528 +4898,525 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="120" t="str">
+      <c r="B1" s="151" t="str">
         <f>Residentes!D8</f>
         <v>Residente ConjutosResidenciales-0001</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="121"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="152"/>
     </row>
     <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="113"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="122"/>
-      <c r="S2" s="115"/>
+      <c r="A2" s="146"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="153"/>
+      <c r="S2" s="148"/>
     </row>
     <row r="3" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="195" t="s">
+      <c r="A3" s="154" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="196"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="196"/>
-      <c r="I3" s="196"/>
-      <c r="J3" s="196" t="s">
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="196"/>
-      <c r="L3" s="196"/>
-      <c r="M3" s="196"/>
-      <c r="N3" s="196"/>
-      <c r="O3" s="196"/>
-      <c r="P3" s="196"/>
-      <c r="Q3" s="197"/>
-      <c r="R3" s="125" t="s">
+      <c r="K3" s="155"/>
+      <c r="L3" s="155"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="155"/>
+      <c r="O3" s="155"/>
+      <c r="P3" s="155"/>
+      <c r="Q3" s="156"/>
+      <c r="R3" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="219" t="s">
+      <c r="S3" s="159" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="199" t="s">
+      <c r="A4" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="199" t="s">
+      <c r="B4" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="199"/>
-      <c r="E4" s="199" t="s">
+      <c r="D4" s="94"/>
+      <c r="E4" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="199" t="s">
+      <c r="F4" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="199" t="s">
+      <c r="G4" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="199" t="s">
+      <c r="H4" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="199" t="s">
+      <c r="I4" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="199" t="s">
+      <c r="J4" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="K4" s="199" t="s">
+      <c r="K4" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="L4" s="199" t="s">
+      <c r="L4" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="199" t="s">
+      <c r="M4" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="199" t="s">
+      <c r="N4" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="O4" s="199" t="s">
+      <c r="O4" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="P4" s="199" t="s">
+      <c r="P4" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="200" t="s">
+      <c r="Q4" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="126"/>
-      <c r="S4" s="220"/>
+      <c r="R4" s="158"/>
+      <c r="S4" s="160"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="201" t="s">
+      <c r="A5" s="174" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="210" t="s">
+      <c r="B5" s="171" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="211" t="s">
+      <c r="C5" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="212" t="s">
+      <c r="D5" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="211">
-        <v>32</v>
-      </c>
-      <c r="F5" s="211">
-        <v>32</v>
-      </c>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="212" t="str">
+      <c r="E5" s="104">
+        <v>32</v>
+      </c>
+      <c r="F5" s="104">
+        <v>32</v>
+      </c>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="105" t="str">
         <f>_xlfn.CONCAT(C5,$B$5)</f>
         <v>identificadorResidente</v>
       </c>
-      <c r="K5" s="212" t="s">
+      <c r="K5" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="212" t="s">
+      <c r="L5" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="M5" s="211">
-        <v>32</v>
-      </c>
-      <c r="N5" s="211">
-        <v>32</v>
-      </c>
-      <c r="O5" s="213"/>
-      <c r="P5" s="213"/>
-      <c r="Q5" s="214"/>
-      <c r="R5" s="215" t="s">
+      <c r="M5" s="104">
+        <v>32</v>
+      </c>
+      <c r="N5" s="104">
+        <v>32</v>
+      </c>
+      <c r="O5" s="106"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="107"/>
+      <c r="R5" s="108" t="s">
         <v>158</v>
       </c>
-      <c r="S5" s="118" t="s">
+      <c r="S5" s="177" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="133"/>
-      <c r="B6" s="216"/>
-      <c r="C6" s="211" t="s">
+      <c r="A6" s="175"/>
+      <c r="B6" s="172"/>
+      <c r="C6" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="212" t="s">
+      <c r="D6" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="211">
+      <c r="E6" s="104">
         <v>1</v>
       </c>
-      <c r="F6" s="211">
+      <c r="F6" s="104">
         <v>50</v>
       </c>
-      <c r="G6" s="211"/>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="212" t="str">
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="105" t="str">
         <f t="shared" ref="J6:J14" si="0">_xlfn.CONCAT(C6,$B$5)</f>
         <v>nombreResidente</v>
       </c>
-      <c r="K6" s="212" t="s">
+      <c r="K6" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="L6" s="212" t="s">
+      <c r="L6" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="M6" s="211">
+      <c r="M6" s="104">
         <v>1</v>
       </c>
-      <c r="N6" s="211">
+      <c r="N6" s="104">
         <v>50</v>
       </c>
-      <c r="O6" s="213"/>
-      <c r="P6" s="213"/>
-      <c r="Q6" s="214"/>
-      <c r="R6" s="215" t="s">
+      <c r="O6" s="106"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="S6" s="118"/>
+      <c r="S6" s="177"/>
     </row>
     <row r="7" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="133"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="211" t="s">
+      <c r="A7" s="175"/>
+      <c r="B7" s="172"/>
+      <c r="C7" s="104" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="212" t="s">
+      <c r="D7" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="211">
+      <c r="E7" s="104">
         <v>1</v>
       </c>
-      <c r="F7" s="211">
+      <c r="F7" s="104">
         <v>50</v>
       </c>
-      <c r="G7" s="211"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="212" t="str">
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="105" t="str">
         <f t="shared" si="0"/>
         <v>apellidoResidente</v>
       </c>
-      <c r="K7" s="212" t="s">
+      <c r="K7" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="212" t="s">
+      <c r="L7" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="211">
+      <c r="M7" s="104">
         <v>1</v>
       </c>
-      <c r="N7" s="211">
+      <c r="N7" s="104">
         <v>50</v>
       </c>
-      <c r="O7" s="213"/>
-      <c r="P7" s="213"/>
-      <c r="Q7" s="214"/>
-      <c r="R7" s="215" t="s">
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="108" t="s">
         <v>160</v>
       </c>
-      <c r="S7" s="118"/>
+      <c r="S7" s="177"/>
     </row>
     <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="133"/>
-      <c r="B8" s="216"/>
-      <c r="C8" s="211" t="s">
+      <c r="A8" s="175"/>
+      <c r="B8" s="172"/>
+      <c r="C8" s="104" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="212" t="s">
+      <c r="D8" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="211">
+      <c r="E8" s="104">
         <v>1</v>
       </c>
-      <c r="F8" s="211">
+      <c r="F8" s="104">
         <v>50</v>
       </c>
-      <c r="G8" s="211"/>
-      <c r="H8" s="211"/>
-      <c r="I8" s="211"/>
-      <c r="J8" s="212" t="str">
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="105" t="str">
         <f t="shared" si="0"/>
         <v>tipoDocumentoResidente</v>
       </c>
-      <c r="K8" s="212" t="s">
+      <c r="K8" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="212" t="s">
+      <c r="L8" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="M8" s="211">
+      <c r="M8" s="104">
         <v>1</v>
       </c>
-      <c r="N8" s="211">
+      <c r="N8" s="104">
         <v>50</v>
       </c>
-      <c r="O8" s="213"/>
-      <c r="P8" s="213"/>
-      <c r="Q8" s="214"/>
-      <c r="R8" s="215" t="s">
+      <c r="O8" s="106"/>
+      <c r="P8" s="106"/>
+      <c r="Q8" s="107"/>
+      <c r="R8" s="108" t="s">
         <v>161</v>
       </c>
-      <c r="S8" s="118"/>
+      <c r="S8" s="177"/>
     </row>
     <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="133"/>
-      <c r="B9" s="216"/>
-      <c r="C9" s="211" t="s">
+      <c r="A9" s="175"/>
+      <c r="B9" s="172"/>
+      <c r="C9" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="212" t="s">
+      <c r="D9" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="211"/>
-      <c r="F9" s="211"/>
-      <c r="G9" s="211"/>
-      <c r="H9" s="211"/>
-      <c r="I9" s="211"/>
-      <c r="J9" s="212" t="str">
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="105" t="str">
         <f t="shared" si="0"/>
         <v>numeroDocumentoResidente</v>
       </c>
-      <c r="K9" s="212" t="s">
+      <c r="K9" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="212" t="s">
+      <c r="L9" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="M9" s="211"/>
-      <c r="N9" s="211"/>
-      <c r="O9" s="213"/>
-      <c r="P9" s="213"/>
-      <c r="Q9" s="214"/>
-      <c r="R9" s="215" t="s">
+      <c r="M9" s="104"/>
+      <c r="N9" s="104"/>
+      <c r="O9" s="106"/>
+      <c r="P9" s="106"/>
+      <c r="Q9" s="107"/>
+      <c r="R9" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="S9" s="118"/>
+      <c r="S9" s="177"/>
     </row>
     <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="133"/>
-      <c r="B10" s="216"/>
-      <c r="C10" s="211" t="s">
+      <c r="A10" s="175"/>
+      <c r="B10" s="172"/>
+      <c r="C10" s="104" t="s">
         <v>153</v>
       </c>
-      <c r="D10" s="212" t="s">
+      <c r="D10" s="105" t="s">
         <v>154</v>
       </c>
-      <c r="E10" s="211"/>
-      <c r="F10" s="211"/>
-      <c r="G10" s="211"/>
-      <c r="H10" s="211"/>
-      <c r="I10" s="211"/>
-      <c r="J10" s="212" t="str">
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="105" t="str">
         <f t="shared" si="0"/>
         <v>fechaNacimientoResidente</v>
       </c>
-      <c r="K10" s="212" t="s">
+      <c r="K10" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="212" t="s">
+      <c r="L10" s="105" t="s">
         <v>154</v>
       </c>
-      <c r="M10" s="211"/>
-      <c r="N10" s="211"/>
-      <c r="O10" s="213"/>
-      <c r="P10" s="213"/>
-      <c r="Q10" s="214"/>
-      <c r="R10" s="215" t="s">
+      <c r="M10" s="104"/>
+      <c r="N10" s="104"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="106"/>
+      <c r="Q10" s="107"/>
+      <c r="R10" s="108" t="s">
         <v>163</v>
       </c>
-      <c r="S10" s="118"/>
+      <c r="S10" s="177"/>
     </row>
     <row r="11" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="133"/>
-      <c r="B11" s="216"/>
-      <c r="C11" s="211" t="s">
+      <c r="A11" s="175"/>
+      <c r="B11" s="172"/>
+      <c r="C11" s="104" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="212" t="s">
+      <c r="D11" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="E11" s="211"/>
-      <c r="F11" s="211"/>
-      <c r="G11" s="211"/>
-      <c r="H11" s="211"/>
-      <c r="I11" s="211"/>
-      <c r="J11" s="212" t="str">
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="105" t="str">
         <f t="shared" si="0"/>
         <v>numeroContactoResidente</v>
       </c>
-      <c r="K11" s="212" t="s">
+      <c r="K11" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="212" t="s">
+      <c r="L11" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="M11" s="211"/>
-      <c r="N11" s="211"/>
-      <c r="O11" s="213"/>
-      <c r="P11" s="213"/>
-      <c r="Q11" s="214"/>
-      <c r="R11" s="215" t="s">
+      <c r="M11" s="104"/>
+      <c r="N11" s="104"/>
+      <c r="O11" s="106"/>
+      <c r="P11" s="106"/>
+      <c r="Q11" s="107"/>
+      <c r="R11" s="108" t="s">
         <v>164</v>
       </c>
-      <c r="S11" s="118"/>
+      <c r="S11" s="177"/>
     </row>
     <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="133"/>
-      <c r="B12" s="216"/>
-      <c r="C12" s="211" t="s">
+      <c r="A12" s="175"/>
+      <c r="B12" s="172"/>
+      <c r="C12" s="104" t="s">
         <v>156</v>
       </c>
-      <c r="D12" s="212" t="s">
+      <c r="D12" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="E12" s="211">
+      <c r="E12" s="104">
         <v>6</v>
       </c>
-      <c r="F12" s="211">
+      <c r="F12" s="104">
         <v>50</v>
       </c>
-      <c r="G12" s="211"/>
-      <c r="H12" s="211"/>
-      <c r="I12" s="211"/>
-      <c r="J12" s="212" t="str">
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="105" t="str">
         <f t="shared" si="0"/>
         <v>correoElectronicoResidente</v>
       </c>
-      <c r="K12" s="212" t="s">
+      <c r="K12" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="212" t="s">
+      <c r="L12" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="M12" s="211">
+      <c r="M12" s="104">
         <v>6</v>
       </c>
-      <c r="N12" s="211">
+      <c r="N12" s="104">
         <v>50</v>
       </c>
-      <c r="O12" s="213"/>
-      <c r="P12" s="213"/>
-      <c r="Q12" s="214"/>
-      <c r="R12" s="215" t="s">
+      <c r="O12" s="106"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="107"/>
+      <c r="R12" s="108" t="s">
         <v>165</v>
       </c>
-      <c r="S12" s="118"/>
+      <c r="S12" s="177"/>
     </row>
     <row r="13" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="133"/>
-      <c r="B13" s="216"/>
-      <c r="C13" s="211" t="s">
+      <c r="A13" s="175"/>
+      <c r="B13" s="172"/>
+      <c r="C13" s="104" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="212" t="s">
+      <c r="D13" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="211">
+      <c r="E13" s="104">
         <v>8</v>
       </c>
-      <c r="F13" s="211">
+      <c r="F13" s="104">
         <v>30</v>
       </c>
-      <c r="G13" s="211"/>
-      <c r="H13" s="211"/>
-      <c r="I13" s="211"/>
-      <c r="J13" s="212" t="str">
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="105" t="str">
         <f t="shared" si="0"/>
         <v>contraseñaResidente</v>
       </c>
-      <c r="K13" s="212" t="s">
+      <c r="K13" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="212" t="s">
+      <c r="L13" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="M13" s="211">
+      <c r="M13" s="104">
         <v>8</v>
       </c>
-      <c r="N13" s="211">
+      <c r="N13" s="104">
         <v>30</v>
       </c>
-      <c r="O13" s="213"/>
-      <c r="P13" s="213"/>
-      <c r="Q13" s="214"/>
-      <c r="R13" s="215" t="s">
+      <c r="O13" s="106"/>
+      <c r="P13" s="106"/>
+      <c r="Q13" s="107"/>
+      <c r="R13" s="108" t="s">
         <v>166</v>
       </c>
-      <c r="S13" s="118"/>
+      <c r="S13" s="177"/>
     </row>
     <row r="14" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="133"/>
-      <c r="B14" s="217"/>
-      <c r="C14" s="211" t="s">
+      <c r="A14" s="175"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="D14" s="218" t="s">
+      <c r="D14" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="211"/>
-      <c r="F14" s="211"/>
-      <c r="G14" s="211"/>
-      <c r="H14" s="211"/>
-      <c r="I14" s="211"/>
-      <c r="J14" s="212" t="str">
-        <f t="shared" si="0"/>
-        <v>inmuebleResidente</v>
-      </c>
-      <c r="K14" s="212"/>
-      <c r="L14" s="213"/>
-      <c r="M14" s="213"/>
-      <c r="N14" s="213"/>
-      <c r="O14" s="213"/>
-      <c r="P14" s="213"/>
-      <c r="Q14" s="214"/>
-      <c r="R14" s="215"/>
-      <c r="S14" s="118"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="106"/>
+      <c r="P14" s="106"/>
+      <c r="Q14" s="107"/>
+      <c r="R14" s="108"/>
+      <c r="S14" s="177"/>
     </row>
     <row r="15" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="133"/>
-      <c r="B15" s="136" t="s">
+      <c r="A15" s="175"/>
+      <c r="B15" s="169" t="s">
         <v>82</v>
       </c>
       <c r="C15" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="202" t="s">
+      <c r="D15" s="96" t="s">
         <v>56</v>
       </c>
       <c r="E15" s="74">
@@ -5452,20 +5446,20 @@
       </c>
       <c r="O15" s="74"/>
       <c r="P15" s="74"/>
-      <c r="Q15" s="198"/>
+      <c r="Q15" s="93"/>
       <c r="R15" s="68" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C15," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S15" s="118"/>
+      <c r="S15" s="177"/>
     </row>
     <row r="16" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="133"/>
-      <c r="B16" s="136"/>
+      <c r="A16" s="175"/>
+      <c r="B16" s="169"/>
       <c r="C16" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="203" t="s">
+      <c r="D16" s="97" t="s">
         <v>93</v>
       </c>
       <c r="E16" s="51">
@@ -5500,15 +5494,15 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del numeroVivienda del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S16" s="118"/>
+      <c r="S16" s="177"/>
     </row>
     <row r="17" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="133"/>
-      <c r="B17" s="136"/>
+      <c r="A17" s="175"/>
+      <c r="B17" s="169"/>
       <c r="C17" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="204" t="s">
+      <c r="D17" s="98" t="s">
         <v>81</v>
       </c>
       <c r="E17" s="51"/>
@@ -5525,15 +5519,15 @@
       <c r="P17" s="51"/>
       <c r="Q17" s="52"/>
       <c r="R17" s="68"/>
-      <c r="S17" s="118"/>
+      <c r="S17" s="177"/>
     </row>
     <row r="18" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="133"/>
-      <c r="B18" s="137"/>
+      <c r="A18" s="175"/>
+      <c r="B18" s="170"/>
       <c r="C18" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="204" t="s">
+      <c r="D18" s="98" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="51"/>
@@ -5550,17 +5544,17 @@
       <c r="P18" s="51"/>
       <c r="Q18" s="52"/>
       <c r="R18" s="68"/>
-      <c r="S18" s="118"/>
+      <c r="S18" s="177"/>
     </row>
     <row r="19" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="133"/>
-      <c r="B19" s="193" t="s">
+      <c r="A19" s="175"/>
+      <c r="B19" s="162" t="s">
         <v>98</v>
       </c>
       <c r="C19" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="205" t="s">
+      <c r="D19" s="99" t="s">
         <v>56</v>
       </c>
       <c r="E19" s="31">
@@ -5595,15 +5589,15 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C19," del objeto dominio ",B19,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S19" s="118"/>
+      <c r="S19" s="177"/>
     </row>
     <row r="20" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="133"/>
-      <c r="B20" s="194"/>
+      <c r="A20" s="175"/>
+      <c r="B20" s="163"/>
       <c r="C20" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="205" t="s">
+      <c r="D20" s="99" t="s">
         <v>58</v>
       </c>
       <c r="E20" s="31">
@@ -5638,17 +5632,17 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C20," del objeto dominio ",B20,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S20" s="118"/>
+      <c r="S20" s="177"/>
     </row>
     <row r="21" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="133"/>
-      <c r="B21" s="130" t="s">
+      <c r="A21" s="175"/>
+      <c r="B21" s="166" t="s">
         <v>81</v>
       </c>
       <c r="C21" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="206" t="s">
+      <c r="D21" s="100" t="s">
         <v>56</v>
       </c>
       <c r="E21" s="56">
@@ -5683,15 +5677,15 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C21," del objeto dominio ",B21,"  en el contexto de ",A3,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Caracterización Origen.</v>
       </c>
-      <c r="S21" s="118"/>
+      <c r="S21" s="177"/>
     </row>
     <row r="22" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="133"/>
-      <c r="B22" s="131"/>
+      <c r="A22" s="175"/>
+      <c r="B22" s="167"/>
       <c r="C22" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="206" t="s">
+      <c r="D22" s="100" t="s">
         <v>116</v>
       </c>
       <c r="E22" s="56">
@@ -5734,15 +5728,15 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C22," del objeto dominio ",B22,"  en el contexto de ",A4,".")</f>
         <v>Atributo que contiene la informacion del numeroZonaInmueble del objeto dominio   en el contexto de Contexto.</v>
       </c>
-      <c r="S22" s="118"/>
+      <c r="S22" s="177"/>
     </row>
     <row r="23" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="133"/>
-      <c r="B23" s="131"/>
+      <c r="A23" s="175"/>
+      <c r="B23" s="167"/>
       <c r="C23" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="207" t="s">
+      <c r="D23" s="101" t="s">
         <v>99</v>
       </c>
       <c r="E23" s="56"/>
@@ -5759,15 +5753,15 @@
       <c r="P23" s="56"/>
       <c r="Q23" s="57"/>
       <c r="R23" s="60"/>
-      <c r="S23" s="118"/>
+      <c r="S23" s="177"/>
     </row>
     <row r="24" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="133"/>
-      <c r="B24" s="132"/>
+      <c r="A24" s="175"/>
+      <c r="B24" s="168"/>
       <c r="C24" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="207" t="s">
+      <c r="D24" s="101" t="s">
         <v>61</v>
       </c>
       <c r="E24" s="56"/>
@@ -5784,17 +5778,17 @@
       <c r="P24" s="56"/>
       <c r="Q24" s="57"/>
       <c r="R24" s="60"/>
-      <c r="S24" s="118"/>
+      <c r="S24" s="177"/>
     </row>
     <row r="25" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="133"/>
-      <c r="B25" s="128" t="s">
+      <c r="A25" s="175"/>
+      <c r="B25" s="164" t="s">
         <v>99</v>
       </c>
       <c r="C25" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="208" t="s">
+      <c r="D25" s="102" t="s">
         <v>56</v>
       </c>
       <c r="E25" s="65">
@@ -5829,15 +5823,15 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C25," del objeto dominio ",B25,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio TipoZonaInmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S25" s="118"/>
+      <c r="S25" s="177"/>
     </row>
     <row r="26" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="133"/>
-      <c r="B26" s="129"/>
+      <c r="A26" s="175"/>
+      <c r="B26" s="165"/>
       <c r="C26" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="208" t="s">
+      <c r="D26" s="102" t="s">
         <v>58</v>
       </c>
       <c r="E26" s="65">
@@ -5872,17 +5866,17 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C26," del objeto dominio ",B26,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S26" s="118"/>
+      <c r="S26" s="177"/>
     </row>
     <row r="27" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="133"/>
-      <c r="B27" s="154" t="s">
+      <c r="A27" s="175"/>
+      <c r="B27" s="161" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="209" t="s">
+      <c r="D27" s="103" t="s">
         <v>56</v>
       </c>
       <c r="E27" s="32">
@@ -5917,15 +5911,15 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C27," del objeto dominio ",B27,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S27" s="118"/>
+      <c r="S27" s="177"/>
     </row>
     <row r="28" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="134"/>
-      <c r="B28" s="154"/>
+      <c r="A28" s="176"/>
+      <c r="B28" s="161"/>
       <c r="C28" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="209" t="s">
+      <c r="D28" s="103" t="s">
         <v>58</v>
       </c>
       <c r="E28" s="32">
@@ -5960,27 +5954,27 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C28," del objeto dominio ",B28,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S28" s="119"/>
+      <c r="S28" s="178"/>
     </row>
     <row r="35" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E35" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="A5:A28"/>
+    <mergeCell ref="S5:S28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B15:B18"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="A5:A28"/>
-    <mergeCell ref="S5:S28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D18" location="'Residente ConjutosResidenciales'!B8" display="TipoInmueble" xr:uid="{7D0F26B2-16BB-4D32-9316-813C92F956E5}"/>
@@ -6010,50 +6004,50 @@
       <c r="A1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="107" t="str">
+      <c r="B1" s="140" t="str">
         <f>Contextos!B12</f>
         <v>Agendas</v>
       </c>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="141"/>
     </row>
     <row r="2" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="109" t="str">
+      <c r="B2" s="142" t="str">
         <f>Contextos!D12</f>
         <v>Contexto cuya motivación es la de gestionar la estructura de la agenda que va a tener una zona común durante un un tiempo estimado y sus diferentes turnos.</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="110"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="143"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="111" t="str">
+      <c r="B3" s="144" t="str">
         <f>Contextos!A12</f>
         <v>Core/Básico</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="112"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="145"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="113" t="s">
+      <c r="A4" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="115"/>
+      <c r="B4" s="147"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="148"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -6062,14 +6056,14 @@
       <c r="B5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117" t="s">
+      <c r="E5" s="149"/>
+      <c r="F5" s="150" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6080,10 +6074,10 @@
       <c r="B6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+      <c r="F6" s="150"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
@@ -6092,14 +6086,14 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="116"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="16" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="117"/>
+      <c r="F7" s="150"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
@@ -6205,75 +6199,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="120" t="str">
+      <c r="B1" s="151" t="str">
         <f>Agendas!D9</f>
         <v>Turno Agenda-0001</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="121"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="152"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="115"/>
+      <c r="A2" s="146"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="148"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="186" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124" t="s">
+      <c r="B3" s="187"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="187"/>
+      <c r="H3" s="187"/>
+      <c r="I3" s="187"/>
+      <c r="J3" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="124"/>
-      <c r="O3" s="124"/>
-      <c r="P3" s="124"/>
-      <c r="Q3" s="124"/>
-      <c r="R3" s="148" t="s">
+      <c r="K3" s="187"/>
+      <c r="L3" s="187"/>
+      <c r="M3" s="187"/>
+      <c r="N3" s="187"/>
+      <c r="O3" s="187"/>
+      <c r="P3" s="187"/>
+      <c r="Q3" s="187"/>
+      <c r="R3" s="188" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="150" t="s">
+      <c r="S3" s="190" t="s">
         <v>44</v>
       </c>
     </row>
@@ -6329,1039 +6323,1045 @@
       <c r="Q4" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="149"/>
-      <c r="S4" s="151"/>
+      <c r="R4" s="189"/>
+      <c r="S4" s="191"/>
     </row>
     <row r="5" spans="1:19" ht="28.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="170" t="s">
+      <c r="A5" s="181" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="171" t="s">
+      <c r="B5" s="183" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="172" t="s">
+      <c r="C5" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="172" t="s">
+      <c r="D5" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="172">
-        <v>32</v>
-      </c>
-      <c r="F5" s="172">
-        <v>32</v>
-      </c>
-      <c r="G5" s="172"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="172" t="str">
+      <c r="E5" s="78">
+        <v>32</v>
+      </c>
+      <c r="F5" s="78">
+        <v>32</v>
+      </c>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78" t="str">
         <f>_xlfn.CONCAT(C5,$B$5)</f>
         <v>identificadorTurno</v>
       </c>
-      <c r="K5" s="173" t="s">
+      <c r="K5" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="173" t="s">
+      <c r="L5" s="79" t="s">
         <v>137</v>
       </c>
-      <c r="M5" s="173">
-        <v>32</v>
-      </c>
-      <c r="N5" s="173">
-        <v>32</v>
-      </c>
-      <c r="O5" s="173"/>
-      <c r="P5" s="173"/>
-      <c r="Q5" s="173"/>
-      <c r="R5" s="174" t="s">
+      <c r="M5" s="79">
+        <v>32</v>
+      </c>
+      <c r="N5" s="79">
+        <v>32</v>
+      </c>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="S5" s="175" t="s">
+      <c r="S5" s="182" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="170"/>
-      <c r="B6" s="171"/>
-      <c r="C6" s="176" t="s">
+      <c r="A6" s="181"/>
+      <c r="B6" s="183"/>
+      <c r="C6" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="172" t="s">
+      <c r="D6" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="172">
+      <c r="E6" s="78">
         <v>1</v>
       </c>
-      <c r="F6" s="172">
+      <c r="F6" s="78">
         <v>50</v>
       </c>
-      <c r="G6" s="172"/>
-      <c r="H6" s="172"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="172" t="str">
-        <f t="shared" ref="J6:J10" si="0">_xlfn.CONCAT(C6,$B$5)</f>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78" t="str">
+        <f t="shared" ref="J6:J9" si="0">_xlfn.CONCAT(C6,$B$5)</f>
         <v>numeroTurnoTurno</v>
       </c>
-      <c r="K6" s="173" t="s">
+      <c r="K6" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="L6" s="173" t="s">
+      <c r="L6" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="M6" s="173">
+      <c r="M6" s="79">
         <v>1</v>
       </c>
-      <c r="N6" s="173">
+      <c r="N6" s="79">
         <v>50</v>
       </c>
-      <c r="O6" s="173"/>
-      <c r="P6" s="173"/>
-      <c r="Q6" s="173"/>
-      <c r="R6" s="174" t="s">
+      <c r="O6" s="79"/>
+      <c r="P6" s="79"/>
+      <c r="Q6" s="79"/>
+      <c r="R6" s="80" t="s">
         <v>139</v>
       </c>
-      <c r="S6" s="175"/>
+      <c r="S6" s="182"/>
     </row>
     <row r="7" spans="1:19" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="170"/>
-      <c r="B7" s="171"/>
-      <c r="C7" s="172" t="s">
+      <c r="A7" s="181"/>
+      <c r="B7" s="183"/>
+      <c r="C7" s="78" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="172" t="s">
+      <c r="D7" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="172"/>
-      <c r="F7" s="172"/>
-      <c r="G7" s="172"/>
-      <c r="H7" s="172"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172" t="str">
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="78" t="str">
         <f t="shared" si="0"/>
         <v>horaInicioTurno</v>
       </c>
-      <c r="K7" s="173" t="s">
+      <c r="K7" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="173" t="s">
+      <c r="L7" s="79" t="s">
         <v>131</v>
       </c>
-      <c r="M7" s="173"/>
-      <c r="N7" s="173"/>
-      <c r="O7" s="173"/>
-      <c r="P7" s="173"/>
-      <c r="Q7" s="173"/>
-      <c r="R7" s="174" t="s">
+      <c r="M7" s="79"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="79"/>
+      <c r="P7" s="79"/>
+      <c r="Q7" s="79"/>
+      <c r="R7" s="80" t="s">
         <v>140</v>
       </c>
-      <c r="S7" s="175"/>
+      <c r="S7" s="182"/>
     </row>
     <row r="8" spans="1:19" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="170"/>
-      <c r="B8" s="171"/>
-      <c r="C8" s="172" t="s">
+      <c r="A8" s="181"/>
+      <c r="B8" s="183"/>
+      <c r="C8" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="172" t="s">
+      <c r="D8" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="E8" s="172"/>
-      <c r="F8" s="172"/>
-      <c r="G8" s="172"/>
-      <c r="H8" s="172"/>
-      <c r="I8" s="172"/>
-      <c r="J8" s="172" t="str">
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="78" t="str">
         <f t="shared" si="0"/>
         <v>horaFinTurno</v>
       </c>
-      <c r="K8" s="173" t="s">
+      <c r="K8" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="173" t="s">
+      <c r="L8" s="79" t="s">
         <v>131</v>
       </c>
-      <c r="M8" s="173"/>
-      <c r="N8" s="173"/>
-      <c r="O8" s="173"/>
-      <c r="P8" s="173"/>
-      <c r="Q8" s="173"/>
-      <c r="R8" s="174" t="s">
+      <c r="M8" s="79"/>
+      <c r="N8" s="79"/>
+      <c r="O8" s="79"/>
+      <c r="P8" s="79"/>
+      <c r="Q8" s="79"/>
+      <c r="R8" s="80" t="s">
         <v>141</v>
       </c>
-      <c r="S8" s="175"/>
+      <c r="S8" s="182"/>
     </row>
     <row r="9" spans="1:19" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="170"/>
-      <c r="B9" s="171"/>
-      <c r="C9" s="172" t="s">
+      <c r="A9" s="181"/>
+      <c r="B9" s="183"/>
+      <c r="C9" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="172" t="s">
+      <c r="D9" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="E9" s="172"/>
-      <c r="F9" s="172"/>
-      <c r="G9" s="172"/>
-      <c r="H9" s="172"/>
-      <c r="I9" s="172"/>
-      <c r="J9" s="172" t="str">
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="78" t="str">
         <f t="shared" si="0"/>
         <v>estadoTurno</v>
       </c>
-      <c r="K9" s="173" t="s">
+      <c r="K9" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="173" t="s">
+      <c r="L9" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="M9" s="173"/>
-      <c r="N9" s="173"/>
-      <c r="O9" s="173"/>
-      <c r="P9" s="173"/>
-      <c r="Q9" s="173"/>
-      <c r="R9" s="174" t="s">
+      <c r="M9" s="79"/>
+      <c r="N9" s="79"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="79"/>
+      <c r="Q9" s="79"/>
+      <c r="R9" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="S9" s="175"/>
+      <c r="S9" s="182"/>
     </row>
     <row r="10" spans="1:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="170"/>
-      <c r="B10" s="171"/>
-      <c r="C10" s="177" t="s">
+      <c r="A10" s="181"/>
+      <c r="B10" s="183"/>
+      <c r="C10" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="178" t="s">
+      <c r="D10" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="172"/>
-      <c r="F10" s="172"/>
-      <c r="G10" s="172"/>
-      <c r="H10" s="172"/>
-      <c r="I10" s="172"/>
-      <c r="J10" s="172" t="str">
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="78" t="str">
         <f>_xlfn.CONCAT(C10,$B$5)</f>
         <v>agendaTurno</v>
       </c>
-      <c r="K10" s="173" t="s">
+      <c r="K10" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="173" t="s">
+      <c r="L10" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="M10" s="173"/>
-      <c r="N10" s="173"/>
-      <c r="O10" s="173"/>
-      <c r="P10" s="173"/>
-      <c r="Q10" s="173"/>
-      <c r="R10" s="174" t="s">
+      <c r="M10" s="79"/>
+      <c r="N10" s="79"/>
+      <c r="O10" s="79"/>
+      <c r="P10" s="79"/>
+      <c r="Q10" s="79"/>
+      <c r="R10" s="80" t="s">
         <v>143</v>
       </c>
-      <c r="S10" s="175"/>
+      <c r="S10" s="182"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="170"/>
-      <c r="B11" s="179" t="s">
+      <c r="A11" s="181"/>
+      <c r="B11" s="184" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="169" t="s">
+      <c r="C11" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="169" t="s">
+      <c r="D11" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="E11" s="169">
-        <v>32</v>
-      </c>
-      <c r="F11" s="169">
-        <v>32</v>
-      </c>
-      <c r="G11" s="169"/>
-      <c r="H11" s="169"/>
-      <c r="I11" s="169"/>
-      <c r="J11" s="169" t="str">
+      <c r="E11" s="77">
+        <v>32</v>
+      </c>
+      <c r="F11" s="77">
+        <v>32</v>
+      </c>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77" t="str">
         <f>_xlfn.CONCAT(C11,$B$11)</f>
         <v>identificadorAgenda</v>
       </c>
-      <c r="K11" s="169" t="s">
+      <c r="K11" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="169" t="s">
+      <c r="L11" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="M11" s="169">
-        <v>32</v>
-      </c>
-      <c r="N11" s="169">
-        <v>32</v>
-      </c>
-      <c r="O11" s="169"/>
-      <c r="P11" s="169"/>
-      <c r="Q11" s="169"/>
-      <c r="R11" s="169" t="s">
+      <c r="M11" s="77">
+        <v>32</v>
+      </c>
+      <c r="N11" s="77">
+        <v>32</v>
+      </c>
+      <c r="O11" s="77"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="77" t="s">
         <v>145</v>
       </c>
-      <c r="S11" s="175"/>
+      <c r="S11" s="182"/>
     </row>
     <row r="12" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="170"/>
-      <c r="B12" s="179"/>
-      <c r="C12" s="169" t="s">
+      <c r="A12" s="181"/>
+      <c r="B12" s="184"/>
+      <c r="C12" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="169" t="s">
+      <c r="D12" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="169">
+      <c r="E12" s="77">
         <v>1</v>
       </c>
-      <c r="F12" s="169">
+      <c r="F12" s="77">
         <v>50</v>
       </c>
-      <c r="G12" s="169"/>
-      <c r="H12" s="169"/>
-      <c r="I12" s="169"/>
-      <c r="J12" s="169" t="str">
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77" t="str">
         <f t="shared" ref="J12:J16" si="1">_xlfn.CONCAT(C12,$B$11)</f>
         <v>nombreAgenda</v>
       </c>
-      <c r="K12" s="169" t="s">
+      <c r="K12" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="169" t="s">
+      <c r="L12" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="169">
+      <c r="M12" s="77">
         <v>1</v>
       </c>
-      <c r="N12" s="169">
+      <c r="N12" s="77">
         <v>50</v>
       </c>
-      <c r="O12" s="169"/>
-      <c r="P12" s="169"/>
-      <c r="Q12" s="169"/>
-      <c r="R12" s="180" t="s">
+      <c r="O12" s="77"/>
+      <c r="P12" s="77"/>
+      <c r="Q12" s="77"/>
+      <c r="R12" s="84" t="s">
         <v>146</v>
       </c>
-      <c r="S12" s="175"/>
+      <c r="S12" s="182"/>
     </row>
     <row r="13" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="170"/>
-      <c r="B13" s="179"/>
-      <c r="C13" s="169" t="s">
+      <c r="A13" s="181"/>
+      <c r="B13" s="184"/>
+      <c r="C13" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="169" t="s">
+      <c r="D13" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="E13" s="169"/>
-      <c r="F13" s="169"/>
-      <c r="G13" s="169"/>
-      <c r="H13" s="169"/>
-      <c r="I13" s="169"/>
-      <c r="J13" s="169" t="str">
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77" t="str">
         <f t="shared" si="1"/>
         <v>disponibilidadAgenda</v>
       </c>
-      <c r="K13" s="169" t="s">
+      <c r="K13" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="169" t="s">
+      <c r="L13" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="M13" s="169"/>
-      <c r="N13" s="169"/>
-      <c r="O13" s="169"/>
-      <c r="P13" s="169"/>
-      <c r="Q13" s="169"/>
-      <c r="R13" s="180" t="s">
+      <c r="M13" s="77"/>
+      <c r="N13" s="77"/>
+      <c r="O13" s="77"/>
+      <c r="P13" s="77"/>
+      <c r="Q13" s="77"/>
+      <c r="R13" s="84" t="s">
         <v>147</v>
       </c>
-      <c r="S13" s="175"/>
+      <c r="S13" s="182"/>
     </row>
     <row r="14" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="170"/>
-      <c r="B14" s="179"/>
-      <c r="C14" s="169" t="s">
+      <c r="A14" s="181"/>
+      <c r="B14" s="184"/>
+      <c r="C14" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="169" t="s">
+      <c r="D14" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="E14" s="169"/>
-      <c r="F14" s="169"/>
-      <c r="G14" s="169"/>
-      <c r="H14" s="169"/>
-      <c r="I14" s="169"/>
-      <c r="J14" s="169" t="str">
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77" t="str">
         <f t="shared" si="1"/>
         <v>fechaHoraInicioAgenda</v>
       </c>
-      <c r="K14" s="169" t="s">
+      <c r="K14" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="L14" s="169" t="s">
+      <c r="L14" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="M14" s="169"/>
-      <c r="N14" s="169"/>
-      <c r="O14" s="169"/>
-      <c r="P14" s="191"/>
-      <c r="Q14" s="169"/>
-      <c r="R14" s="180" t="s">
+      <c r="M14" s="77"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="77"/>
+      <c r="P14" s="77"/>
+      <c r="Q14" s="77"/>
+      <c r="R14" s="84" t="s">
         <v>148</v>
       </c>
-      <c r="S14" s="175"/>
+      <c r="S14" s="182"/>
     </row>
     <row r="15" spans="1:19" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="170"/>
-      <c r="B15" s="179"/>
-      <c r="C15" s="169" t="s">
+      <c r="A15" s="181"/>
+      <c r="B15" s="184"/>
+      <c r="C15" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="169" t="s">
+      <c r="D15" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="E15" s="169"/>
-      <c r="F15" s="169"/>
-      <c r="G15" s="169"/>
-      <c r="H15" s="169"/>
-      <c r="I15" s="169"/>
-      <c r="J15" s="169" t="str">
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77" t="str">
         <f t="shared" si="1"/>
         <v>fechaHoraFinAgenda</v>
       </c>
-      <c r="K15" s="169" t="s">
+      <c r="K15" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="169" t="s">
+      <c r="L15" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="M15" s="169"/>
-      <c r="N15" s="169"/>
-      <c r="O15" s="169"/>
-      <c r="P15" s="169"/>
-      <c r="Q15" s="169"/>
-      <c r="R15" s="169" t="s">
+      <c r="M15" s="77"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="77"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="77"/>
+      <c r="R15" s="77" t="s">
         <v>149</v>
       </c>
-      <c r="S15" s="175"/>
+      <c r="S15" s="182"/>
     </row>
     <row r="16" spans="1:19" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="170"/>
-      <c r="B16" s="179"/>
-      <c r="C16" s="169" t="s">
+      <c r="A16" s="181"/>
+      <c r="B16" s="184"/>
+      <c r="C16" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="D16" s="192" t="s">
+      <c r="D16" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="169"/>
-      <c r="F16" s="169"/>
-      <c r="G16" s="169"/>
-      <c r="H16" s="169"/>
-      <c r="I16" s="169"/>
-      <c r="J16" s="169" t="str">
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77" t="str">
         <f t="shared" si="1"/>
         <v>zonaComunAgenda</v>
       </c>
-      <c r="K16" s="169" t="s">
+      <c r="K16" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="L16" s="169" t="s">
+      <c r="L16" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="M16" s="169"/>
-      <c r="N16" s="169"/>
-      <c r="O16" s="169"/>
-      <c r="P16" s="169"/>
-      <c r="Q16" s="169"/>
-      <c r="R16" s="180" t="s">
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="84" t="s">
         <v>150</v>
       </c>
-      <c r="S16" s="175"/>
+      <c r="S16" s="182"/>
     </row>
     <row r="17" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="170"/>
-      <c r="B17" s="181" t="s">
+      <c r="A17" s="181"/>
+      <c r="B17" s="185" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="182" t="s">
+      <c r="C17" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="182" t="s">
+      <c r="D17" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="182">
-        <v>32</v>
-      </c>
-      <c r="F17" s="182">
-        <v>32</v>
-      </c>
-      <c r="G17" s="182"/>
-      <c r="H17" s="182"/>
-      <c r="I17" s="182"/>
-      <c r="J17" s="182" t="str">
+      <c r="E17" s="85">
+        <v>32</v>
+      </c>
+      <c r="F17" s="85">
+        <v>32</v>
+      </c>
+      <c r="G17" s="85"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="85" t="str">
         <f>_xlfn.CONCAT(C17,$B$17)</f>
         <v>identificadorZonaComun</v>
       </c>
-      <c r="K17" s="182" t="s">
+      <c r="K17" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="L17" s="182" t="s">
+      <c r="L17" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="M17" s="182">
-        <v>32</v>
-      </c>
-      <c r="N17" s="182">
-        <v>32</v>
-      </c>
-      <c r="O17" s="182"/>
-      <c r="P17" s="182"/>
-      <c r="Q17" s="182"/>
-      <c r="R17" s="183" t="str">
+      <c r="M17" s="85">
+        <v>32</v>
+      </c>
+      <c r="N17" s="85">
+        <v>32</v>
+      </c>
+      <c r="O17" s="85"/>
+      <c r="P17" s="85"/>
+      <c r="Q17" s="85"/>
+      <c r="R17" s="86" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaComun  en el contexto de Agendas.</v>
       </c>
-      <c r="S17" s="175"/>
+      <c r="S17" s="182"/>
     </row>
     <row r="18" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="170"/>
-      <c r="B18" s="181"/>
-      <c r="C18" s="182" t="s">
+      <c r="A18" s="181"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="182" t="s">
+      <c r="D18" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="182">
+      <c r="E18" s="85">
         <v>3</v>
       </c>
-      <c r="F18" s="182">
+      <c r="F18" s="85">
         <v>50</v>
       </c>
-      <c r="G18" s="182"/>
-      <c r="H18" s="182"/>
-      <c r="I18" s="182"/>
-      <c r="J18" s="182" t="str">
-        <f t="shared" ref="J18:J30" si="2">_xlfn.CONCAT(C18,$B$17)</f>
+      <c r="G18" s="85"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="85" t="str">
+        <f t="shared" ref="J18:J22" si="2">_xlfn.CONCAT(C18,$B$17)</f>
         <v>NombreZonaComun</v>
       </c>
-      <c r="K18" s="182" t="s">
+      <c r="K18" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="L18" s="182" t="s">
+      <c r="L18" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="M18" s="182">
+      <c r="M18" s="85">
         <v>3</v>
       </c>
-      <c r="N18" s="182">
+      <c r="N18" s="85">
         <v>50</v>
       </c>
-      <c r="O18" s="182"/>
-      <c r="P18" s="182"/>
-      <c r="Q18" s="182"/>
-      <c r="R18" s="183" t="str">
+      <c r="O18" s="85"/>
+      <c r="P18" s="85"/>
+      <c r="Q18" s="85"/>
+      <c r="R18" s="86" t="str">
         <f t="shared" ref="R18:R22" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C18," del objeto dominio ",B18,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S18" s="175"/>
+      <c r="S18" s="182"/>
     </row>
     <row r="19" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="170"/>
-      <c r="B19" s="181"/>
-      <c r="C19" s="182" t="s">
+      <c r="A19" s="181"/>
+      <c r="B19" s="185"/>
+      <c r="C19" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="182" t="s">
+      <c r="D19" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="182">
+      <c r="E19" s="85">
         <v>1</v>
       </c>
-      <c r="F19" s="182">
+      <c r="F19" s="85">
         <v>4</v>
       </c>
-      <c r="G19" s="182"/>
-      <c r="H19" s="182"/>
-      <c r="I19" s="182"/>
-      <c r="J19" s="182" t="str">
+      <c r="G19" s="85"/>
+      <c r="H19" s="85"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="85" t="str">
         <f t="shared" si="2"/>
         <v>capacidadPersonasZonaComun</v>
       </c>
-      <c r="K19" s="182" t="s">
+      <c r="K19" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="L19" s="182" t="s">
+      <c r="L19" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="M19" s="182">
+      <c r="M19" s="85">
         <v>1</v>
       </c>
-      <c r="N19" s="182">
+      <c r="N19" s="85">
         <v>4</v>
       </c>
-      <c r="O19" s="182"/>
-      <c r="P19" s="182"/>
-      <c r="Q19" s="182"/>
-      <c r="R19" s="183" t="str">
+      <c r="O19" s="85"/>
+      <c r="P19" s="85"/>
+      <c r="Q19" s="85"/>
+      <c r="R19" s="86" t="str">
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del capacidadPersonas del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S19" s="175"/>
+      <c r="S19" s="182"/>
     </row>
     <row r="20" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="170"/>
-      <c r="B20" s="181"/>
-      <c r="C20" s="182" t="s">
+      <c r="A20" s="181"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="85" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="182" t="s">
+      <c r="D20" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="182">
+      <c r="E20" s="85">
         <v>0</v>
       </c>
-      <c r="F20" s="182">
+      <c r="F20" s="85">
         <v>255</v>
       </c>
-      <c r="G20" s="182"/>
-      <c r="H20" s="182"/>
-      <c r="I20" s="182"/>
-      <c r="J20" s="182" t="str">
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85" t="str">
         <f t="shared" si="2"/>
         <v>descripcionZonaComun</v>
       </c>
-      <c r="K20" s="182" t="s">
+      <c r="K20" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="L20" s="182" t="s">
+      <c r="L20" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="M20" s="182">
+      <c r="M20" s="85">
         <v>0</v>
       </c>
-      <c r="N20" s="182">
+      <c r="N20" s="85">
         <v>255</v>
       </c>
-      <c r="O20" s="182"/>
-      <c r="P20" s="182"/>
-      <c r="Q20" s="182"/>
-      <c r="R20" s="183" t="str">
+      <c r="O20" s="85"/>
+      <c r="P20" s="85"/>
+      <c r="Q20" s="85"/>
+      <c r="R20" s="86" t="str">
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del descripcion del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S20" s="175"/>
+      <c r="S20" s="182"/>
     </row>
     <row r="21" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="170"/>
-      <c r="B21" s="181"/>
-      <c r="C21" s="182" t="s">
+      <c r="A21" s="181"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="85" t="s">
         <v>136</v>
       </c>
-      <c r="D21" s="182" t="s">
+      <c r="D21" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="182">
+      <c r="E21" s="85">
         <v>0</v>
       </c>
-      <c r="F21" s="182">
+      <c r="F21" s="85">
         <v>5000</v>
       </c>
-      <c r="G21" s="182"/>
-      <c r="H21" s="182"/>
-      <c r="I21" s="182"/>
-      <c r="J21" s="182" t="str">
+      <c r="G21" s="85"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="85" t="str">
         <f t="shared" si="2"/>
         <v>normasZonaComun</v>
       </c>
-      <c r="K21" s="182" t="s">
+      <c r="K21" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="L21" s="182" t="s">
+      <c r="L21" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="M21" s="182">
+      <c r="M21" s="85">
         <v>0</v>
       </c>
-      <c r="N21" s="182">
+      <c r="N21" s="85">
         <v>5000</v>
       </c>
-      <c r="O21" s="182"/>
-      <c r="P21" s="182"/>
-      <c r="Q21" s="182"/>
-      <c r="R21" s="183" t="str">
+      <c r="O21" s="85"/>
+      <c r="P21" s="85"/>
+      <c r="Q21" s="85"/>
+      <c r="R21" s="86" t="str">
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del normas del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S21" s="175"/>
+      <c r="S21" s="182"/>
     </row>
     <row r="22" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="170"/>
-      <c r="B22" s="181"/>
-      <c r="C22" s="182" t="s">
+      <c r="A22" s="181"/>
+      <c r="B22" s="185"/>
+      <c r="C22" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="182" t="s">
+      <c r="D22" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E22" s="182">
+      <c r="E22" s="85">
         <v>1</v>
       </c>
-      <c r="F22" s="182">
+      <c r="F22" s="85">
         <v>5</v>
       </c>
-      <c r="G22" s="182"/>
-      <c r="H22" s="182">
+      <c r="G22" s="85"/>
+      <c r="H22" s="85">
         <v>0</v>
       </c>
-      <c r="I22" s="182">
+      <c r="I22" s="85">
         <v>3600</v>
       </c>
-      <c r="J22" s="182" t="str">
+      <c r="J22" s="85" t="str">
         <f t="shared" si="2"/>
         <v>tiempoUsoZonaComun</v>
       </c>
-      <c r="K22" s="182" t="s">
+      <c r="K22" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="L22" s="182" t="s">
+      <c r="L22" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="M22" s="182">
+      <c r="M22" s="85">
         <v>1</v>
       </c>
-      <c r="N22" s="182">
+      <c r="N22" s="85">
         <v>5</v>
       </c>
-      <c r="O22" s="182"/>
-      <c r="P22" s="182">
+      <c r="O22" s="85"/>
+      <c r="P22" s="85">
         <v>0</v>
       </c>
-      <c r="Q22" s="182">
+      <c r="Q22" s="85">
         <v>3600</v>
       </c>
-      <c r="R22" s="183" t="str">
+      <c r="R22" s="86" t="str">
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del tiempoUso del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S22" s="175"/>
+      <c r="S22" s="182"/>
     </row>
     <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="170"/>
-      <c r="B23" s="181"/>
-      <c r="C23" s="182" t="s">
+      <c r="A23" s="181"/>
+      <c r="B23" s="185"/>
+      <c r="C23" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="184" t="s">
+      <c r="D23" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="182"/>
-      <c r="F23" s="182"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="182"/>
-      <c r="I23" s="182"/>
-      <c r="J23" s="182"/>
-      <c r="K23" s="182"/>
-      <c r="L23" s="182"/>
-      <c r="M23" s="182"/>
-      <c r="N23" s="182"/>
-      <c r="O23" s="182"/>
-      <c r="P23" s="182"/>
-      <c r="Q23" s="182"/>
-      <c r="R23" s="183"/>
-      <c r="S23" s="175"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="85"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="85"/>
+      <c r="P23" s="85"/>
+      <c r="Q23" s="85"/>
+      <c r="R23" s="86"/>
+      <c r="S23" s="182"/>
     </row>
     <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="170"/>
-      <c r="B24" s="181"/>
-      <c r="C24" s="182" t="s">
+      <c r="A24" s="181"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="184" t="s">
+      <c r="D24" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="182"/>
-      <c r="F24" s="182"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="182"/>
-      <c r="I24" s="182"/>
-      <c r="J24" s="182"/>
-      <c r="K24" s="182"/>
-      <c r="L24" s="182"/>
-      <c r="M24" s="182"/>
-      <c r="N24" s="182"/>
-      <c r="O24" s="182"/>
-      <c r="P24" s="182"/>
-      <c r="Q24" s="182"/>
-      <c r="R24" s="183"/>
-      <c r="S24" s="175"/>
+      <c r="E24" s="85"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="85"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="85"/>
+      <c r="P24" s="85"/>
+      <c r="Q24" s="85"/>
+      <c r="R24" s="86"/>
+      <c r="S24" s="182"/>
     </row>
     <row r="25" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="170"/>
-      <c r="B25" s="185" t="s">
+      <c r="A25" s="181"/>
+      <c r="B25" s="179" t="s">
         <v>104</v>
       </c>
-      <c r="C25" s="186" t="s">
+      <c r="C25" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="186" t="s">
+      <c r="D25" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="186">
-        <v>32</v>
-      </c>
-      <c r="F25" s="186">
-        <v>32</v>
-      </c>
-      <c r="G25" s="186"/>
-      <c r="H25" s="186"/>
-      <c r="I25" s="186"/>
-      <c r="J25" s="186" t="str">
+      <c r="E25" s="88">
+        <v>32</v>
+      </c>
+      <c r="F25" s="88">
+        <v>32</v>
+      </c>
+      <c r="G25" s="88"/>
+      <c r="H25" s="88"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="88" t="str">
         <f>_xlfn.CONCAT(C25,$B$25)</f>
         <v>identificadorUnidadTiempoUso</v>
       </c>
-      <c r="K25" s="186" t="s">
+      <c r="K25" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="L25" s="186" t="s">
+      <c r="L25" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="M25" s="186">
-        <v>32</v>
-      </c>
-      <c r="N25" s="186">
-        <v>32</v>
-      </c>
-      <c r="O25" s="186"/>
-      <c r="P25" s="186"/>
-      <c r="Q25" s="186"/>
-      <c r="R25" s="187" t="str">
+      <c r="M25" s="88">
+        <v>32</v>
+      </c>
+      <c r="N25" s="88">
+        <v>32</v>
+      </c>
+      <c r="O25" s="88"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="89" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C25," del objeto dominio ",B25,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio UnidadTiempoUso  en el contexto de Agendas.</v>
       </c>
-      <c r="S25" s="175"/>
+      <c r="S25" s="182"/>
     </row>
     <row r="26" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="170"/>
-      <c r="B26" s="185"/>
-      <c r="C26" s="186" t="s">
+      <c r="A26" s="181"/>
+      <c r="B26" s="179"/>
+      <c r="C26" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="186" t="s">
+      <c r="D26" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="186">
+      <c r="E26" s="88">
         <v>3</v>
       </c>
-      <c r="F26" s="186">
+      <c r="F26" s="88">
         <v>50</v>
       </c>
-      <c r="G26" s="186"/>
-      <c r="H26" s="186"/>
-      <c r="I26" s="186"/>
-      <c r="J26" s="186" t="str">
+      <c r="G26" s="88"/>
+      <c r="H26" s="88"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="88" t="str">
         <f t="shared" ref="J26:J28" si="4">_xlfn.CONCAT(C26,$B$25)</f>
         <v>nombreUnidadTiempoUso</v>
       </c>
-      <c r="K26" s="186" t="s">
+      <c r="K26" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="L26" s="186" t="s">
+      <c r="L26" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="M26" s="186">
+      <c r="M26" s="88">
         <v>3</v>
       </c>
-      <c r="N26" s="186">
+      <c r="N26" s="88">
         <v>50</v>
       </c>
-      <c r="O26" s="186"/>
-      <c r="P26" s="186"/>
-      <c r="Q26" s="186"/>
-      <c r="R26" s="187" t="str">
+      <c r="O26" s="88"/>
+      <c r="P26" s="88"/>
+      <c r="Q26" s="88"/>
+      <c r="R26" s="89" t="str">
         <f t="shared" ref="R26:R28" si="5">_xlfn.CONCAT("Atributo que contiene la informacion del ",C26," del objeto dominio ",B26,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S26" s="175"/>
+      <c r="S26" s="182"/>
     </row>
     <row r="27" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="170"/>
-      <c r="B27" s="185"/>
-      <c r="C27" s="186" t="s">
+      <c r="A27" s="181"/>
+      <c r="B27" s="179"/>
+      <c r="C27" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="186" t="s">
+      <c r="D27" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="186">
+      <c r="E27" s="88">
         <v>1</v>
       </c>
-      <c r="F27" s="186">
+      <c r="F27" s="88">
         <v>3</v>
       </c>
-      <c r="G27" s="186"/>
-      <c r="H27" s="186"/>
-      <c r="I27" s="186"/>
-      <c r="J27" s="186" t="str">
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88" t="str">
         <f t="shared" si="4"/>
         <v>abreviaturaUnidadTiempoUso</v>
       </c>
-      <c r="K27" s="186" t="s">
+      <c r="K27" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="L27" s="186" t="s">
+      <c r="L27" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="M27" s="186">
+      <c r="M27" s="88">
         <v>1</v>
       </c>
-      <c r="N27" s="186">
+      <c r="N27" s="88">
         <v>3</v>
       </c>
-      <c r="O27" s="186"/>
-      <c r="P27" s="186"/>
-      <c r="Q27" s="186"/>
-      <c r="R27" s="187" t="str">
+      <c r="O27" s="88"/>
+      <c r="P27" s="88"/>
+      <c r="Q27" s="88"/>
+      <c r="R27" s="89" t="str">
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del abreviatura del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S27" s="175"/>
+      <c r="S27" s="182"/>
     </row>
     <row r="28" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="170"/>
-      <c r="B28" s="185"/>
-      <c r="C28" s="186" t="s">
+      <c r="A28" s="181"/>
+      <c r="B28" s="179"/>
+      <c r="C28" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="186" t="s">
+      <c r="D28" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="E28" s="186">
+      <c r="E28" s="88">
         <v>4</v>
       </c>
-      <c r="F28" s="186">
+      <c r="F28" s="88">
         <v>5</v>
       </c>
-      <c r="G28" s="186"/>
-      <c r="H28" s="186"/>
-      <c r="I28" s="186"/>
-      <c r="J28" s="186" t="str">
+      <c r="G28" s="88"/>
+      <c r="H28" s="88"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="88" t="str">
         <f t="shared" si="4"/>
         <v>enBaseUnidadTiempoUso</v>
       </c>
-      <c r="K28" s="186" t="s">
+      <c r="K28" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="L28" s="186" t="s">
+      <c r="L28" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="M28" s="186">
+      <c r="M28" s="88">
         <v>4</v>
       </c>
-      <c r="N28" s="186">
+      <c r="N28" s="88">
         <v>5</v>
       </c>
-      <c r="O28" s="186"/>
-      <c r="P28" s="186"/>
-      <c r="Q28" s="186"/>
-      <c r="R28" s="187" t="str">
+      <c r="O28" s="88"/>
+      <c r="P28" s="88"/>
+      <c r="Q28" s="88"/>
+      <c r="R28" s="89" t="str">
         <f t="shared" si="5"/>
         <v>Atributo que contiene la informacion del enBase del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S28" s="175"/>
+      <c r="S28" s="182"/>
     </row>
     <row r="29" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="170"/>
-      <c r="B29" s="188" t="s">
+      <c r="A29" s="181"/>
+      <c r="B29" s="180" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="189" t="s">
+      <c r="C29" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="189" t="s">
+      <c r="D29" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E29" s="189">
-        <v>32</v>
-      </c>
-      <c r="F29" s="189">
-        <v>32</v>
-      </c>
-      <c r="G29" s="189"/>
-      <c r="H29" s="189"/>
-      <c r="I29" s="189"/>
-      <c r="J29" s="189" t="str">
+      <c r="E29" s="90">
+        <v>32</v>
+      </c>
+      <c r="F29" s="90">
+        <v>32</v>
+      </c>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90" t="str">
         <f>_xlfn.CONCAT(C29,$B$29)</f>
         <v>identificadorConjuntoResidencial</v>
       </c>
-      <c r="K29" s="189" t="s">
+      <c r="K29" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="L29" s="189" t="s">
+      <c r="L29" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="M29" s="189">
-        <v>32</v>
-      </c>
-      <c r="N29" s="189">
-        <v>32</v>
-      </c>
-      <c r="O29" s="189"/>
-      <c r="P29" s="189"/>
-      <c r="Q29" s="189"/>
-      <c r="R29" s="190" t="str">
+      <c r="M29" s="90">
+        <v>32</v>
+      </c>
+      <c r="N29" s="90">
+        <v>32</v>
+      </c>
+      <c r="O29" s="90"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="90"/>
+      <c r="R29" s="91" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C29," del objeto dominio ",B29,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Agendas.</v>
       </c>
-      <c r="S29" s="175"/>
+      <c r="S29" s="182"/>
     </row>
     <row r="30" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="170"/>
-      <c r="B30" s="188"/>
-      <c r="C30" s="189" t="s">
+      <c r="A30" s="181"/>
+      <c r="B30" s="180"/>
+      <c r="C30" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="189" t="s">
+      <c r="D30" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="189">
+      <c r="E30" s="90">
         <v>1</v>
       </c>
-      <c r="F30" s="189">
+      <c r="F30" s="90">
         <v>50</v>
       </c>
-      <c r="G30" s="189"/>
-      <c r="H30" s="189"/>
-      <c r="I30" s="189"/>
-      <c r="J30" s="189" t="str">
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90" t="str">
         <f>_xlfn.CONCAT(C30,$B$29)</f>
         <v>nombreConjuntoResidencial</v>
       </c>
-      <c r="K30" s="189" t="s">
+      <c r="K30" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="L30" s="189" t="s">
+      <c r="L30" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="M30" s="189">
+      <c r="M30" s="90">
         <v>1</v>
       </c>
-      <c r="N30" s="189">
+      <c r="N30" s="90">
         <v>50</v>
       </c>
-      <c r="O30" s="189"/>
-      <c r="P30" s="189"/>
-      <c r="Q30" s="189"/>
-      <c r="R30" s="190" t="str">
+      <c r="O30" s="90"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="90"/>
+      <c r="R30" s="91" t="str">
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C30," del objeto dominio ",B30,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Agendas.</v>
       </c>
-      <c r="S30" s="175"/>
+      <c r="S30" s="182"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
     <mergeCell ref="B25:B28"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="A5:A30"/>
@@ -7369,12 +7369,6 @@
     <mergeCell ref="B5:B10"/>
     <mergeCell ref="B11:B16"/>
     <mergeCell ref="B17:B24"/>
-    <mergeCell ref="B1:S1"/>
-    <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="J3:Q3"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="S3:S4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" location="Residente!A12" display="identificador" xr:uid="{80169430-9A83-40F6-BE78-C9769A7F908B}"/>
@@ -7418,75 +7412,75 @@
       <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="120" t="str">
+      <c r="B1" s="151" t="str">
         <f>Agendas!D8</f>
         <v>Agenda ConjuntosResidenciales-0001</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="121"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="152"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="115"/>
+      <c r="A2" s="146"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="148"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="186" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124" t="s">
+      <c r="B3" s="187"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="187"/>
+      <c r="H3" s="187"/>
+      <c r="I3" s="187"/>
+      <c r="J3" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="124"/>
-      <c r="O3" s="124"/>
-      <c r="P3" s="124"/>
-      <c r="Q3" s="124"/>
-      <c r="R3" s="148" t="s">
+      <c r="K3" s="187"/>
+      <c r="L3" s="187"/>
+      <c r="M3" s="187"/>
+      <c r="N3" s="187"/>
+      <c r="O3" s="187"/>
+      <c r="P3" s="187"/>
+      <c r="Q3" s="187"/>
+      <c r="R3" s="188" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="150" t="s">
+      <c r="S3" s="190" t="s">
         <v>44</v>
       </c>
     </row>
@@ -7542,14 +7536,14 @@
       <c r="Q4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="149"/>
-      <c r="S4" s="151"/>
+      <c r="R4" s="189"/>
+      <c r="S4" s="191"/>
     </row>
     <row r="5" spans="1:19" ht="28.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="138" t="s">
+      <c r="A5" s="192" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="142" t="s">
+      <c r="B5" s="197" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="51" t="s">
@@ -7590,13 +7584,13 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C5," del objeto dominio ",B5,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaComun  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S5" s="141" t="s">
+      <c r="S5" s="195" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="139"/>
-      <c r="B6" s="143"/>
+      <c r="A6" s="193"/>
+      <c r="B6" s="198"/>
       <c r="C6" s="51" t="s">
         <v>4</v>
       </c>
@@ -7635,11 +7629,11 @@
         <f t="shared" ref="R6:R10" si="1">_xlfn.CONCAT("Atributo que contiene la informacion del ",C6," del objeto dominio ",B6,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del Nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S6" s="141"/>
+      <c r="S6" s="195"/>
     </row>
     <row r="7" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="139"/>
-      <c r="B7" s="143"/>
+      <c r="A7" s="193"/>
+      <c r="B7" s="198"/>
       <c r="C7" s="51" t="s">
         <v>95</v>
       </c>
@@ -7678,11 +7672,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del capacidadPersonas del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S7" s="141"/>
+      <c r="S7" s="195"/>
     </row>
     <row r="8" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="139"/>
-      <c r="B8" s="143"/>
+      <c r="A8" s="193"/>
+      <c r="B8" s="198"/>
       <c r="C8" s="51" t="s">
         <v>108</v>
       </c>
@@ -7721,11 +7715,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del descripcion del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S8" s="141"/>
+      <c r="S8" s="195"/>
     </row>
     <row r="9" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="139"/>
-      <c r="B9" s="143"/>
+      <c r="A9" s="193"/>
+      <c r="B9" s="198"/>
       <c r="C9" s="51" t="s">
         <v>136</v>
       </c>
@@ -7764,11 +7758,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del normas del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S9" s="141"/>
+      <c r="S9" s="195"/>
     </row>
     <row r="10" spans="1:19" ht="30.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="139"/>
-      <c r="B10" s="143"/>
+      <c r="A10" s="193"/>
+      <c r="B10" s="198"/>
       <c r="C10" s="51" t="s">
         <v>96</v>
       </c>
@@ -7815,11 +7809,11 @@
         <f t="shared" si="1"/>
         <v>Atributo que contiene la informacion del tiempoUso del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S10" s="141"/>
+      <c r="S10" s="195"/>
     </row>
     <row r="11" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="139"/>
-      <c r="B11" s="143"/>
+      <c r="A11" s="193"/>
+      <c r="B11" s="198"/>
       <c r="C11" s="51" t="s">
         <v>97</v>
       </c>
@@ -7840,11 +7834,11 @@
       <c r="P11" s="51"/>
       <c r="Q11" s="52"/>
       <c r="R11" s="68"/>
-      <c r="S11" s="141"/>
+      <c r="S11" s="195"/>
     </row>
     <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="139"/>
-      <c r="B12" s="144"/>
+      <c r="A12" s="193"/>
+      <c r="B12" s="199"/>
       <c r="C12" s="51" t="s">
         <v>62</v>
       </c>
@@ -7865,11 +7859,11 @@
       <c r="P12" s="51"/>
       <c r="Q12" s="52"/>
       <c r="R12" s="68"/>
-      <c r="S12" s="141"/>
+      <c r="S12" s="195"/>
     </row>
     <row r="13" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="139"/>
-      <c r="B13" s="145" t="s">
+      <c r="A13" s="193"/>
+      <c r="B13" s="200" t="s">
         <v>104</v>
       </c>
       <c r="C13" s="71" t="s">
@@ -7910,11 +7904,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C13," del objeto dominio ",B13,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio UnidadTiempoUso  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S13" s="141"/>
+      <c r="S13" s="195"/>
     </row>
     <row r="14" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="139"/>
-      <c r="B14" s="146"/>
+      <c r="A14" s="193"/>
+      <c r="B14" s="201"/>
       <c r="C14" s="71" t="s">
         <v>57</v>
       </c>
@@ -7953,11 +7947,11 @@
         <f t="shared" ref="R14:R16" si="3">_xlfn.CONCAT("Atributo que contiene la informacion del ",C14," del objeto dominio ",B14,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S14" s="141"/>
+      <c r="S14" s="195"/>
     </row>
     <row r="15" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="139"/>
-      <c r="B15" s="146"/>
+      <c r="A15" s="193"/>
+      <c r="B15" s="201"/>
       <c r="C15" s="71" t="s">
         <v>105</v>
       </c>
@@ -7996,11 +7990,11 @@
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del abreviatura del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S15" s="141"/>
+      <c r="S15" s="195"/>
     </row>
     <row r="16" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="139"/>
-      <c r="B16" s="147"/>
+      <c r="A16" s="193"/>
+      <c r="B16" s="202"/>
       <c r="C16" s="71" t="s">
         <v>106</v>
       </c>
@@ -8039,11 +8033,11 @@
         <f t="shared" si="3"/>
         <v>Atributo que contiene la informacion del enBase del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S16" s="141"/>
+      <c r="S16" s="195"/>
     </row>
     <row r="17" spans="1:19" ht="60.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="139"/>
-      <c r="B17" s="127" t="s">
+      <c r="A17" s="193"/>
+      <c r="B17" s="196" t="s">
         <v>61</v>
       </c>
       <c r="C17" s="32" t="s">
@@ -8084,11 +8078,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C17," del objeto dominio ",B17,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S17" s="141"/>
+      <c r="S17" s="195"/>
     </row>
     <row r="18" spans="1:19" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="140"/>
-      <c r="B18" s="127"/>
+      <c r="A18" s="194"/>
+      <c r="B18" s="196"/>
       <c r="C18" s="32" t="s">
         <v>57</v>
       </c>
@@ -8127,21 +8121,21 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C18," del objeto dominio ",B18,"  en el contexto de ",$A$5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S18" s="141"/>
+      <c r="S18" s="195"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A5:A18"/>
+    <mergeCell ref="S5:S18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B5:B12"/>
+    <mergeCell ref="B13:B16"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="J3:Q3"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
-    <mergeCell ref="A5:A18"/>
-    <mergeCell ref="S5:S18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B5:B12"/>
-    <mergeCell ref="B13:B16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" location="'Agenda ConjuntosResidenciales-0'!B13" display="UnidadTiempoUso" xr:uid="{7145F6A3-A24A-4F31-B98A-658FB31AEB42}"/>

--- a/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelo de dominio anémico/Modelo de dominio anémico de contextos-VictusResidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelo de dominio anémico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A3C368-59A1-4926-BAFA-AB5BF8B373BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F118F89-A757-43E2-BCED-B27A78E9FAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{082AFB46-52C9-4E4C-AE4E-19443AA1B53B}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="3" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="166">
   <si>
     <t>Problema/Dominio:</t>
   </si>
@@ -476,9 +476,6 @@
   </si>
   <si>
     <t>Este dato es de tipo logico el cual dice si esta disponible o no disponible un turno</t>
-  </si>
-  <si>
-    <t>Este dato representa con que agenda está relacionada el turno.</t>
   </si>
   <si>
     <t>disponibilidad</t>
@@ -1763,6 +1760,30 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1791,30 +1812,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2818,7 +2815,7 @@
       <c r="S4" s="191"/>
     </row>
     <row r="5" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="175" t="s">
+      <c r="A5" s="165" t="s">
         <v>83</v>
       </c>
       <c r="B5" s="208" t="s">
@@ -2867,8 +2864,8 @@
       </c>
     </row>
     <row r="6" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="175"/>
-      <c r="B6" s="169"/>
+      <c r="A6" s="165"/>
+      <c r="B6" s="177"/>
       <c r="C6" s="51" t="s">
         <v>119</v>
       </c>
@@ -2910,8 +2907,8 @@
       <c r="S6" s="203"/>
     </row>
     <row r="7" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="175"/>
-      <c r="B7" s="169"/>
+      <c r="A7" s="165"/>
+      <c r="B7" s="177"/>
       <c r="C7" s="51" t="s">
         <v>120</v>
       </c>
@@ -2953,8 +2950,8 @@
       <c r="S7" s="203"/>
     </row>
     <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="175"/>
-      <c r="B8" s="169"/>
+      <c r="A8" s="165"/>
+      <c r="B8" s="177"/>
       <c r="C8" s="51" t="s">
         <v>121</v>
       </c>
@@ -2996,8 +2993,8 @@
       <c r="S8" s="203"/>
     </row>
     <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="175"/>
-      <c r="B9" s="169"/>
+      <c r="A9" s="165"/>
+      <c r="B9" s="177"/>
       <c r="C9" s="51" t="s">
         <v>122</v>
       </c>
@@ -3039,8 +3036,8 @@
       <c r="S9" s="203"/>
     </row>
     <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="175"/>
-      <c r="B10" s="169"/>
+      <c r="A10" s="165"/>
+      <c r="B10" s="177"/>
       <c r="C10" s="74" t="s">
         <v>123</v>
       </c>
@@ -3082,8 +3079,8 @@
       <c r="S10" s="203"/>
     </row>
     <row r="11" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="175"/>
-      <c r="B11" s="169"/>
+      <c r="A11" s="165"/>
+      <c r="B11" s="177"/>
       <c r="C11" s="74" t="s">
         <v>124</v>
       </c>
@@ -3125,8 +3122,8 @@
       <c r="S11" s="203"/>
     </row>
     <row r="12" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="175"/>
-      <c r="B12" s="169"/>
+      <c r="A12" s="165"/>
+      <c r="B12" s="177"/>
       <c r="C12" s="74" t="s">
         <v>125</v>
       </c>
@@ -3168,8 +3165,8 @@
       <c r="S12" s="203"/>
     </row>
     <row r="13" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="175"/>
-      <c r="B13" s="169"/>
+      <c r="A13" s="165"/>
+      <c r="B13" s="177"/>
       <c r="C13" s="74" t="s">
         <v>126</v>
       </c>
@@ -3211,8 +3208,8 @@
       <c r="S13" s="203"/>
     </row>
     <row r="14" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="175"/>
-      <c r="B14" s="169"/>
+      <c r="A14" s="165"/>
+      <c r="B14" s="177"/>
       <c r="C14" s="74" t="s">
         <v>127</v>
       </c>
@@ -3254,8 +3251,8 @@
       <c r="S14" s="203"/>
     </row>
     <row r="15" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="175"/>
-      <c r="B15" s="170"/>
+      <c r="A15" s="165"/>
+      <c r="B15" s="178"/>
       <c r="C15" s="74" t="s">
         <v>128</v>
       </c>
@@ -3305,7 +3302,7 @@
       <c r="S15" s="203"/>
     </row>
     <row r="16" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="175"/>
+      <c r="A16" s="165"/>
       <c r="B16" s="207" t="s">
         <v>64</v>
       </c>
@@ -3350,7 +3347,7 @@
       <c r="S16" s="203"/>
     </row>
     <row r="17" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="175"/>
+      <c r="A17" s="165"/>
       <c r="B17" s="207"/>
       <c r="C17" s="50" t="s">
         <v>4</v>
@@ -3393,7 +3390,7 @@
       <c r="S17" s="203"/>
     </row>
     <row r="18" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="175"/>
+      <c r="A18" s="165"/>
       <c r="B18" s="207"/>
       <c r="C18" s="31" t="s">
         <v>90</v>
@@ -3428,7 +3425,7 @@
       <c r="S18" s="203"/>
     </row>
     <row r="19" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="175"/>
+      <c r="A19" s="165"/>
       <c r="B19" s="207"/>
       <c r="C19" s="31" t="s">
         <v>94</v>
@@ -3463,7 +3460,7 @@
       <c r="S19" s="203"/>
     </row>
     <row r="20" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="175"/>
+      <c r="A20" s="165"/>
       <c r="B20" s="207"/>
       <c r="C20" s="31" t="s">
         <v>109</v>
@@ -3488,8 +3485,8 @@
       <c r="S20" s="203"/>
     </row>
     <row r="21" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="175"/>
-      <c r="B21" s="161" t="s">
+      <c r="A21" s="165"/>
+      <c r="B21" s="169" t="s">
         <v>65</v>
       </c>
       <c r="C21" s="32" t="s">
@@ -3533,8 +3530,8 @@
       <c r="S21" s="203"/>
     </row>
     <row r="22" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="175"/>
-      <c r="B22" s="161"/>
+      <c r="A22" s="165"/>
+      <c r="B22" s="169"/>
       <c r="C22" s="32" t="s">
         <v>129</v>
       </c>
@@ -3576,8 +3573,8 @@
       <c r="S22" s="203"/>
     </row>
     <row r="23" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="175"/>
-      <c r="B23" s="161"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="169"/>
       <c r="C23" s="32" t="s">
         <v>130</v>
       </c>
@@ -3609,8 +3606,8 @@
       <c r="S23" s="203"/>
     </row>
     <row r="24" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="175"/>
-      <c r="B24" s="161"/>
+      <c r="A24" s="165"/>
+      <c r="B24" s="169"/>
       <c r="C24" s="32" t="s">
         <v>132</v>
       </c>
@@ -3642,8 +3639,8 @@
       <c r="S24" s="203"/>
     </row>
     <row r="25" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="175"/>
-      <c r="B25" s="161"/>
+      <c r="A25" s="165"/>
+      <c r="B25" s="169"/>
       <c r="C25" s="32" t="s">
         <v>133</v>
       </c>
@@ -3676,7 +3673,7 @@
     </row>
     <row r="26" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="206"/>
-      <c r="B26" s="161"/>
+      <c r="B26" s="169"/>
       <c r="C26" s="32" t="s">
         <v>110</v>
       </c>
@@ -5024,10 +5021,10 @@
       <c r="S4" s="160"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="171" t="s">
+      <c r="B5" s="161" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="104" t="s">
@@ -5065,15 +5062,15 @@
       <c r="P5" s="106"/>
       <c r="Q5" s="107"/>
       <c r="R5" s="108" t="s">
-        <v>158</v>
-      </c>
-      <c r="S5" s="177" t="s">
+        <v>157</v>
+      </c>
+      <c r="S5" s="167" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="175"/>
-      <c r="B6" s="172"/>
+      <c r="A6" s="165"/>
+      <c r="B6" s="162"/>
       <c r="C6" s="104" t="s">
         <v>57</v>
       </c>
@@ -5090,7 +5087,7 @@
       <c r="H6" s="104"/>
       <c r="I6" s="104"/>
       <c r="J6" s="105" t="str">
-        <f t="shared" ref="J6:J14" si="0">_xlfn.CONCAT(C6,$B$5)</f>
+        <f t="shared" ref="J6:J13" si="0">_xlfn.CONCAT(C6,$B$5)</f>
         <v>nombreResidente</v>
       </c>
       <c r="K6" s="105" t="s">
@@ -5109,15 +5106,15 @@
       <c r="P6" s="106"/>
       <c r="Q6" s="107"/>
       <c r="R6" s="108" t="s">
-        <v>159</v>
-      </c>
-      <c r="S6" s="177"/>
+        <v>158</v>
+      </c>
+      <c r="S6" s="167"/>
     </row>
     <row r="7" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="175"/>
-      <c r="B7" s="172"/>
+      <c r="A7" s="165"/>
+      <c r="B7" s="162"/>
       <c r="C7" s="104" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D7" s="105" t="s">
         <v>58</v>
@@ -5151,15 +5148,15 @@
       <c r="P7" s="106"/>
       <c r="Q7" s="107"/>
       <c r="R7" s="108" t="s">
-        <v>160</v>
-      </c>
-      <c r="S7" s="177"/>
+        <v>159</v>
+      </c>
+      <c r="S7" s="167"/>
     </row>
     <row r="8" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="175"/>
-      <c r="B8" s="172"/>
+      <c r="A8" s="165"/>
+      <c r="B8" s="162"/>
       <c r="C8" s="104" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D8" s="105" t="s">
         <v>58</v>
@@ -5193,13 +5190,13 @@
       <c r="P8" s="106"/>
       <c r="Q8" s="107"/>
       <c r="R8" s="108" t="s">
-        <v>161</v>
-      </c>
-      <c r="S8" s="177"/>
+        <v>160</v>
+      </c>
+      <c r="S8" s="167"/>
     </row>
     <row r="9" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="175"/>
-      <c r="B9" s="172"/>
+      <c r="A9" s="165"/>
+      <c r="B9" s="162"/>
       <c r="C9" s="104" t="s">
         <v>117</v>
       </c>
@@ -5227,18 +5224,18 @@
       <c r="P9" s="106"/>
       <c r="Q9" s="107"/>
       <c r="R9" s="108" t="s">
-        <v>162</v>
-      </c>
-      <c r="S9" s="177"/>
+        <v>161</v>
+      </c>
+      <c r="S9" s="167"/>
     </row>
     <row r="10" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="175"/>
-      <c r="B10" s="172"/>
+      <c r="A10" s="165"/>
+      <c r="B10" s="162"/>
       <c r="C10" s="104" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="105" t="s">
         <v>153</v>
-      </c>
-      <c r="D10" s="105" t="s">
-        <v>154</v>
       </c>
       <c r="E10" s="104"/>
       <c r="F10" s="104"/>
@@ -5253,7 +5250,7 @@
         <v>59</v>
       </c>
       <c r="L10" s="105" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M10" s="104"/>
       <c r="N10" s="104"/>
@@ -5261,15 +5258,15 @@
       <c r="P10" s="106"/>
       <c r="Q10" s="107"/>
       <c r="R10" s="108" t="s">
-        <v>163</v>
-      </c>
-      <c r="S10" s="177"/>
+        <v>162</v>
+      </c>
+      <c r="S10" s="167"/>
     </row>
     <row r="11" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="175"/>
-      <c r="B11" s="172"/>
+      <c r="A11" s="165"/>
+      <c r="B11" s="162"/>
       <c r="C11" s="104" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D11" s="105" t="s">
         <v>116</v>
@@ -5295,15 +5292,15 @@
       <c r="P11" s="106"/>
       <c r="Q11" s="107"/>
       <c r="R11" s="108" t="s">
-        <v>164</v>
-      </c>
-      <c r="S11" s="177"/>
+        <v>163</v>
+      </c>
+      <c r="S11" s="167"/>
     </row>
     <row r="12" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="175"/>
-      <c r="B12" s="172"/>
+      <c r="A12" s="165"/>
+      <c r="B12" s="162"/>
       <c r="C12" s="104" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" s="105" t="s">
         <v>137</v>
@@ -5337,15 +5334,15 @@
       <c r="P12" s="106"/>
       <c r="Q12" s="107"/>
       <c r="R12" s="108" t="s">
-        <v>165</v>
-      </c>
-      <c r="S12" s="177"/>
+        <v>164</v>
+      </c>
+      <c r="S12" s="167"/>
     </row>
     <row r="13" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="175"/>
-      <c r="B13" s="172"/>
+      <c r="A13" s="165"/>
+      <c r="B13" s="162"/>
       <c r="C13" s="104" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D13" s="105" t="s">
         <v>137</v>
@@ -5379,13 +5376,13 @@
       <c r="P13" s="106"/>
       <c r="Q13" s="107"/>
       <c r="R13" s="108" t="s">
-        <v>166</v>
-      </c>
-      <c r="S13" s="177"/>
+        <v>165</v>
+      </c>
+      <c r="S13" s="167"/>
     </row>
     <row r="14" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="175"/>
-      <c r="B14" s="173"/>
+      <c r="A14" s="165"/>
+      <c r="B14" s="163"/>
       <c r="C14" s="104" t="s">
         <v>115</v>
       </c>
@@ -5406,11 +5403,11 @@
       <c r="P14" s="106"/>
       <c r="Q14" s="107"/>
       <c r="R14" s="108"/>
-      <c r="S14" s="177"/>
+      <c r="S14" s="167"/>
     </row>
     <row r="15" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="175"/>
-      <c r="B15" s="169" t="s">
+      <c r="A15" s="165"/>
+      <c r="B15" s="177" t="s">
         <v>82</v>
       </c>
       <c r="C15" s="62" t="s">
@@ -5451,11 +5448,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C15," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S15" s="177"/>
+      <c r="S15" s="167"/>
     </row>
     <row r="16" spans="1:19" ht="46.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="175"/>
-      <c r="B16" s="169"/>
+      <c r="A16" s="165"/>
+      <c r="B16" s="177"/>
       <c r="C16" s="58" t="s">
         <v>92</v>
       </c>
@@ -5494,11 +5491,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C16," del objeto dominio ",B15,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del numeroVivienda del objeto dominio Inmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S16" s="177"/>
+      <c r="S16" s="167"/>
     </row>
     <row r="17" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="175"/>
-      <c r="B17" s="169"/>
+      <c r="A17" s="165"/>
+      <c r="B17" s="177"/>
       <c r="C17" s="62" t="s">
         <v>101</v>
       </c>
@@ -5519,11 +5516,11 @@
       <c r="P17" s="51"/>
       <c r="Q17" s="52"/>
       <c r="R17" s="68"/>
-      <c r="S17" s="177"/>
+      <c r="S17" s="167"/>
     </row>
     <row r="18" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="175"/>
-      <c r="B18" s="170"/>
+      <c r="A18" s="165"/>
+      <c r="B18" s="178"/>
       <c r="C18" s="62" t="s">
         <v>91</v>
       </c>
@@ -5544,11 +5541,11 @@
       <c r="P18" s="51"/>
       <c r="Q18" s="52"/>
       <c r="R18" s="68"/>
-      <c r="S18" s="177"/>
+      <c r="S18" s="167"/>
     </row>
     <row r="19" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="175"/>
-      <c r="B19" s="162" t="s">
+      <c r="A19" s="165"/>
+      <c r="B19" s="170" t="s">
         <v>98</v>
       </c>
       <c r="C19" s="50" t="s">
@@ -5589,11 +5586,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C19," del objeto dominio ",B19,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio TipoInmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S19" s="177"/>
+      <c r="S19" s="167"/>
     </row>
     <row r="20" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="175"/>
-      <c r="B20" s="163"/>
+      <c r="A20" s="165"/>
+      <c r="B20" s="171"/>
       <c r="C20" s="50" t="s">
         <v>57</v>
       </c>
@@ -5632,11 +5629,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C20," del objeto dominio ",B20,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S20" s="177"/>
+      <c r="S20" s="167"/>
     </row>
     <row r="21" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="175"/>
-      <c r="B21" s="166" t="s">
+      <c r="A21" s="165"/>
+      <c r="B21" s="174" t="s">
         <v>81</v>
       </c>
       <c r="C21" s="55" t="s">
@@ -5677,11 +5674,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C21," del objeto dominio ",B21,"  en el contexto de ",A3,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ZonaInmueble  en el contexto de Caracterización Origen.</v>
       </c>
-      <c r="S21" s="177"/>
+      <c r="S21" s="167"/>
     </row>
     <row r="22" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="175"/>
-      <c r="B22" s="167"/>
+      <c r="A22" s="165"/>
+      <c r="B22" s="175"/>
       <c r="C22" s="55" t="s">
         <v>135</v>
       </c>
@@ -5728,11 +5725,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C22," del objeto dominio ",B22,"  en el contexto de ",A4,".")</f>
         <v>Atributo que contiene la informacion del numeroZonaInmueble del objeto dominio   en el contexto de Contexto.</v>
       </c>
-      <c r="S22" s="177"/>
+      <c r="S22" s="167"/>
     </row>
     <row r="23" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="175"/>
-      <c r="B23" s="167"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="175"/>
       <c r="C23" s="55" t="s">
         <v>102</v>
       </c>
@@ -5753,11 +5750,11 @@
       <c r="P23" s="56"/>
       <c r="Q23" s="57"/>
       <c r="R23" s="60"/>
-      <c r="S23" s="177"/>
+      <c r="S23" s="167"/>
     </row>
     <row r="24" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="175"/>
-      <c r="B24" s="168"/>
+      <c r="A24" s="165"/>
+      <c r="B24" s="176"/>
       <c r="C24" s="55" t="s">
         <v>62</v>
       </c>
@@ -5778,11 +5775,11 @@
       <c r="P24" s="56"/>
       <c r="Q24" s="57"/>
       <c r="R24" s="60"/>
-      <c r="S24" s="177"/>
+      <c r="S24" s="167"/>
     </row>
     <row r="25" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="175"/>
-      <c r="B25" s="164" t="s">
+      <c r="A25" s="165"/>
+      <c r="B25" s="172" t="s">
         <v>99</v>
       </c>
       <c r="C25" s="64" t="s">
@@ -5823,11 +5820,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C25," del objeto dominio ",B25,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio TipoZonaInmueble  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S25" s="177"/>
+      <c r="S25" s="167"/>
     </row>
     <row r="26" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="175"/>
-      <c r="B26" s="165"/>
+      <c r="A26" s="165"/>
+      <c r="B26" s="173"/>
       <c r="C26" s="64" t="s">
         <v>57</v>
       </c>
@@ -5866,11 +5863,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C26," del objeto dominio ",B26,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S26" s="177"/>
+      <c r="S26" s="167"/>
     </row>
     <row r="27" spans="1:19" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="175"/>
-      <c r="B27" s="161" t="s">
+      <c r="A27" s="165"/>
+      <c r="B27" s="169" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="32" t="s">
@@ -5911,11 +5908,11 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C27," del objeto dominio ",B27,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del identificador del objeto dominio ConjuntoResidencial  en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S27" s="177"/>
+      <c r="S27" s="167"/>
     </row>
     <row r="28" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="176"/>
-      <c r="B28" s="161"/>
+      <c r="A28" s="166"/>
+      <c r="B28" s="169"/>
       <c r="C28" s="32" t="s">
         <v>57</v>
       </c>
@@ -5954,7 +5951,7 @@
         <f>_xlfn.CONCAT("Atributo que contiene la informacion del ",C28," del objeto dominio ",B28,"  en el contexto de ",A5,".")</f>
         <v>Atributo que contiene la informacion del nombre del objeto dominio   en el contexto de Conjuntos Residenciales.</v>
       </c>
-      <c r="S28" s="178"/>
+      <c r="S28" s="168"/>
     </row>
     <row r="35" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E35" s="70"/>
@@ -6393,8 +6390,8 @@
       <c r="H6" s="78"/>
       <c r="I6" s="78"/>
       <c r="J6" s="78" t="str">
-        <f t="shared" ref="J6:J9" si="0">_xlfn.CONCAT(C6,$B$5)</f>
-        <v>numeroTurnoTurno</v>
+        <f>_xlfn.CONCAT(C6,)</f>
+        <v>numeroTurno</v>
       </c>
       <c r="K6" s="79" t="s">
         <v>59</v>
@@ -6431,7 +6428,7 @@
       <c r="H7" s="78"/>
       <c r="I7" s="78"/>
       <c r="J7" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J6:J9" si="0">_xlfn.CONCAT(C7,$B$5)</f>
         <v>horaInicioTurno</v>
       </c>
       <c r="K7" s="79" t="s">
@@ -6532,24 +6529,15 @@
       <c r="G10" s="78"/>
       <c r="H10" s="78"/>
       <c r="I10" s="78"/>
-      <c r="J10" s="78" t="str">
-        <f>_xlfn.CONCAT(C10,$B$5)</f>
-        <v>agendaTurno</v>
-      </c>
-      <c r="K10" s="79" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="79" t="s">
-        <v>64</v>
-      </c>
+      <c r="J10" s="78"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
       <c r="M10" s="79"/>
       <c r="N10" s="79"/>
       <c r="O10" s="79"/>
       <c r="P10" s="79"/>
       <c r="Q10" s="79"/>
-      <c r="R10" s="80" t="s">
-        <v>143</v>
-      </c>
+      <c r="R10" s="80"/>
       <c r="S10" s="182"/>
     </row>
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6592,7 +6580,7 @@
       <c r="P11" s="77"/>
       <c r="Q11" s="77"/>
       <c r="R11" s="77" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S11" s="182"/>
     </row>
@@ -6615,7 +6603,7 @@
       <c r="H12" s="77"/>
       <c r="I12" s="77"/>
       <c r="J12" s="77" t="str">
-        <f t="shared" ref="J12:J16" si="1">_xlfn.CONCAT(C12,$B$11)</f>
+        <f t="shared" ref="J12:J15" si="1">_xlfn.CONCAT(C12,$B$11)</f>
         <v>nombreAgenda</v>
       </c>
       <c r="K12" s="77" t="s">
@@ -6634,7 +6622,7 @@
       <c r="P12" s="77"/>
       <c r="Q12" s="77"/>
       <c r="R12" s="84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S12" s="182"/>
     </row>
@@ -6642,7 +6630,7 @@
       <c r="A13" s="181"/>
       <c r="B13" s="184"/>
       <c r="C13" s="77" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D13" s="77" t="s">
         <v>134</v>
@@ -6668,7 +6656,7 @@
       <c r="P13" s="77"/>
       <c r="Q13" s="77"/>
       <c r="R13" s="84" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="S13" s="182"/>
     </row>
@@ -6702,7 +6690,7 @@
       <c r="P14" s="77"/>
       <c r="Q14" s="77"/>
       <c r="R14" s="84" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S14" s="182"/>
     </row>
@@ -6736,7 +6724,7 @@
       <c r="P15" s="77"/>
       <c r="Q15" s="77"/>
       <c r="R15" s="77" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S15" s="182"/>
     </row>
@@ -6754,23 +6742,16 @@
       <c r="G16" s="77"/>
       <c r="H16" s="77"/>
       <c r="I16" s="77"/>
-      <c r="J16" s="77" t="str">
-        <f t="shared" si="1"/>
-        <v>zonaComunAgenda</v>
-      </c>
-      <c r="K16" s="77" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="77" t="s">
-        <v>41</v>
-      </c>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
       <c r="M16" s="77"/>
       <c r="N16" s="77"/>
       <c r="O16" s="77"/>
       <c r="P16" s="77"/>
       <c r="Q16" s="77"/>
       <c r="R16" s="84" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S16" s="182"/>
     </row>
